--- a/4 четверть_13_JavaScript_sugarJS.xlsx
+++ b/4 четверть_13_JavaScript_sugarJS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA410CE-F335-4ED7-BDA4-1E50BCEE77C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC510D96-5667-406B-B33F-CA5E55D4AEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-360" yWindow="-216" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="192" yWindow="-216" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sugarjs" sheetId="20" r:id="rId1"/>
@@ -6482,57 +6482,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>create</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Array</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - не модифицирует оригинальный массив, а возвращает новый</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
     <t>Простое преобразование значений</t>
   </si>
   <si>
@@ -17985,6 +17934,128 @@
 [1,2,3].includes(2, 3) false
 аналог includes
 tfaAccessChannel.filter(item =&gt; item.frontName === 'Max').length</t>
+  </si>
+  <si>
+    <r>
+      <t>create</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Array</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - не модифицирует оригинальный массив, а возвращает новый</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ДОПОЛНИТЕЛЬНО</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>map(Number)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+const result = timeString.split(':')  // ["14", "30"]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  .map(Number)  // [14, 30]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Действует по принципу лямбда выражения в Java Array::append. Позволяет не прописывать отдельно итерируемый объект в параметры единстенной функции</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -19913,7 +19984,7 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -20024,7 +20095,7 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -20048,10 +20119,10 @@
         <v>13</v>
       </c>
       <c r="C20" s="37" t="s">
+        <v>912</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>913</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>914</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="1"/>
@@ -20082,7 +20153,7 @@
         <v>206</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>1</v>
@@ -20093,153 +20164,153 @@
     </row>
     <row r="23" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>1019</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>974</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>1020</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>1024</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>974</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>1025</v>
-      </c>
       <c r="E24" s="32" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>1070</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>1072</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>1071</v>
-      </c>
       <c r="E25" s="32" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D26" s="32" t="s">
         <v>971</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>974</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D26" s="32" t="s">
+      <c r="E26" s="32" t="s">
         <v>972</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D31" s="32" t="s">
         <v>1070</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D31" s="32" t="s">
-        <v>1071</v>
-      </c>
       <c r="E31" s="32" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>908</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="D32" s="17" t="s">
         <v>442</v>
-      </c>
-      <c r="B32" s="27" t="s">
-        <v>909</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
@@ -20247,10 +20318,10 @@
         <v>97</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>98</v>
@@ -20258,7 +20329,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
@@ -20266,13 +20337,13 @@
         <v>236</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>673</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>237</v>
@@ -20281,10 +20352,10 @@
     <row r="36" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>677</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>678</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -20292,10 +20363,10 @@
     <row r="37" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -20303,10 +20374,10 @@
     <row r="38" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>682</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -20365,7 +20436,7 @@
         <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>76</v>
@@ -20572,10 +20643,10 @@
         <v>44</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>46</v>
@@ -20771,7 +20842,7 @@
         <v>50</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>49</v>
@@ -20785,7 +20856,7 @@
         <v>50</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>92</v>
@@ -20799,7 +20870,7 @@
         <v>199</v>
       </c>
       <c r="C76" s="35" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="D76" s="14" t="s">
         <v>147</v>
@@ -20814,7 +20885,7 @@
         <v>199</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>67</v>
@@ -20851,10 +20922,10 @@
         <v>97</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>394</v>
+        <v>1089</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>98</v>
@@ -20868,7 +20939,7 @@
         <v>393</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>43</v>
@@ -21129,7 +21200,7 @@
         <v>116</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C101" s="14" t="s">
         <v>118</v>
@@ -21146,7 +21217,7 @@
         <v>120</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C102" s="14" t="s">
         <v>122</v>
@@ -21444,68 +21515,68 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B11" s="1"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -21515,17 +21586,17 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
@@ -21553,7 +21624,7 @@
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -21567,15 +21638,15 @@
         <v>13</v>
       </c>
       <c r="C23" s="27" t="s">
+        <v>916</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>917</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="24" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -21599,16 +21670,16 @@
     </row>
     <row r="25" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>606</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>607</v>
       </c>
       <c r="E25" s="2"/>
       <c r="G25" s="1"/>
@@ -21632,16 +21703,16 @@
         <v>209</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="2"/>
@@ -21661,10 +21732,10 @@
     </row>
     <row r="27" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>647</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>648</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>210</v>
@@ -21692,7 +21763,7 @@
     <row r="28" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>213</v>
@@ -21720,7 +21791,7 @@
     <row r="29" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>215</v>
@@ -21748,7 +21819,7 @@
     <row r="30" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>216</v>
@@ -21776,7 +21847,7 @@
     <row r="31" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>219</v>
@@ -21804,7 +21875,7 @@
     <row r="32" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>220</v>
@@ -21832,7 +21903,7 @@
     <row r="33" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>222</v>
@@ -21859,19 +21930,19 @@
     </row>
     <row r="34" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>513</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="2"/>
@@ -21891,12 +21962,12 @@
     </row>
     <row r="35" spans="1:23" s="7" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="22" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E35" s="4"/>
       <c r="G35" s="1"/>
@@ -21917,7 +21988,7 @@
     </row>
     <row r="36" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -21941,12 +22012,12 @@
     </row>
     <row r="37" spans="1:23" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="22" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E37" s="4"/>
       <c r="G37" s="1"/>
@@ -21967,12 +22038,12 @@
     </row>
     <row r="38" spans="1:23" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="22" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E38" s="4"/>
       <c r="G38" s="1"/>
@@ -21993,12 +22064,12 @@
     </row>
     <row r="39" spans="1:23" s="7" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="22" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E39" s="4"/>
       <c r="G39" s="1"/>
@@ -22019,12 +22090,12 @@
     </row>
     <row r="40" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="22" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E40" s="4"/>
       <c r="G40" s="1"/>
@@ -22045,12 +22116,12 @@
     </row>
     <row r="41" spans="1:23" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="22" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E41" s="4"/>
       <c r="G41" s="1"/>
@@ -22071,12 +22142,12 @@
     </row>
     <row r="42" spans="1:23" s="7" customFormat="1" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="22" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E42" s="4"/>
       <c r="G42" s="1"/>
@@ -22097,7 +22168,7 @@
     </row>
     <row r="43" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -22130,7 +22201,7 @@
         <v>279</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E44" s="2"/>
       <c r="G44" s="1"/>
@@ -22181,16 +22252,16 @@
     </row>
     <row r="46" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="E46" s="2"/>
       <c r="G46" s="1"/>
@@ -22211,16 +22282,16 @@
     </row>
     <row r="47" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="E47" s="2"/>
       <c r="G47" s="1"/>
@@ -22241,16 +22312,16 @@
     </row>
     <row r="48" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>610</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>611</v>
       </c>
       <c r="E48" s="2"/>
       <c r="G48" s="1"/>
@@ -22271,7 +22342,7 @@
     </row>
     <row r="49" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -22327,19 +22398,19 @@
     </row>
     <row r="51" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>956</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>629</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>630</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="2"/>
@@ -22359,19 +22430,19 @@
     </row>
     <row r="52" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>957</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>634</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="2"/>
@@ -22391,19 +22462,19 @@
     </row>
     <row r="53" spans="1:23" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="C53" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>638</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>639</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="2"/>
@@ -22423,19 +22494,19 @@
     </row>
     <row r="54" spans="1:23" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="E54" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>643</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="2"/>
@@ -22455,7 +22526,7 @@
     </row>
     <row r="55" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="15" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -22479,19 +22550,19 @@
     </row>
     <row r="56" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="D56" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="2"/>
@@ -22511,16 +22582,16 @@
     </row>
     <row r="57" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>509</v>
       </c>
       <c r="E57" s="2"/>
       <c r="G57" s="1"/>
@@ -22541,16 +22612,16 @@
     </row>
     <row r="58" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>585</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>586</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="7"/>
@@ -22574,37 +22645,37 @@
     </row>
     <row r="59" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>589</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>590</v>
       </c>
       <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>615</v>
       </c>
       <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -22631,16 +22702,16 @@
         <v>255</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>683</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>684</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>254</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="2"/>
@@ -22881,7 +22952,7 @@
         <v>276</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E71" s="2"/>
       <c r="G71" s="1"/>
@@ -22902,16 +22973,16 @@
     </row>
     <row r="72" spans="1:23" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>605</v>
-      </c>
       <c r="D72" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E72" s="2"/>
       <c r="G72" s="1"/>
@@ -22932,19 +23003,19 @@
     </row>
     <row r="73" spans="1:23" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="C73" s="27" t="s">
+        <v>904</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>904</v>
-      </c>
-      <c r="C73" s="27" t="s">
-        <v>905</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="E73" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="2"/>
@@ -22964,16 +23035,16 @@
     </row>
     <row r="74" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>596</v>
       </c>
       <c r="E74" s="2"/>
       <c r="G74" s="1"/>
@@ -22994,16 +23065,16 @@
     </row>
     <row r="75" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>599</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>600</v>
       </c>
       <c r="E75" s="2"/>
       <c r="G75" s="1"/>
@@ -23024,7 +23095,7 @@
     </row>
     <row r="76" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="15" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -23051,10 +23122,10 @@
         <v>28</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>491</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>284</v>
@@ -23078,7 +23149,7 @@
     </row>
     <row r="78" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="15" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -23102,16 +23173,16 @@
     </row>
     <row r="79" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>494</v>
-      </c>
       <c r="D79" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E79" s="2"/>
       <c r="G79" s="1"/>
@@ -23132,21 +23203,21 @@
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="81" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>518</v>
       </c>
       <c r="E81" s="2"/>
       <c r="G81" s="1"/>
@@ -23167,7 +23238,7 @@
     </row>
     <row r="82" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="15" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -23191,16 +23262,16 @@
     </row>
     <row r="83" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="7"/>
@@ -23224,21 +23295,21 @@
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A84" s="11" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="85" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>526</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="7"/>
@@ -23262,16 +23333,16 @@
     </row>
     <row r="86" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="C86" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D86" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="7"/>
@@ -23322,16 +23393,16 @@
     </row>
     <row r="88" spans="1:23" s="4" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>532</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>533</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="7"/>
@@ -23355,16 +23426,16 @@
     </row>
     <row r="89" spans="1:23" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>536</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>537</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="7"/>
@@ -23388,16 +23459,16 @@
     </row>
     <row r="90" spans="1:23" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>540</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>541</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="7"/>
@@ -23421,19 +23492,19 @@
     </row>
     <row r="91" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>545</v>
-      </c>
       <c r="E91" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F91" s="7"/>
       <c r="G91" s="1"/>
@@ -23456,19 +23527,19 @@
     </row>
     <row r="92" spans="1:23" s="4" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="C92" s="2" t="s">
+      <c r="E92" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="F92" s="7"/>
       <c r="G92" s="1"/>
@@ -23491,16 +23562,16 @@
     </row>
     <row r="93" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>553</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="7"/>
@@ -23524,16 +23595,16 @@
     </row>
     <row r="94" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D94" s="2" t="s">
         <v>567</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>568</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="7"/>
@@ -23557,19 +23628,19 @@
     </row>
     <row r="95" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="E95" s="2" t="s">
         <v>565</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>566</v>
       </c>
       <c r="F95" s="7"/>
       <c r="G95" s="1"/>
@@ -23592,19 +23663,19 @@
     </row>
     <row r="96" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="C96" s="2" t="s">
+      <c r="E96" s="2" t="s">
         <v>573</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>574</v>
       </c>
       <c r="F96" s="7"/>
       <c r="G96" s="1"/>
@@ -23627,19 +23698,19 @@
     </row>
     <row r="97" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="C97" s="2" t="s">
+      <c r="E97" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>559</v>
       </c>
       <c r="F97" s="7"/>
       <c r="G97" s="1"/>
@@ -23662,16 +23733,16 @@
     </row>
     <row r="98" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>247</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="7"/>
@@ -23695,16 +23766,16 @@
     </row>
     <row r="99" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>575</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>576</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="7"/>
@@ -23728,7 +23799,7 @@
     </row>
     <row r="100" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="15" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -23755,16 +23826,16 @@
     </row>
     <row r="101" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D101" s="2" t="s">
         <v>578</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>579</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="7"/>
@@ -23788,16 +23859,16 @@
     </row>
     <row r="102" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="D102" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>582</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="7"/>
@@ -23821,46 +23892,46 @@
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A103" s="15" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
     </row>
     <row r="104" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>619</v>
       </c>
       <c r="E104" s="2"/>
     </row>
     <row r="105" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="D105" s="2" t="s">
+      <c r="E105" s="2" t="s">
         <v>623</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A106" s="15" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="107" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
@@ -23868,13 +23939,13 @@
         <v>236</v>
       </c>
       <c r="B107" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="D107" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>673</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>237</v>
@@ -23898,10 +23969,10 @@
     <row r="108" spans="1:23" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A108" s="2"/>
       <c r="B108" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>677</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>678</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
@@ -23924,10 +23995,10 @@
     <row r="109" spans="1:23" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A109" s="2"/>
       <c r="B109" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
@@ -23950,10 +24021,10 @@
     <row r="110" spans="1:23" s="7" customFormat="1" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A110" s="2"/>
       <c r="B110" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>682</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
@@ -23975,7 +24046,7 @@
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A111" s="11" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="112" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
@@ -24170,75 +24241,75 @@
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A118" s="15" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="119" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="D119" s="32" t="s">
+        <v>946</v>
+      </c>
+      <c r="E119" s="32" t="s">
         <v>948</v>
-      </c>
-      <c r="D119" s="32" t="s">
-        <v>947</v>
-      </c>
-      <c r="E119" s="32" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="120" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="C120" s="25" t="s">
+        <v>951</v>
+      </c>
+      <c r="D120" s="32" t="s">
         <v>950</v>
       </c>
-      <c r="C120" s="25" t="s">
+      <c r="E120" s="32" t="s">
         <v>952</v>
-      </c>
-      <c r="D120" s="32" t="s">
-        <v>951</v>
-      </c>
-      <c r="E120" s="32" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="121" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A121" s="25" t="s">
+        <v>953</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="D121" s="32" t="s">
         <v>954</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>958</v>
-      </c>
-      <c r="D121" s="32" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="122" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="C122" s="33" t="s">
+        <v>960</v>
+      </c>
+      <c r="D122" s="32" t="s">
         <v>959</v>
       </c>
-      <c r="C122" s="33" t="s">
+      <c r="E122" s="32" t="s">
         <v>961</v>
-      </c>
-      <c r="D122" s="32" t="s">
-        <v>960</v>
-      </c>
-      <c r="E122" s="32" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="123" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="C123" s="25" t="s">
+        <v>964</v>
+      </c>
+      <c r="D123" s="32" t="s">
         <v>963</v>
       </c>
-      <c r="C123" s="25" t="s">
+      <c r="E123" s="32" t="s">
         <v>965</v>
-      </c>
-      <c r="D123" s="32" t="s">
-        <v>964</v>
-      </c>
-      <c r="E123" s="32" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.3">
@@ -24342,12 +24413,12 @@
   <sheetData>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -24357,13 +24428,13 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B5" s="20"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B6" s="21"/>
     </row>
@@ -24387,7 +24458,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B10" s="20"/>
     </row>
@@ -24398,18 +24469,18 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B13" s="21"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B14" s="20"/>
     </row>
@@ -24438,7 +24509,7 @@
     </row>
     <row r="18" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -24461,22 +24532,22 @@
     </row>
     <row r="20" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F20" s="7"/>
     </row>
     <row r="21" spans="1:23" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>445</v>
       </c>
       <c r="F21" s="7"/>
     </row>
@@ -24488,16 +24559,16 @@
     </row>
     <row r="23" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D23" s="17" t="s">
         <v>438</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>439</v>
       </c>
       <c r="F23" s="7"/>
     </row>
@@ -24506,10 +24577,10 @@
         <v>353</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>480</v>
       </c>
       <c r="D24" s="17" t="s">
         <v>358</v>
@@ -24521,10 +24592,10 @@
         <v>353</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D25" s="17" t="s">
         <v>358</v>
@@ -24533,10 +24604,10 @@
     </row>
     <row r="26" spans="1:23" s="2" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="C26" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="F26" s="7"/>
     </row>
@@ -24545,7 +24616,7 @@
         <v>344</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>346</v>
@@ -24563,7 +24634,7 @@
         <v>385</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>387</v>
@@ -24578,16 +24649,16 @@
     </row>
     <row r="29" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>386</v>
@@ -24596,7 +24667,7 @@
     </row>
     <row r="30" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -24626,7 +24697,7 @@
         <v>296</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>305</v>
@@ -24774,19 +24845,19 @@
     </row>
     <row r="36" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="E36" s="17" t="s">
         <v>410</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>411</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="1"/>
@@ -24928,7 +24999,7 @@
         <v>306</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>309</v>
@@ -25076,16 +25147,16 @@
     </row>
     <row r="46" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="7"/>
@@ -25112,7 +25183,7 @@
         <v>331</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>332</v>
@@ -25142,16 +25213,16 @@
     </row>
     <row r="48" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D48" s="17" t="s">
         <v>442</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>443</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="1"/>
@@ -25174,16 +25245,16 @@
     </row>
     <row r="49" spans="1:28" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B49" s="27" t="s">
+        <v>907</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="D49" s="17" t="s">
         <v>442</v>
-      </c>
-      <c r="B49" s="27" t="s">
-        <v>908</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>911</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>443</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="1"/>
@@ -25206,7 +25277,7 @@
     </row>
     <row r="50" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="15" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -25233,16 +25304,16 @@
     </row>
     <row r="51" spans="1:28" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B51" s="37" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="B51" s="37" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>435</v>
       </c>
       <c r="E51" s="2"/>
       <c r="G51" s="1"/>
@@ -25271,7 +25342,7 @@
         <v>40</v>
       </c>
       <c r="B52" s="37" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>338</v>
@@ -25306,13 +25377,13 @@
         <v>123</v>
       </c>
       <c r="B53" s="37" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>437</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>336</v>
@@ -25531,16 +25602,16 @@
     </row>
     <row r="60" spans="1:28" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="E60" s="17" t="s">
         <v>328</v>
@@ -25566,19 +25637,19 @@
     </row>
     <row r="61" spans="1:28" s="4" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C61" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="E61" s="17" t="s">
         <v>425</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="E61" s="17" t="s">
-        <v>426</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="1"/>
@@ -25746,10 +25817,10 @@
         <v>197</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E67" s="2"/>
       <c r="G67" s="1"/>
@@ -25775,16 +25846,16 @@
     </row>
     <row r="68" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E68" s="17" t="s">
         <v>386</v>
@@ -25795,13 +25866,13 @@
         <v>100</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="E69" s="17" t="s">
         <v>386</v>
@@ -25809,16 +25880,16 @@
     </row>
     <row r="70" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C70" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>418</v>
       </c>
       <c r="E70" s="17" t="s">
         <v>386</v>
@@ -25848,22 +25919,22 @@
     </row>
     <row r="73" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>363</v>
       </c>
       <c r="C73" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="E73" s="2"/>
     </row>
     <row r="74" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A74" s="15" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
@@ -25897,10 +25968,10 @@
         <v>383</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>384</v>
@@ -25909,16 +25980,16 @@
     </row>
     <row r="78" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>469</v>
       </c>
       <c r="E78" s="2"/>
     </row>
@@ -25942,10 +26013,10 @@
     <row r="80" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A80" s="2"/>
       <c r="B80" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
@@ -25953,10 +26024,10 @@
     <row r="81" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A81" s="2"/>
       <c r="B81" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>398</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
@@ -25964,10 +26035,10 @@
     <row r="82" spans="1:28" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A82" s="2"/>
       <c r="B82" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>400</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
@@ -25991,16 +26062,16 @@
         <v>116</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="2"/>
@@ -26062,7 +26133,7 @@
     </row>
     <row r="86" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -26091,24 +26162,24 @@
     </row>
     <row r="87" spans="1:28" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="89" spans="1:28" ht="57.6" x14ac:dyDescent="0.3">
@@ -26116,7 +26187,7 @@
         <v>285</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>294</v>
@@ -26168,19 +26239,19 @@
     </row>
     <row r="94" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E94" s="17" t="s">
         <v>461</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="E94" s="17" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="95" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
@@ -26225,7 +26296,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
@@ -26289,91 +26360,91 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B9" s="21"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B10" s="20"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B11" s="20"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B14" s="21"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B15" s="20"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B16" s="20"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B17" s="20"/>
     </row>
@@ -26402,7 +26473,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -26416,31 +26487,31 @@
         <v>13</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C23" s="25"/>
       <c r="D23" s="24"/>
     </row>
     <row r="24" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="C24" s="25" t="s">
         <v>755</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>756</v>
-      </c>
       <c r="D24" s="24" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
@@ -26448,596 +26519,596 @@
         <v>84</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C25" s="25" t="s">
+        <v>756</v>
+      </c>
+      <c r="D25" s="24" t="s">
         <v>757</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C26" s="25"/>
       <c r="D26" s="24"/>
     </row>
     <row r="27" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C27" s="25" t="s">
         <v>749</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="C27" s="25" t="s">
+      <c r="D27" s="24" t="s">
         <v>750</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>801</v>
+      </c>
+      <c r="D28" s="27" t="s">
         <v>800</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>802</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>732</v>
+      </c>
+      <c r="D29" s="24" t="s">
         <v>731</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>733</v>
-      </c>
-      <c r="D29" s="24" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C30" s="25"/>
       <c r="D30" s="24"/>
     </row>
     <row r="31" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>870</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>871</v>
+      </c>
+      <c r="E37" s="27" t="s">
         <v>869</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>873</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>871</v>
-      </c>
-      <c r="D37" s="27" t="s">
-        <v>872</v>
-      </c>
-      <c r="E37" s="27" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>787</v>
+      </c>
+      <c r="D39" s="24" t="s">
         <v>786</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="C39" s="25" t="s">
-        <v>788</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D40" s="24"/>
     </row>
     <row r="41" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D41" s="24" t="s">
         <v>789</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="C41" s="25" t="s">
-        <v>1080</v>
-      </c>
-      <c r="D41" s="24" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C42" s="25" t="s">
         <v>776</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>777</v>
-      </c>
       <c r="D42" s="24" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C44" s="25" t="s">
+        <v>753</v>
+      </c>
+      <c r="D44" s="24" t="s">
         <v>752</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>754</v>
-      </c>
-      <c r="D44" s="24" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>805</v>
+      </c>
+      <c r="D45" s="24" t="s">
         <v>791</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="C45" s="25" t="s">
-        <v>806</v>
-      </c>
-      <c r="D45" s="24" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>846</v>
+      </c>
+      <c r="D47" s="27" t="s">
         <v>844</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="C47" s="25" t="s">
-        <v>847</v>
-      </c>
-      <c r="D47" s="27" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>768</v>
+      </c>
+      <c r="D48" s="24" t="s">
         <v>767</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>769</v>
-      </c>
-      <c r="D48" s="24" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>771</v>
+      </c>
+      <c r="D49" s="24" t="s">
         <v>770</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>772</v>
-      </c>
-      <c r="D49" s="24" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>774</v>
+      </c>
+      <c r="D50" s="24" t="s">
         <v>773</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>775</v>
-      </c>
-      <c r="D50" s="24" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="27"/>
     </row>
     <row r="52" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B52" s="27" t="s">
         <v>831</v>
       </c>
-      <c r="B52" s="27" t="s">
-        <v>832</v>
-      </c>
       <c r="C52" s="25" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B54" s="27" t="s">
         <v>834</v>
       </c>
-      <c r="B54" s="27" t="s">
-        <v>835</v>
-      </c>
       <c r="C54" s="25" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D54" s="27" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>816</v>
+      </c>
+      <c r="C55" s="26" t="s">
         <v>719</v>
       </c>
-      <c r="B55" s="27" t="s">
-        <v>817</v>
-      </c>
-      <c r="C55" s="26" t="s">
+      <c r="D55" s="24" t="s">
         <v>720</v>
-      </c>
-      <c r="D55" s="24" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>828</v>
+      </c>
+      <c r="D57" s="27" t="s">
         <v>827</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="C57" s="25" t="s">
-        <v>829</v>
-      </c>
-      <c r="D57" s="27" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>876</v>
+      </c>
+      <c r="D59" s="27" t="s">
         <v>875</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="C59" s="25" t="s">
+      <c r="E59" s="27" t="s">
         <v>877</v>
-      </c>
-      <c r="D59" s="27" t="s">
-        <v>876</v>
-      </c>
-      <c r="E59" s="27" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>813</v>
+      </c>
+      <c r="D60" s="27" t="s">
         <v>811</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>814</v>
-      </c>
-      <c r="D60" s="27" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>708</v>
+      </c>
+      <c r="D61" s="24" t="s">
         <v>704</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>709</v>
-      </c>
-      <c r="D61" s="24" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C62" s="25"/>
       <c r="D62" s="27"/>
     </row>
     <row r="63" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>803</v>
+      </c>
+      <c r="D63" s="27" t="s">
         <v>797</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="C63" s="25" t="s">
-        <v>804</v>
-      </c>
-      <c r="D63" s="27" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>880</v>
+      </c>
+      <c r="D64" s="27" t="s">
         <v>879</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="E64" s="27" t="s">
         <v>882</v>
-      </c>
-      <c r="C64" s="25" t="s">
-        <v>881</v>
-      </c>
-      <c r="D64" s="27" t="s">
-        <v>880</v>
-      </c>
-      <c r="E64" s="27" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C65" s="25"/>
       <c r="D65" s="24"/>
     </row>
     <row r="66" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="C66" s="25" t="s">
+        <v>709</v>
+      </c>
+      <c r="D66" s="24" t="s">
         <v>701</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>894</v>
-      </c>
-      <c r="C66" s="25" t="s">
-        <v>710</v>
-      </c>
-      <c r="D66" s="24" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>738</v>
+      </c>
+      <c r="D67" s="24" t="s">
         <v>736</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="C67" s="25" t="s">
-        <v>739</v>
-      </c>
-      <c r="D67" s="24" t="s">
+      <c r="E67" s="24" t="s">
         <v>737</v>
-      </c>
-      <c r="E67" s="24" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="C68" s="26" t="s">
+        <v>707</v>
+      </c>
+      <c r="D68" s="24" t="s">
         <v>706</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="C68" s="26" t="s">
-        <v>708</v>
-      </c>
-      <c r="D68" s="24" t="s">
-        <v>707</v>
-      </c>
       <c r="E68" s="24" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="C69" s="25" t="s">
         <v>712</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="C69" s="25" t="s">
-        <v>713</v>
-      </c>
       <c r="D69" s="24" t="s">
+        <v>715</v>
+      </c>
+      <c r="E69" s="24" t="s">
         <v>716</v>
-      </c>
-      <c r="E69" s="24" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>804</v>
+      </c>
+      <c r="D70" s="27" t="s">
         <v>794</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="C70" s="25" t="s">
-        <v>805</v>
-      </c>
-      <c r="D70" s="27" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="28" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B71" s="27"/>
       <c r="C71" s="26"/>
@@ -27045,91 +27116,91 @@
     </row>
     <row r="72" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="C72" s="25" t="s">
+        <v>862</v>
+      </c>
+      <c r="D72" s="27" t="s">
         <v>857</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="C72" s="25" t="s">
-        <v>863</v>
-      </c>
-      <c r="D72" s="27" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="C73" s="25" t="s">
+        <v>861</v>
+      </c>
+      <c r="D73" s="27" t="s">
         <v>859</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>868</v>
-      </c>
-      <c r="C73" s="25" t="s">
-        <v>862</v>
-      </c>
-      <c r="D73" s="27" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>860</v>
+      </c>
+      <c r="D74" s="27" t="s">
         <v>808</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>866</v>
-      </c>
-      <c r="C74" s="25" t="s">
-        <v>861</v>
-      </c>
-      <c r="D74" s="27" t="s">
+      <c r="E74" s="27" t="s">
         <v>809</v>
-      </c>
-      <c r="E74" s="27" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>863</v>
+      </c>
+      <c r="D75" s="24" t="s">
         <v>782</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>865</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>864</v>
-      </c>
-      <c r="D75" s="24" t="s">
+      <c r="E75" s="24" t="s">
         <v>783</v>
-      </c>
-      <c r="E75" s="24" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C76" s="25"/>
       <c r="D76" s="24"/>
     </row>
     <row r="77" spans="1:5" ht="216" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C77" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D77" s="24" t="s">
         <v>747</v>
-      </c>
-      <c r="D77" s="24" t="s">
-        <v>748</v>
       </c>
       <c r="E77" s="24"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C78" s="25"/>
       <c r="D78" s="27"/>
@@ -27137,75 +27208,75 @@
     </row>
     <row r="79" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="C79" s="25" t="s">
+        <v>853</v>
+      </c>
+      <c r="D79" s="27" t="s">
         <v>848</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>853</v>
-      </c>
-      <c r="C79" s="25" t="s">
-        <v>854</v>
-      </c>
-      <c r="D79" s="27" t="s">
-        <v>849</v>
-      </c>
       <c r="E79" s="27" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E80" s="27" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D82" s="27" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E82" s="27" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="28" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C83" s="25"/>
       <c r="D83" s="24"/>
@@ -27213,35 +27284,35 @@
     </row>
     <row r="84" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="C84" s="25" t="s">
+        <v>724</v>
+      </c>
+      <c r="D84" s="24" t="s">
         <v>723</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="C84" s="25" t="s">
-        <v>725</v>
-      </c>
-      <c r="D84" s="24" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="C85" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="C85" s="25" t="s">
+      <c r="D85" s="24" t="s">
         <v>728</v>
-      </c>
-      <c r="D85" s="24" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -27249,16 +27320,16 @@
     </row>
     <row r="87" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="C87" s="25" t="s">
+        <v>741</v>
+      </c>
+      <c r="D87" s="24" t="s">
         <v>740</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="C87" s="25" t="s">
-        <v>742</v>
-      </c>
-      <c r="D87" s="24" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -27344,76 +27415,76 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B9" s="21"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -27448,7 +27519,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -27459,111 +27530,111 @@
         <v>380</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="D23" s="32" t="s">
         <v>988</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>990</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>992</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>991</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>993</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>997</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>999</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>995</v>
+      </c>
+      <c r="D26" s="32" t="s">
         <v>994</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>996</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D28" s="32" t="s">
         <v>1000</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>1002</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>1001</v>
       </c>
       <c r="E28" s="24"/>
     </row>
     <row r="29" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E29" s="32" t="s">
         <v>1004</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E29" s="32" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="28" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -27571,18 +27642,18 @@
     </row>
     <row r="31" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>922</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>921</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>923</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="34" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -27593,140 +27664,140 @@
         <v>236</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="C34" s="25"/>
       <c r="D34" s="32"/>
     </row>
     <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>944</v>
+      </c>
+      <c r="D36" s="32" t="s">
         <v>943</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>945</v>
-      </c>
-      <c r="D36" s="32" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C37" s="25"/>
       <c r="D37" s="32"/>
     </row>
     <row r="38" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>980</v>
+      </c>
+      <c r="D38" s="32" t="s">
         <v>938</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C38" s="25" t="s">
-        <v>981</v>
-      </c>
-      <c r="D38" s="32" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="D39" s="32" t="s">
         <v>978</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="D39" s="32" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D40" s="32" t="s">
         <v>1016</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C40" s="25" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D40" s="32" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="D41" s="32"/>
     </row>
     <row r="42" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>941</v>
+      </c>
+      <c r="D42" s="32" t="s">
         <v>940</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>942</v>
-      </c>
-      <c r="D42" s="32" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C43" s="25"/>
       <c r="D43" s="32"/>
     </row>
     <row r="44" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="D44" s="32" t="s">
         <v>985</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>987</v>
-      </c>
-      <c r="D44" s="32" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C45" s="25"/>
       <c r="D45" s="32"/>
@@ -27734,88 +27805,88 @@
     </row>
     <row r="46" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D46" s="32" t="s">
         <v>1007</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>1009</v>
-      </c>
-      <c r="D46" s="32" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="D47" s="32" t="s">
         <v>982</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>984</v>
-      </c>
-      <c r="D47" s="32" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="D48" s="32" t="s">
         <v>975</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>977</v>
-      </c>
-      <c r="D48" s="32" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D49" s="32" t="s">
         <v>1010</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D49" s="32" t="s">
-        <v>1011</v>
       </c>
       <c r="E49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D50" s="32" t="s">
         <v>1013</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D50" s="32" t="s">
-        <v>1014</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>933</v>
+      </c>
+      <c r="D51" s="32" t="s">
         <v>932</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C51" s="25" t="s">
-        <v>934</v>
-      </c>
-      <c r="D51" s="32" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
@@ -29158,72 +29229,72 @@
     </row>
     <row r="21" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>1050</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>1052</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D23" s="32" t="s">
         <v>1056</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1058</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>1059</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>1061</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>1062</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">

--- a/4 четверть_13_JavaScript_sugarJS.xlsx
+++ b/4 четверть_13_JavaScript_sugarJS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC510D96-5667-406B-B33F-CA5E55D4AEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73591E57-8EF0-4A9E-92E6-1F3E66BEDA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="192" yWindow="-216" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sugarjs" sheetId="20" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="1090">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="1092">
   <si>
     <t>construct(n,indexMapFn)</t>
   </si>
@@ -5255,81 +5255,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Object.filter({a:1,b:2}, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>function(val) {
-  return val == 1;
-}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>); {"a":1}
-Object.filter({a:'a',z:'z'},</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> /[a-f]/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">); {"a":"a"}
-Object.filter(usersByName, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/^H/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">); {} </t>
-    </r>
-  </si>
-  <si>
     <t>find(search)</t>
   </si>
   <si>
@@ -18057,12 +17982,295 @@
 Действует по принципу лямбда выражения в Java Array::append. Позволяет не прописывать отдельно итерируемый объект в параметры единстенной функции</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Object.filter({a:1,b:2}, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>function(key, val) {
+  return val == 1;
+}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>); {"a":1}
+Object.filter({a:'a',z:'z'},</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> /[a-f]/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">); {"a":"a"}
+Object.filter(usersByName, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/^H/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">); {} </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">compare </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF002060"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>values</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+boolean</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">compare </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>keys</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+boolean
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">аналог: 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in { </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>planing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: null, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>journal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: null, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>planexport</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: null, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>favoriteexport</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: null }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Оператор in проверяет, существует ли свойство с указанным именем в объекте</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -18332,6 +18540,15 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF002060"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -18512,6 +18729,55 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>60961</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>533400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3421380</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>840585</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF8CD2B0-691B-4B8D-BB46-51E034584C35}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2529841" y="31988760"/>
+          <a:ext cx="3360419" cy="307185"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -19984,7 +20250,7 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -20054,10 +20320,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C16" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="D16" s="17" t="s">
         <v>355</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -20095,7 +20361,7 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -20113,16 +20379,16 @@
     </row>
     <row r="20" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="37" t="s">
+        <v>911</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>912</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>913</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="1"/>
@@ -20153,7 +20419,7 @@
         <v>206</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>1</v>
@@ -20164,153 +20430,153 @@
     </row>
     <row r="23" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>1018</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>973</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>1019</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>1023</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>973</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>1024</v>
-      </c>
       <c r="E24" s="32" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>1069</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>1071</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>1070</v>
-      </c>
       <c r="E25" s="32" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D26" s="32" t="s">
         <v>970</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>973</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1072</v>
-      </c>
-      <c r="D26" s="32" t="s">
+      <c r="E26" s="32" t="s">
         <v>971</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D31" s="32" t="s">
         <v>1069</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>1074</v>
-      </c>
-      <c r="D31" s="32" t="s">
-        <v>1070</v>
-      </c>
       <c r="E31" s="32" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>907</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="D32" s="17" t="s">
         <v>441</v>
-      </c>
-      <c r="B32" s="27" t="s">
-        <v>908</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>909</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
@@ -20318,10 +20584,10 @@
         <v>97</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>98</v>
@@ -20329,7 +20595,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
@@ -20337,13 +20603,13 @@
         <v>236</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>672</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>237</v>
@@ -20352,10 +20618,10 @@
     <row r="36" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>677</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -20363,10 +20629,10 @@
     <row r="37" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>679</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -20374,10 +20640,10 @@
     <row r="38" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>681</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -20436,7 +20702,7 @@
         <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>76</v>
@@ -20643,10 +20909,10 @@
         <v>44</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>46</v>
@@ -20842,7 +21108,7 @@
         <v>50</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>49</v>
@@ -20856,7 +21122,7 @@
         <v>50</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>92</v>
@@ -20870,7 +21136,7 @@
         <v>199</v>
       </c>
       <c r="C76" s="35" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="D76" s="14" t="s">
         <v>147</v>
@@ -20885,7 +21151,7 @@
         <v>199</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>67</v>
@@ -20905,7 +21171,7 @@
         <v>65</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>63</v>
@@ -20922,10 +21188,10 @@
         <v>97</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>98</v>
@@ -20936,10 +21202,10 @@
         <v>42</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>43</v>
@@ -21200,7 +21466,7 @@
         <v>116</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C101" s="14" t="s">
         <v>118</v>
@@ -21217,7 +21483,7 @@
         <v>120</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C102" s="14" t="s">
         <v>122</v>
@@ -21473,6 +21739,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -21515,68 +21782,68 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B11" s="1"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -21586,17 +21853,17 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
@@ -21624,7 +21891,7 @@
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -21632,21 +21899,21 @@
     </row>
     <row r="23" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="27" t="s">
+        <v>915</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>916</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="24" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -21670,16 +21937,16 @@
     </row>
     <row r="25" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>605</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>606</v>
       </c>
       <c r="E25" s="2"/>
       <c r="G25" s="1"/>
@@ -21703,16 +21970,16 @@
         <v>209</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>644</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>645</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="2"/>
@@ -21732,10 +21999,10 @@
     </row>
     <row r="27" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>647</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>210</v>
@@ -21763,7 +22030,7 @@
     <row r="28" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>213</v>
@@ -21791,7 +22058,7 @@
     <row r="29" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>215</v>
@@ -21819,7 +22086,7 @@
     <row r="30" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>216</v>
@@ -21847,7 +22114,7 @@
     <row r="31" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>219</v>
@@ -21875,7 +22142,7 @@
     <row r="32" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>220</v>
@@ -21903,7 +22170,7 @@
     <row r="33" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>222</v>
@@ -21930,19 +22197,19 @@
     </row>
     <row r="34" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="2"/>
@@ -21962,12 +22229,12 @@
     </row>
     <row r="35" spans="1:23" s="7" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="22" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E35" s="4"/>
       <c r="G35" s="1"/>
@@ -21988,7 +22255,7 @@
     </row>
     <row r="36" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -22012,12 +22279,12 @@
     </row>
     <row r="37" spans="1:23" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="22" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E37" s="4"/>
       <c r="G37" s="1"/>
@@ -22038,12 +22305,12 @@
     </row>
     <row r="38" spans="1:23" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="22" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E38" s="4"/>
       <c r="G38" s="1"/>
@@ -22064,12 +22331,12 @@
     </row>
     <row r="39" spans="1:23" s="7" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="22" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E39" s="4"/>
       <c r="G39" s="1"/>
@@ -22090,12 +22357,12 @@
     </row>
     <row r="40" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="22" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E40" s="4"/>
       <c r="G40" s="1"/>
@@ -22116,12 +22383,12 @@
     </row>
     <row r="41" spans="1:23" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="22" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E41" s="4"/>
       <c r="G41" s="1"/>
@@ -22142,12 +22409,12 @@
     </row>
     <row r="42" spans="1:23" s="7" customFormat="1" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="22" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E42" s="4"/>
       <c r="G42" s="1"/>
@@ -22168,7 +22435,7 @@
     </row>
     <row r="43" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -22201,7 +22468,7 @@
         <v>279</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E44" s="2"/>
       <c r="G44" s="1"/>
@@ -22252,16 +22519,16 @@
     </row>
     <row r="46" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>495</v>
       </c>
       <c r="E46" s="2"/>
       <c r="G46" s="1"/>
@@ -22282,16 +22549,16 @@
     </row>
     <row r="47" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="E47" s="2"/>
       <c r="G47" s="1"/>
@@ -22312,16 +22579,16 @@
     </row>
     <row r="48" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>609</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>610</v>
       </c>
       <c r="E48" s="2"/>
       <c r="G48" s="1"/>
@@ -22342,7 +22609,7 @@
     </row>
     <row r="49" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -22398,19 +22665,19 @@
     </row>
     <row r="51" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>955</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>628</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>629</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="2"/>
@@ -22430,19 +22697,19 @@
     </row>
     <row r="52" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>956</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>632</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>633</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="2"/>
@@ -22462,19 +22729,19 @@
     </row>
     <row r="53" spans="1:23" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="C53" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>637</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>638</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="2"/>
@@ -22494,19 +22761,19 @@
     </row>
     <row r="54" spans="1:23" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="E54" s="2" t="s">
         <v>641</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>642</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="2"/>
@@ -22526,7 +22793,7 @@
     </row>
     <row r="55" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="15" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -22550,19 +22817,19 @@
     </row>
     <row r="56" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="D56" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="2"/>
@@ -22582,16 +22849,16 @@
     </row>
     <row r="57" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="E57" s="2"/>
       <c r="G57" s="1"/>
@@ -22612,16 +22879,16 @@
     </row>
     <row r="58" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="7"/>
@@ -22645,37 +22912,37 @@
     </row>
     <row r="59" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>588</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>589</v>
       </c>
       <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>613</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>614</v>
       </c>
       <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -22702,16 +22969,16 @@
         <v>255</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>682</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>683</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>254</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="2"/>
@@ -22952,7 +23219,7 @@
         <v>276</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E71" s="2"/>
       <c r="G71" s="1"/>
@@ -22973,16 +23240,16 @@
     </row>
     <row r="72" spans="1:23" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>604</v>
-      </c>
       <c r="D72" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E72" s="2"/>
       <c r="G72" s="1"/>
@@ -23003,19 +23270,19 @@
     </row>
     <row r="73" spans="1:23" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="C73" s="27" t="s">
+        <v>903</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>903</v>
-      </c>
-      <c r="C73" s="27" t="s">
-        <v>904</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>593</v>
-      </c>
       <c r="E73" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="2"/>
@@ -23035,16 +23302,16 @@
     </row>
     <row r="74" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>594</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>595</v>
       </c>
       <c r="E74" s="2"/>
       <c r="G74" s="1"/>
@@ -23065,16 +23332,16 @@
     </row>
     <row r="75" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>599</v>
       </c>
       <c r="E75" s="2"/>
       <c r="G75" s="1"/>
@@ -23095,7 +23362,7 @@
     </row>
     <row r="76" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="15" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -23122,10 +23389,10 @@
         <v>28</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>490</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>284</v>
@@ -23149,7 +23416,7 @@
     </row>
     <row r="78" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="15" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -23173,16 +23440,16 @@
     </row>
     <row r="79" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>493</v>
-      </c>
       <c r="D79" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E79" s="2"/>
       <c r="G79" s="1"/>
@@ -23203,21 +23470,21 @@
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="81" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>517</v>
       </c>
       <c r="E81" s="2"/>
       <c r="G81" s="1"/>
@@ -23238,7 +23505,7 @@
     </row>
     <row r="82" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="15" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -23262,16 +23529,16 @@
     </row>
     <row r="83" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>521</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="7"/>
@@ -23295,21 +23562,21 @@
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A84" s="11" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="85" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>525</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="7"/>
@@ -23333,16 +23600,16 @@
     </row>
     <row r="86" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="C86" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="D86" s="2" t="s">
         <v>529</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>530</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="7"/>
@@ -23393,16 +23660,16 @@
     </row>
     <row r="88" spans="1:23" s="4" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>531</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>532</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="7"/>
@@ -23426,16 +23693,16 @@
     </row>
     <row r="89" spans="1:23" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>536</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="7"/>
@@ -23459,16 +23726,16 @@
     </row>
     <row r="90" spans="1:23" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>539</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>540</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="7"/>
@@ -23492,19 +23759,19 @@
     </row>
     <row r="91" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>544</v>
-      </c>
       <c r="E91" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F91" s="7"/>
       <c r="G91" s="1"/>
@@ -23527,19 +23794,19 @@
     </row>
     <row r="92" spans="1:23" s="4" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C92" s="2" t="s">
+      <c r="E92" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="F92" s="7"/>
       <c r="G92" s="1"/>
@@ -23562,16 +23829,16 @@
     </row>
     <row r="93" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>552</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="7"/>
@@ -23595,16 +23862,16 @@
     </row>
     <row r="94" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D94" s="2" t="s">
         <v>566</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>567</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="7"/>
@@ -23628,19 +23895,19 @@
     </row>
     <row r="95" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="E95" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>565</v>
       </c>
       <c r="F95" s="7"/>
       <c r="G95" s="1"/>
@@ -23663,19 +23930,19 @@
     </row>
     <row r="96" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="C96" s="2" t="s">
+      <c r="E96" s="2" t="s">
         <v>572</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>573</v>
       </c>
       <c r="F96" s="7"/>
       <c r="G96" s="1"/>
@@ -23698,19 +23965,19 @@
     </row>
     <row r="97" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="C97" s="2" t="s">
+      <c r="E97" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>558</v>
       </c>
       <c r="F97" s="7"/>
       <c r="G97" s="1"/>
@@ -23733,16 +24000,16 @@
     </row>
     <row r="98" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>247</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="7"/>
@@ -23766,16 +24033,16 @@
     </row>
     <row r="99" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>575</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="7"/>
@@ -23799,7 +24066,7 @@
     </row>
     <row r="100" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="15" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -23826,16 +24093,16 @@
     </row>
     <row r="101" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D101" s="2" t="s">
         <v>577</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>578</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="7"/>
@@ -23859,16 +24126,16 @@
     </row>
     <row r="102" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="D102" s="2" t="s">
         <v>580</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>581</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="7"/>
@@ -23892,46 +24159,46 @@
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A103" s="15" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
     </row>
     <row r="104" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>618</v>
       </c>
       <c r="E104" s="2"/>
     </row>
     <row r="105" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="D105" s="2" t="s">
+      <c r="E105" s="2" t="s">
         <v>622</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A106" s="15" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="107" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
@@ -23939,13 +24206,13 @@
         <v>236</v>
       </c>
       <c r="B107" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="D107" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>672</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>237</v>
@@ -23969,10 +24236,10 @@
     <row r="108" spans="1:23" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A108" s="2"/>
       <c r="B108" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>677</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
@@ -23995,10 +24262,10 @@
     <row r="109" spans="1:23" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A109" s="2"/>
       <c r="B109" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>679</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
@@ -24021,10 +24288,10 @@
     <row r="110" spans="1:23" s="7" customFormat="1" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A110" s="2"/>
       <c r="B110" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>681</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
@@ -24046,7 +24313,7 @@
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A111" s="11" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="112" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
@@ -24241,75 +24508,75 @@
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A118" s="15" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="119" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="D119" s="32" t="s">
+        <v>945</v>
+      </c>
+      <c r="E119" s="32" t="s">
         <v>947</v>
-      </c>
-      <c r="D119" s="32" t="s">
-        <v>946</v>
-      </c>
-      <c r="E119" s="32" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="120" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="C120" s="25" t="s">
+        <v>950</v>
+      </c>
+      <c r="D120" s="32" t="s">
         <v>949</v>
       </c>
-      <c r="C120" s="25" t="s">
+      <c r="E120" s="32" t="s">
         <v>951</v>
-      </c>
-      <c r="D120" s="32" t="s">
-        <v>950</v>
-      </c>
-      <c r="E120" s="32" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="121" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A121" s="25" t="s">
+        <v>952</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="D121" s="32" t="s">
         <v>953</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>957</v>
-      </c>
-      <c r="D121" s="32" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="122" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="C122" s="33" t="s">
+        <v>959</v>
+      </c>
+      <c r="D122" s="32" t="s">
         <v>958</v>
       </c>
-      <c r="C122" s="33" t="s">
+      <c r="E122" s="32" t="s">
         <v>960</v>
-      </c>
-      <c r="D122" s="32" t="s">
-        <v>959</v>
-      </c>
-      <c r="E122" s="32" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="123" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="C123" s="25" t="s">
+        <v>963</v>
+      </c>
+      <c r="D123" s="32" t="s">
         <v>962</v>
       </c>
-      <c r="C123" s="25" t="s">
+      <c r="E123" s="32" t="s">
         <v>964</v>
-      </c>
-      <c r="D123" s="32" t="s">
-        <v>963</v>
-      </c>
-      <c r="E123" s="32" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.3">
@@ -24413,12 +24680,12 @@
   <sheetData>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -24428,13 +24695,13 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B5" s="20"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B6" s="21"/>
     </row>
@@ -24458,7 +24725,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B10" s="20"/>
     </row>
@@ -24469,18 +24736,18 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B13" s="21"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B14" s="20"/>
     </row>
@@ -24509,7 +24776,7 @@
     </row>
     <row r="18" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -24532,22 +24799,22 @@
     </row>
     <row r="20" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F20" s="7"/>
     </row>
     <row r="21" spans="1:23" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>444</v>
       </c>
       <c r="F21" s="7"/>
     </row>
@@ -24559,70 +24826,70 @@
     </row>
     <row r="23" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D23" s="17" t="s">
         <v>437</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>438</v>
       </c>
       <c r="F23" s="7"/>
     </row>
     <row r="24" spans="1:23" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>479</v>
-      </c>
       <c r="D24" s="17" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F24" s="7"/>
     </row>
     <row r="25" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:23" s="2" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="C26" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:23" s="2" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>336</v>
@@ -24631,43 +24898,43 @@
     </row>
     <row r="28" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E28" s="17" t="s">
         <v>385</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>386</v>
       </c>
       <c r="F28" s="7"/>
     </row>
     <row r="29" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F29" s="7"/>
     </row>
     <row r="30" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -24697,7 +24964,7 @@
         <v>296</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>305</v>
@@ -24845,19 +25112,19 @@
     </row>
     <row r="36" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="E36" s="17" t="s">
         <v>409</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>410</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="1"/>
@@ -24999,7 +25266,7 @@
         <v>306</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>309</v>
@@ -25147,16 +25414,16 @@
     </row>
     <row r="46" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>413</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="7"/>
@@ -25183,7 +25450,7 @@
         <v>331</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>332</v>
@@ -25213,16 +25480,16 @@
     </row>
     <row r="48" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D48" s="17" t="s">
         <v>441</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>442</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="1"/>
@@ -25245,16 +25512,16 @@
     </row>
     <row r="49" spans="1:28" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B49" s="27" t="s">
+        <v>906</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="D49" s="17" t="s">
         <v>441</v>
-      </c>
-      <c r="B49" s="27" t="s">
-        <v>907</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>442</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="1"/>
@@ -25277,7 +25544,7 @@
     </row>
     <row r="50" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -25304,16 +25571,16 @@
     </row>
     <row r="51" spans="1:28" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B51" s="37" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="B51" s="37" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="E51" s="2"/>
       <c r="G51" s="1"/>
@@ -25342,7 +25609,7 @@
         <v>40</v>
       </c>
       <c r="B52" s="37" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>338</v>
@@ -25377,13 +25644,13 @@
         <v>123</v>
       </c>
       <c r="B53" s="37" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>336</v>
@@ -25442,10 +25709,10 @@
         <v>13</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="1"/>
@@ -25468,16 +25735,16 @@
     </row>
     <row r="56" spans="1:28" s="4" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>375</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="7"/>
@@ -25501,16 +25768,16 @@
     </row>
     <row r="57" spans="1:28" s="4" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>379</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="7"/>
@@ -25534,16 +25801,16 @@
     </row>
     <row r="58" spans="1:28" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="7"/>
@@ -25570,7 +25837,7 @@
         <v>334</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>13</v>
+        <v>1090</v>
       </c>
       <c r="C59" s="17" t="s">
         <v>337</v>
@@ -25602,16 +25869,16 @@
     </row>
     <row r="60" spans="1:28" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>448</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>449</v>
       </c>
       <c r="E60" s="17" t="s">
         <v>328</v>
@@ -25637,19 +25904,19 @@
     </row>
     <row r="61" spans="1:28" s="4" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="2" t="s">
+      <c r="E61" s="17" t="s">
         <v>424</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="E61" s="17" t="s">
-        <v>425</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="1"/>
@@ -25670,18 +25937,18 @@
       <c r="V61" s="2"/>
       <c r="W61" s="1"/>
     </row>
-    <row r="62" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:28" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>13</v>
+        <v>1091</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E62" s="2"/>
     </row>
@@ -25817,10 +26084,10 @@
         <v>197</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E67" s="2"/>
       <c r="G67" s="1"/>
@@ -25846,19 +26113,19 @@
     </row>
     <row r="68" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="69" spans="1:28" ht="72" x14ac:dyDescent="0.3">
@@ -25866,33 +26133,33 @@
         <v>100</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>405</v>
-      </c>
       <c r="E69" s="17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="70" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C70" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>417</v>
-      </c>
       <c r="E70" s="17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="71" spans="1:28" x14ac:dyDescent="0.3">
@@ -25904,53 +26171,53 @@
     </row>
     <row r="72" spans="1:28" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="E72" s="2"/>
     </row>
     <row r="73" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="C73" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>452</v>
       </c>
       <c r="E73" s="2"/>
     </row>
     <row r="74" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A74" s="15" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C75" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="E75" s="2"/>
     </row>
@@ -25965,58 +26232,58 @@
     </row>
     <row r="77" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>384</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="E78" s="2"/>
     </row>
     <row r="79" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>390</v>
-      </c>
       <c r="E79" s="17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="80" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A80" s="2"/>
       <c r="B80" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
@@ -26024,10 +26291,10 @@
     <row r="81" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A81" s="2"/>
       <c r="B81" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>397</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
@@ -26035,10 +26302,10 @@
     <row r="82" spans="1:28" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A82" s="2"/>
       <c r="B82" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
@@ -26048,10 +26315,10 @@
         <v>341</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>343</v>
+        <v>1089</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>342</v>
@@ -26062,16 +26329,16 @@
         <v>116</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="2"/>
@@ -26096,19 +26363,19 @@
     </row>
     <row r="85" spans="1:28" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E85" s="17" t="s">
         <v>347</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E85" s="17" t="s">
-        <v>348</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="2"/>
@@ -26133,7 +26400,7 @@
     </row>
     <row r="86" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -26162,24 +26429,24 @@
     </row>
     <row r="87" spans="1:28" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" s="11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="89" spans="1:28" ht="57.6" x14ac:dyDescent="0.3">
@@ -26187,7 +26454,7 @@
         <v>285</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>294</v>
@@ -26239,19 +26506,19 @@
     </row>
     <row r="94" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E94" s="17" t="s">
         <v>460</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="E94" s="17" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="95" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
@@ -26296,21 +26563,21 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="11" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E100" s="2"/>
     </row>
@@ -26360,91 +26627,91 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B9" s="21"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B10" s="20"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B11" s="20"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B14" s="21"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B15" s="20"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B16" s="20"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B17" s="20"/>
     </row>
@@ -26473,7 +26740,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -26481,37 +26748,37 @@
     </row>
     <row r="22" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C23" s="25"/>
       <c r="D23" s="24"/>
     </row>
     <row r="24" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C24" s="25" t="s">
         <v>754</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>755</v>
-      </c>
       <c r="D24" s="24" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
@@ -26519,596 +26786,596 @@
         <v>84</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C25" s="25" t="s">
+        <v>755</v>
+      </c>
+      <c r="D25" s="24" t="s">
         <v>756</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C26" s="25"/>
       <c r="D26" s="24"/>
     </row>
     <row r="27" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C27" s="25" t="s">
         <v>748</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="C27" s="25" t="s">
+      <c r="D27" s="24" t="s">
         <v>749</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>800</v>
+      </c>
+      <c r="D28" s="27" t="s">
         <v>799</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>801</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>731</v>
+      </c>
+      <c r="D29" s="24" t="s">
         <v>730</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>732</v>
-      </c>
-      <c r="D29" s="24" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C30" s="25"/>
       <c r="D30" s="24"/>
     </row>
     <row r="31" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>869</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>870</v>
+      </c>
+      <c r="E37" s="27" t="s">
         <v>868</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>870</v>
-      </c>
-      <c r="D37" s="27" t="s">
-        <v>871</v>
-      </c>
-      <c r="E37" s="27" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>786</v>
+      </c>
+      <c r="D39" s="24" t="s">
         <v>785</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="C39" s="25" t="s">
-        <v>787</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="D40" s="24"/>
     </row>
     <row r="41" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D41" s="24" t="s">
         <v>788</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="C41" s="25" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D41" s="24" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C42" s="25" t="s">
         <v>775</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>776</v>
-      </c>
       <c r="D42" s="24" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C44" s="25" t="s">
+        <v>752</v>
+      </c>
+      <c r="D44" s="24" t="s">
         <v>751</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>753</v>
-      </c>
-      <c r="D44" s="24" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>804</v>
+      </c>
+      <c r="D45" s="24" t="s">
         <v>790</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="C45" s="25" t="s">
-        <v>805</v>
-      </c>
-      <c r="D45" s="24" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>845</v>
+      </c>
+      <c r="D47" s="27" t="s">
         <v>843</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="C47" s="25" t="s">
-        <v>846</v>
-      </c>
-      <c r="D47" s="27" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>767</v>
+      </c>
+      <c r="D48" s="24" t="s">
         <v>766</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>768</v>
-      </c>
-      <c r="D48" s="24" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>770</v>
+      </c>
+      <c r="D49" s="24" t="s">
         <v>769</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>771</v>
-      </c>
-      <c r="D49" s="24" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>773</v>
+      </c>
+      <c r="D50" s="24" t="s">
         <v>772</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>774</v>
-      </c>
-      <c r="D50" s="24" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="27"/>
     </row>
     <row r="52" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B52" s="27" t="s">
         <v>830</v>
       </c>
-      <c r="B52" s="27" t="s">
-        <v>831</v>
-      </c>
       <c r="C52" s="25" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="B54" s="27" t="s">
         <v>833</v>
       </c>
-      <c r="B54" s="27" t="s">
-        <v>834</v>
-      </c>
       <c r="C54" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D54" s="27" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>815</v>
+      </c>
+      <c r="C55" s="26" t="s">
         <v>718</v>
       </c>
-      <c r="B55" s="27" t="s">
-        <v>816</v>
-      </c>
-      <c r="C55" s="26" t="s">
+      <c r="D55" s="24" t="s">
         <v>719</v>
-      </c>
-      <c r="D55" s="24" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>827</v>
+      </c>
+      <c r="D57" s="27" t="s">
         <v>826</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="C57" s="25" t="s">
-        <v>828</v>
-      </c>
-      <c r="D57" s="27" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>875</v>
+      </c>
+      <c r="D59" s="27" t="s">
         <v>874</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="C59" s="25" t="s">
+      <c r="E59" s="27" t="s">
         <v>876</v>
-      </c>
-      <c r="D59" s="27" t="s">
-        <v>875</v>
-      </c>
-      <c r="E59" s="27" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>812</v>
+      </c>
+      <c r="D60" s="27" t="s">
         <v>810</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>813</v>
-      </c>
-      <c r="D60" s="27" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>707</v>
+      </c>
+      <c r="D61" s="24" t="s">
         <v>703</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>708</v>
-      </c>
-      <c r="D61" s="24" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C62" s="25"/>
       <c r="D62" s="27"/>
     </row>
     <row r="63" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>802</v>
+      </c>
+      <c r="D63" s="27" t="s">
         <v>796</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="C63" s="25" t="s">
-        <v>803</v>
-      </c>
-      <c r="D63" s="27" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>879</v>
+      </c>
+      <c r="D64" s="27" t="s">
         <v>878</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="E64" s="27" t="s">
         <v>881</v>
-      </c>
-      <c r="C64" s="25" t="s">
-        <v>880</v>
-      </c>
-      <c r="D64" s="27" t="s">
-        <v>879</v>
-      </c>
-      <c r="E64" s="27" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C65" s="25"/>
       <c r="D65" s="24"/>
     </row>
     <row r="66" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="C66" s="25" t="s">
+        <v>708</v>
+      </c>
+      <c r="D66" s="24" t="s">
         <v>700</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>893</v>
-      </c>
-      <c r="C66" s="25" t="s">
-        <v>709</v>
-      </c>
-      <c r="D66" s="24" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>737</v>
+      </c>
+      <c r="D67" s="24" t="s">
         <v>735</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="C67" s="25" t="s">
-        <v>738</v>
-      </c>
-      <c r="D67" s="24" t="s">
+      <c r="E67" s="24" t="s">
         <v>736</v>
-      </c>
-      <c r="E67" s="24" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="C68" s="26" t="s">
+        <v>706</v>
+      </c>
+      <c r="D68" s="24" t="s">
         <v>705</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="C68" s="26" t="s">
-        <v>707</v>
-      </c>
-      <c r="D68" s="24" t="s">
-        <v>706</v>
-      </c>
       <c r="E68" s="24" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="C69" s="25" t="s">
         <v>711</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="C69" s="25" t="s">
-        <v>712</v>
-      </c>
       <c r="D69" s="24" t="s">
+        <v>714</v>
+      </c>
+      <c r="E69" s="24" t="s">
         <v>715</v>
-      </c>
-      <c r="E69" s="24" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>803</v>
+      </c>
+      <c r="D70" s="27" t="s">
         <v>793</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="C70" s="25" t="s">
-        <v>804</v>
-      </c>
-      <c r="D70" s="27" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="28" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B71" s="27"/>
       <c r="C71" s="26"/>
@@ -27116,91 +27383,91 @@
     </row>
     <row r="72" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="C72" s="25" t="s">
+        <v>861</v>
+      </c>
+      <c r="D72" s="27" t="s">
         <v>856</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>866</v>
-      </c>
-      <c r="C72" s="25" t="s">
-        <v>862</v>
-      </c>
-      <c r="D72" s="27" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="C73" s="25" t="s">
+        <v>860</v>
+      </c>
+      <c r="D73" s="27" t="s">
         <v>858</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="C73" s="25" t="s">
-        <v>861</v>
-      </c>
-      <c r="D73" s="27" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>859</v>
+      </c>
+      <c r="D74" s="27" t="s">
         <v>807</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>865</v>
-      </c>
-      <c r="C74" s="25" t="s">
-        <v>860</v>
-      </c>
-      <c r="D74" s="27" t="s">
+      <c r="E74" s="27" t="s">
         <v>808</v>
-      </c>
-      <c r="E74" s="27" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>862</v>
+      </c>
+      <c r="D75" s="24" t="s">
         <v>781</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>864</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>863</v>
-      </c>
-      <c r="D75" s="24" t="s">
+      <c r="E75" s="24" t="s">
         <v>782</v>
-      </c>
-      <c r="E75" s="24" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C76" s="25"/>
       <c r="D76" s="24"/>
     </row>
     <row r="77" spans="1:5" ht="216" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C77" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="D77" s="24" t="s">
         <v>746</v>
-      </c>
-      <c r="D77" s="24" t="s">
-        <v>747</v>
       </c>
       <c r="E77" s="24"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C78" s="25"/>
       <c r="D78" s="27"/>
@@ -27208,75 +27475,75 @@
     </row>
     <row r="79" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="C79" s="25" t="s">
+        <v>852</v>
+      </c>
+      <c r="D79" s="27" t="s">
         <v>847</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>852</v>
-      </c>
-      <c r="C79" s="25" t="s">
-        <v>853</v>
-      </c>
-      <c r="D79" s="27" t="s">
-        <v>848</v>
-      </c>
       <c r="E79" s="27" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E80" s="27" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D82" s="27" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="E82" s="27" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="28" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C83" s="25"/>
       <c r="D83" s="24"/>
@@ -27284,35 +27551,35 @@
     </row>
     <row r="84" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="C84" s="25" t="s">
+        <v>723</v>
+      </c>
+      <c r="D84" s="24" t="s">
         <v>722</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="C84" s="25" t="s">
-        <v>724</v>
-      </c>
-      <c r="D84" s="24" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="C85" s="25" t="s">
         <v>726</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="C85" s="25" t="s">
+      <c r="D85" s="24" t="s">
         <v>727</v>
-      </c>
-      <c r="D85" s="24" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -27320,16 +27587,16 @@
     </row>
     <row r="87" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="C87" s="25" t="s">
+        <v>740</v>
+      </c>
+      <c r="D87" s="24" t="s">
         <v>739</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="C87" s="25" t="s">
-        <v>741</v>
-      </c>
-      <c r="D87" s="24" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -27415,76 +27682,76 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B9" s="21"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -27519,7 +27786,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -27527,114 +27794,114 @@
     </row>
     <row r="22" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="D23" s="32" t="s">
         <v>987</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>989</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>991</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>990</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>992</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>996</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>994</v>
+      </c>
+      <c r="D26" s="32" t="s">
         <v>993</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>995</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D28" s="32" t="s">
         <v>999</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>1000</v>
       </c>
       <c r="E28" s="24"/>
     </row>
     <row r="29" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E29" s="32" t="s">
         <v>1003</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>1002</v>
-      </c>
-      <c r="E29" s="32" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="28" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -27642,18 +27909,18 @@
     </row>
     <row r="31" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>921</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>920</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>922</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="34" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -27664,140 +27931,140 @@
         <v>236</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C34" s="25"/>
       <c r="D34" s="32"/>
     </row>
     <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>943</v>
+      </c>
+      <c r="D36" s="32" t="s">
         <v>942</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>944</v>
-      </c>
-      <c r="D36" s="32" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C37" s="25"/>
       <c r="D37" s="32"/>
     </row>
     <row r="38" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>979</v>
+      </c>
+      <c r="D38" s="32" t="s">
         <v>937</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C38" s="25" t="s">
-        <v>980</v>
-      </c>
-      <c r="D38" s="32" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D39" s="32" t="s">
         <v>977</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>979</v>
-      </c>
-      <c r="D39" s="32" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D40" s="32" t="s">
         <v>1015</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C40" s="25" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D40" s="32" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="D41" s="32"/>
     </row>
     <row r="42" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>940</v>
+      </c>
+      <c r="D42" s="32" t="s">
         <v>939</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>941</v>
-      </c>
-      <c r="D42" s="32" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C43" s="25"/>
       <c r="D43" s="32"/>
     </row>
     <row r="44" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="D44" s="32" t="s">
         <v>984</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>986</v>
-      </c>
-      <c r="D44" s="32" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C45" s="25"/>
       <c r="D45" s="32"/>
@@ -27805,88 +28072,88 @@
     </row>
     <row r="46" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D46" s="32" t="s">
         <v>1006</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D46" s="32" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="D47" s="32" t="s">
         <v>981</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>983</v>
-      </c>
-      <c r="D47" s="32" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="D48" s="32" t="s">
         <v>974</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>976</v>
-      </c>
-      <c r="D48" s="32" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D49" s="32" t="s">
         <v>1009</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D49" s="32" t="s">
-        <v>1010</v>
       </c>
       <c r="E49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D50" s="32" t="s">
         <v>1012</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D50" s="32" t="s">
-        <v>1013</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>932</v>
+      </c>
+      <c r="D51" s="32" t="s">
         <v>931</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C51" s="25" t="s">
-        <v>933</v>
-      </c>
-      <c r="D51" s="32" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
@@ -29229,72 +29496,72 @@
     </row>
     <row r="21" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>1049</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D23" s="32" t="s">
         <v>1055</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1057</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>1058</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>1060</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>1061</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">

--- a/4 четверть_13_JavaScript_sugarJS.xlsx
+++ b/4 четверть_13_JavaScript_sugarJS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73591E57-8EF0-4A9E-92E6-1F3E66BEDA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585B7D47-A702-413C-BA4D-66087824D8C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11730" yWindow="-18075" windowWidth="28770" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sugarjs" sheetId="20" r:id="rId1"/>
@@ -639,13 +639,6 @@
     <t>exclude(search)</t>
   </si>
   <si>
-    <t>[1,2,3].exclude(3) [1, 2]
-['a','b','c'].exclude(/b/) ["a", "c"]
-[{a:1},{b:2}].exclude(function(n) {
-  return n['a'] == 1;
-}); [{"b":2}]</t>
-  </si>
-  <si>
     <t>filter(search,[context])</t>
   </si>
   <si>
@@ -17578,91 +17571,6 @@
   </si>
   <si>
     <r>
-      <t>[1,2,3].first() 1
-[</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1,2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,3].first(2) [1, 2]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>[1,2,3].last() 3
-[1,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2,3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>].last(2) [2, 3]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>['a','b','c'].to(1) ["a"] - аналог first
-[</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>'a','b'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,'c'].to(2) ["a", "b"]</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>['a',</t>
     </r>
     <r>
@@ -18264,6 +18172,177 @@
       </rPr>
       <t>Оператор in проверяет, существует ли свойство с указанным именем в объекте</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'a</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,'b','c'].to(1) ["a"] - аналог first
+[</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'a','b'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,'c'].to(2) ["a", "b"]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,2,3].first() 1
+[</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1,2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,3].first(2) [1, 2]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[1,2,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>].last() 3
+[1,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2,3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>].last(2) [2, 3]</t>
+    </r>
+  </si>
+  <si>
+    <t>[1,2,3].exclude(3) [1, 2]
+['a','b','c'].exclude(/b/) ["a", "c"] //только для строк
+[{a:1},{b:2}].exclude(function(n) {
+  return n['a'] == 1;
+}); [{"b":2}]</t>
   </si>
 </sst>
 </file>
@@ -18701,13 +18780,13 @@
     <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -19146,7 +19225,7 @@
     </row>
     <row r="4" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -19170,11 +19249,11 @@
     </row>
     <row r="5" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -19196,13 +19275,13 @@
     </row>
     <row r="6" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -19224,7 +19303,7 @@
     </row>
     <row r="7" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -19250,7 +19329,7 @@
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -20250,80 +20329,80 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C16" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="D16" s="17" t="s">
         <v>354</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -20361,7 +20440,7 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -20379,16 +20458,16 @@
     </row>
     <row r="20" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="36" t="s">
+        <v>910</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>911</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>912</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="1"/>
@@ -20403,7 +20482,7 @@
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="9"/>
@@ -20416,10 +20495,10 @@
         <v>0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>1</v>
@@ -20430,198 +20509,198 @@
     </row>
     <row r="23" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>1017</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>972</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>1018</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>1022</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>972</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>1023</v>
-      </c>
       <c r="E24" s="32" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>1068</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>1069</v>
-      </c>
       <c r="E25" s="32" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D26" s="32" t="s">
         <v>969</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>972</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1071</v>
-      </c>
-      <c r="D26" s="32" t="s">
+      <c r="E26" s="32" t="s">
         <v>970</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D31" s="32" t="s">
         <v>1068</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D31" s="32" t="s">
-        <v>1069</v>
-      </c>
       <c r="E31" s="32" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>906</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="D32" s="17" t="s">
         <v>440</v>
-      </c>
-      <c r="B32" s="27" t="s">
-        <v>907</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>908</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="D33" s="14" t="s">
         <v>97</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>676</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -20629,10 +20708,10 @@
     <row r="37" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>677</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>678</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -20640,10 +20719,10 @@
     <row r="38" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -20653,7 +20732,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="2"/>
@@ -20664,7 +20743,7 @@
         <v>28</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>30</v>
@@ -20675,7 +20754,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
@@ -20696,30 +20775,30 @@
     </row>
     <row r="44" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D45" s="14" t="s">
         <v>113</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>114</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>27</v>
@@ -20727,30 +20806,30 @@
     </row>
     <row r="46" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="D46" s="14" t="s">
         <v>86</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C47" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47" s="14" t="s">
         <v>89</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
@@ -20772,22 +20851,22 @@
     </row>
     <row r="49" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C49" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="D49" s="14" t="s">
         <v>134</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>135</v>
       </c>
       <c r="E49" s="14"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C50" s="10"/>
       <c r="D50" s="10"/>
@@ -20798,7 +20877,7 @@
         <v>16</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>14</v>
@@ -20812,13 +20891,13 @@
         <v>40</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>41</v>
+        <v>1091</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>27</v>
@@ -20829,13 +20908,13 @@
         <v>17</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -20843,27 +20922,27 @@
         <v>22</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C55" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C55" s="14" t="s">
-        <v>124</v>
-      </c>
       <c r="D55" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>27</v>
@@ -20871,22 +20950,22 @@
     </row>
     <row r="56" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C56" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="D56" s="16" t="s">
         <v>187</v>
-      </c>
-      <c r="C56" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>188</v>
       </c>
       <c r="E56" s="14"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D57" s="10"/>
     </row>
@@ -20895,7 +20974,7 @@
         <v>23</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>20</v>
@@ -20906,16 +20985,16 @@
     </row>
     <row r="59" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>27</v>
@@ -20923,44 +21002,44 @@
     </row>
     <row r="60" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D60" s="14" t="s">
         <v>78</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D60" s="14" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D61" s="14" t="s">
         <v>93</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>27</v>
@@ -20968,94 +21047,94 @@
     </row>
     <row r="63" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D63" s="14" t="s">
         <v>107</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C64" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64" s="14" t="s">
         <v>110</v>
-      </c>
-      <c r="D64" s="14" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D65" s="14"/>
     </row>
     <row r="66" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="D66" s="14" t="s">
         <v>137</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="D66" s="14" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D67" s="14" t="s">
         <v>161</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D68" s="14" t="s">
         <v>164</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D68" s="14" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="144" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C69" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="D69" s="14" t="s">
         <v>166</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="2"/>
@@ -21066,7 +21145,7 @@
         <v>2</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>7</v>
@@ -21083,7 +21162,7 @@
         <v>6</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>9</v>
@@ -21095,71 +21174,71 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D73" s="10"/>
       <c r="E73" s="10"/>
     </row>
     <row r="74" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D74" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D74" s="10" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D75" s="14" t="s">
         <v>91</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="D75" s="14" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C76" s="37" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D76" s="14" t="s">
         <v>146</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C76" s="35" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D76" s="14" t="s">
-        <v>147</v>
       </c>
       <c r="E76" s="14"/>
     </row>
     <row r="77" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D77" s="13" t="s">
         <v>66</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="D77" s="13" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -21168,16 +21247,16 @@
     </row>
     <row r="79" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C79" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D79" s="13" t="s">
         <v>63</v>
-      </c>
-      <c r="D79" s="13" t="s">
-        <v>64</v>
       </c>
       <c r="E79" s="13" t="s">
         <v>27</v>
@@ -21185,30 +21264,30 @@
     </row>
     <row r="80" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="D80" s="14" t="s">
         <v>97</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="D80" s="14" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="D81" s="10" t="s">
         <v>42</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>905</v>
-      </c>
-      <c r="D81" s="10" t="s">
-        <v>43</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>27</v>
@@ -21216,40 +21295,40 @@
     </row>
     <row r="82" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D82" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="C82" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D82" s="10" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="C83" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="C84" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="D84" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D85" s="14"/>
     </row>
@@ -21258,7 +21337,7 @@
         <v>33</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>31</v>
@@ -21269,176 +21348,176 @@
     </row>
     <row r="87" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D87" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D87" s="10" t="s">
+      <c r="E87" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C88" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C88" s="14" t="s">
-        <v>159</v>
-      </c>
       <c r="D88" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E88" s="14"/>
     </row>
     <row r="89" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D89" s="14" t="s">
         <v>154</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D89" s="14" t="s">
-        <v>155</v>
       </c>
       <c r="E89" s="1"/>
     </row>
     <row r="90" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E90" s="13" t="s">
         <v>68</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D90" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E90" s="13" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C91" s="2" t="s">
+      <c r="D91" s="13" t="s">
         <v>73</v>
-      </c>
-      <c r="D91" s="13" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D93" s="14"/>
     </row>
     <row r="94" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D94" s="14" t="s">
         <v>81</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D94" s="14" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C95" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="D95" s="14" t="s">
         <v>140</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C95" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="D95" s="14" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="E96" s="1"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C99" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D99" s="14" t="s">
         <v>103</v>
-      </c>
-      <c r="D99" s="14" t="s">
-        <v>104</v>
       </c>
       <c r="E99" s="14" t="s">
         <v>27</v>
@@ -21446,16 +21525,16 @@
     </row>
     <row r="100" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C100" s="2" t="s">
+      <c r="D100" s="14" t="s">
         <v>101</v>
-      </c>
-      <c r="D100" s="14" t="s">
-        <v>102</v>
       </c>
       <c r="E100" s="14" t="s">
         <v>27</v>
@@ -21463,36 +21542,36 @@
     </row>
     <row r="101" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="C101" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D101" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="E101" s="14" t="s">
         <v>116</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="C101" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="D101" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="E101" s="14" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="C102" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D102" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="C102" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="D102" s="14" t="s">
-        <v>121</v>
-      </c>
       <c r="E102" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
@@ -21500,7 +21579,7 @@
         <v>24</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>26</v>
@@ -21517,7 +21596,7 @@
         <v>34</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>36</v>
@@ -21531,22 +21610,22 @@
     </row>
     <row r="105" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D105" s="14" t="s">
         <v>143</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D105" s="14" t="s">
-        <v>144</v>
       </c>
       <c r="E105" s="14"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C106" s="10"/>
       <c r="D106" s="2"/>
@@ -21554,31 +21633,31 @@
     </row>
     <row r="107" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D107" s="14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E107" s="14"/>
     </row>
     <row r="108" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C108" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D108" s="14" t="s">
         <v>129</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C108" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D108" s="14" t="s">
-        <v>130</v>
       </c>
       <c r="E108" s="2"/>
     </row>
@@ -21782,88 +21861,88 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B11" s="1"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
@@ -21891,7 +21970,7 @@
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -21899,21 +21978,21 @@
     </row>
     <row r="23" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="27" t="s">
+        <v>914</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>915</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="24" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -21937,16 +22016,16 @@
     </row>
     <row r="25" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>604</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>605</v>
       </c>
       <c r="E25" s="2"/>
       <c r="G25" s="1"/>
@@ -21967,19 +22046,19 @@
     </row>
     <row r="26" spans="1:23" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>644</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="2"/>
@@ -21999,16 +22078,16 @@
     </row>
     <row r="27" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>646</v>
-      </c>
       <c r="C27" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="E27" s="2"/>
       <c r="G27" s="1"/>
@@ -22030,13 +22109,13 @@
     <row r="28" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E28" s="2"/>
       <c r="G28" s="1"/>
@@ -22058,13 +22137,13 @@
     <row r="29" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E29" s="2"/>
       <c r="G29" s="1"/>
@@ -22086,13 +22165,13 @@
     <row r="30" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="E30" s="2"/>
       <c r="G30" s="1"/>
@@ -22114,13 +22193,13 @@
     <row r="31" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E31" s="2"/>
       <c r="G31" s="1"/>
@@ -22142,13 +22221,13 @@
     <row r="32" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="E32" s="2"/>
       <c r="G32" s="1"/>
@@ -22170,13 +22249,13 @@
     <row r="33" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>223</v>
       </c>
       <c r="E33" s="2"/>
       <c r="G33" s="1"/>
@@ -22197,19 +22276,19 @@
     </row>
     <row r="34" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="2"/>
@@ -22229,12 +22308,12 @@
     </row>
     <row r="35" spans="1:23" s="7" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="22" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E35" s="4"/>
       <c r="G35" s="1"/>
@@ -22255,7 +22334,7 @@
     </row>
     <row r="36" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -22279,12 +22358,12 @@
     </row>
     <row r="37" spans="1:23" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="22" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E37" s="4"/>
       <c r="G37" s="1"/>
@@ -22305,12 +22384,12 @@
     </row>
     <row r="38" spans="1:23" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="22" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E38" s="4"/>
       <c r="G38" s="1"/>
@@ -22331,12 +22410,12 @@
     </row>
     <row r="39" spans="1:23" s="7" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="22" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E39" s="4"/>
       <c r="G39" s="1"/>
@@ -22357,12 +22436,12 @@
     </row>
     <row r="40" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="22" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E40" s="4"/>
       <c r="G40" s="1"/>
@@ -22383,12 +22462,12 @@
     </row>
     <row r="41" spans="1:23" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="22" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E41" s="4"/>
       <c r="G41" s="1"/>
@@ -22409,12 +22488,12 @@
     </row>
     <row r="42" spans="1:23" s="7" customFormat="1" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="22" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E42" s="4"/>
       <c r="G42" s="1"/>
@@ -22435,7 +22514,7 @@
     </row>
     <row r="43" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -22459,16 +22538,16 @@
     </row>
     <row r="44" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>279</v>
-      </c>
       <c r="D44" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E44" s="2"/>
       <c r="G44" s="1"/>
@@ -22489,16 +22568,16 @@
     </row>
     <row r="45" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="E45" s="2"/>
       <c r="G45" s="1"/>
@@ -22519,16 +22598,16 @@
     </row>
     <row r="46" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="E46" s="2"/>
       <c r="G46" s="1"/>
@@ -22549,16 +22628,16 @@
     </row>
     <row r="47" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="E47" s="2"/>
       <c r="G47" s="1"/>
@@ -22579,16 +22658,16 @@
     </row>
     <row r="48" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>608</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>609</v>
       </c>
       <c r="E48" s="2"/>
       <c r="G48" s="1"/>
@@ -22609,7 +22688,7 @@
     </row>
     <row r="49" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -22633,19 +22712,19 @@
     </row>
     <row r="50" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="D50" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="2"/>
@@ -22665,19 +22744,19 @@
     </row>
     <row r="51" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>954</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>628</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="2"/>
@@ -22697,19 +22776,19 @@
     </row>
     <row r="52" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>955</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>631</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>632</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="2"/>
@@ -22729,19 +22808,19 @@
     </row>
     <row r="53" spans="1:23" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C53" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>636</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>637</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="2"/>
@@ -22761,19 +22840,19 @@
     </row>
     <row r="54" spans="1:23" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="E54" s="2" t="s">
         <v>640</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>641</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="2"/>
@@ -22793,7 +22872,7 @@
     </row>
     <row r="55" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="15" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -22817,19 +22896,19 @@
     </row>
     <row r="56" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="D56" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>502</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>503</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="2"/>
@@ -22849,16 +22928,16 @@
     </row>
     <row r="57" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>507</v>
       </c>
       <c r="E57" s="2"/>
       <c r="G57" s="1"/>
@@ -22879,16 +22958,16 @@
     </row>
     <row r="58" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>584</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="7"/>
@@ -22912,37 +22991,37 @@
     </row>
     <row r="59" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>612</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>613</v>
       </c>
       <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -22966,19 +23045,19 @@
     </row>
     <row r="62" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="D62" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>682</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>683</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="2"/>
@@ -22998,10 +23077,10 @@
     </row>
     <row r="63" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -23024,10 +23103,10 @@
     </row>
     <row r="64" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -23050,10 +23129,10 @@
     </row>
     <row r="65" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -23076,10 +23155,10 @@
     </row>
     <row r="66" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
@@ -23102,13 +23181,13 @@
     </row>
     <row r="67" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
@@ -23130,10 +23209,10 @@
     </row>
     <row r="68" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
@@ -23156,10 +23235,10 @@
     </row>
     <row r="69" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -23182,13 +23261,13 @@
     </row>
     <row r="70" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="C70" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
@@ -23210,16 +23289,16 @@
     </row>
     <row r="71" spans="1:23" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>276</v>
-      </c>
       <c r="D71" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E71" s="2"/>
       <c r="G71" s="1"/>
@@ -23240,16 +23319,16 @@
     </row>
     <row r="72" spans="1:23" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>603</v>
-      </c>
       <c r="D72" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E72" s="2"/>
       <c r="G72" s="1"/>
@@ -23270,19 +23349,19 @@
     </row>
     <row r="73" spans="1:23" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="C73" s="27" t="s">
+        <v>902</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>902</v>
-      </c>
-      <c r="C73" s="27" t="s">
-        <v>903</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>592</v>
-      </c>
       <c r="E73" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="2"/>
@@ -23302,16 +23381,16 @@
     </row>
     <row r="74" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>593</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>594</v>
       </c>
       <c r="E74" s="2"/>
       <c r="G74" s="1"/>
@@ -23332,16 +23411,16 @@
     </row>
     <row r="75" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>597</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>598</v>
       </c>
       <c r="E75" s="2"/>
       <c r="G75" s="1"/>
@@ -23362,7 +23441,7 @@
     </row>
     <row r="76" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="15" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -23389,13 +23468,13 @@
         <v>28</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>489</v>
-      </c>
       <c r="D77" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E77" s="2"/>
       <c r="G77" s="1"/>
@@ -23416,7 +23495,7 @@
     </row>
     <row r="78" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="15" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -23440,16 +23519,16 @@
     </row>
     <row r="79" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>492</v>
-      </c>
       <c r="D79" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E79" s="2"/>
       <c r="G79" s="1"/>
@@ -23470,21 +23549,21 @@
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="81" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>515</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>516</v>
       </c>
       <c r="E81" s="2"/>
       <c r="G81" s="1"/>
@@ -23505,7 +23584,7 @@
     </row>
     <row r="82" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="15" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -23529,16 +23608,16 @@
     </row>
     <row r="83" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="7"/>
@@ -23562,21 +23641,21 @@
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A84" s="11" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="85" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>523</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>524</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="7"/>
@@ -23600,16 +23679,16 @@
     </row>
     <row r="86" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="C86" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D86" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="7"/>
@@ -23633,7 +23712,7 @@
     </row>
     <row r="87" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -23660,16 +23739,16 @@
     </row>
     <row r="88" spans="1:23" s="4" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="7"/>
@@ -23693,16 +23772,16 @@
     </row>
     <row r="89" spans="1:23" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>534</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>535</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="7"/>
@@ -23726,16 +23805,16 @@
     </row>
     <row r="90" spans="1:23" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>539</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="7"/>
@@ -23759,19 +23838,19 @@
     </row>
     <row r="91" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>543</v>
-      </c>
       <c r="E91" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F91" s="7"/>
       <c r="G91" s="1"/>
@@ -23794,19 +23873,19 @@
     </row>
     <row r="92" spans="1:23" s="4" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="C92" s="2" t="s">
+      <c r="E92" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>549</v>
       </c>
       <c r="F92" s="7"/>
       <c r="G92" s="1"/>
@@ -23829,16 +23908,16 @@
     </row>
     <row r="93" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="7"/>
@@ -23862,16 +23941,16 @@
     </row>
     <row r="94" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D94" s="2" t="s">
         <v>565</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>566</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="7"/>
@@ -23895,19 +23974,19 @@
     </row>
     <row r="95" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="E95" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>564</v>
       </c>
       <c r="F95" s="7"/>
       <c r="G95" s="1"/>
@@ -23930,19 +24009,19 @@
     </row>
     <row r="96" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="C96" s="2" t="s">
+      <c r="E96" s="2" t="s">
         <v>571</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>572</v>
       </c>
       <c r="F96" s="7"/>
       <c r="G96" s="1"/>
@@ -23965,19 +24044,19 @@
     </row>
     <row r="97" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="C97" s="2" t="s">
+      <c r="E97" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>557</v>
       </c>
       <c r="F97" s="7"/>
       <c r="G97" s="1"/>
@@ -24000,16 +24079,16 @@
     </row>
     <row r="98" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>559</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="7"/>
@@ -24033,16 +24112,16 @@
     </row>
     <row r="99" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>573</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>574</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="7"/>
@@ -24066,7 +24145,7 @@
     </row>
     <row r="100" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="15" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -24093,16 +24172,16 @@
     </row>
     <row r="101" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D101" s="2" t="s">
         <v>576</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>577</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="7"/>
@@ -24126,16 +24205,16 @@
     </row>
     <row r="102" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="D102" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>580</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="7"/>
@@ -24159,63 +24238,63 @@
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A103" s="15" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
     </row>
     <row r="104" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>616</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>617</v>
       </c>
       <c r="E104" s="2"/>
     </row>
     <row r="105" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="D105" s="2" t="s">
+      <c r="E105" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A106" s="15" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="107" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="G107" s="1"/>
       <c r="H107" s="2"/>
@@ -24236,10 +24315,10 @@
     <row r="108" spans="1:23" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A108" s="2"/>
       <c r="B108" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>676</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
@@ -24262,10 +24341,10 @@
     <row r="109" spans="1:23" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A109" s="2"/>
       <c r="B109" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>677</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>678</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
@@ -24288,10 +24367,10 @@
     <row r="110" spans="1:23" s="7" customFormat="1" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A110" s="2"/>
       <c r="B110" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
@@ -24313,22 +24392,22 @@
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A111" s="11" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="112" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G112" s="1"/>
       <c r="H112" s="2"/>
@@ -24348,19 +24427,19 @@
     </row>
     <row r="113" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="C113" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>226</v>
-      </c>
       <c r="D113" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G113" s="1"/>
       <c r="H113" s="2"/>
@@ -24380,19 +24459,19 @@
     </row>
     <row r="114" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="C114" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C114" s="2" t="s">
-        <v>229</v>
-      </c>
       <c r="D114" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G114" s="1"/>
       <c r="H114" s="2"/>
@@ -24412,19 +24491,19 @@
     </row>
     <row r="115" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="C115" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="D115" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="2"/>
@@ -24444,19 +24523,19 @@
     </row>
     <row r="116" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="C116" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="D116" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D116" s="2" t="s">
+      <c r="E116" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="2"/>
@@ -24476,19 +24555,19 @@
     </row>
     <row r="117" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>251</v>
-      </c>
       <c r="E117" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G117" s="1"/>
       <c r="H117" s="2"/>
@@ -24508,75 +24587,75 @@
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A118" s="15" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="119" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="D119" s="32" t="s">
+        <v>944</v>
+      </c>
+      <c r="E119" s="32" t="s">
         <v>946</v>
-      </c>
-      <c r="D119" s="32" t="s">
-        <v>945</v>
-      </c>
-      <c r="E119" s="32" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="120" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="C120" s="25" t="s">
+        <v>949</v>
+      </c>
+      <c r="D120" s="32" t="s">
         <v>948</v>
       </c>
-      <c r="C120" s="25" t="s">
+      <c r="E120" s="32" t="s">
         <v>950</v>
-      </c>
-      <c r="D120" s="32" t="s">
-        <v>949</v>
-      </c>
-      <c r="E120" s="32" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="121" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A121" s="25" t="s">
+        <v>951</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="D121" s="32" t="s">
         <v>952</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>956</v>
-      </c>
-      <c r="D121" s="32" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="122" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="C122" s="33" t="s">
+        <v>958</v>
+      </c>
+      <c r="D122" s="32" t="s">
         <v>957</v>
       </c>
-      <c r="C122" s="33" t="s">
+      <c r="E122" s="32" t="s">
         <v>959</v>
-      </c>
-      <c r="D122" s="32" t="s">
-        <v>958</v>
-      </c>
-      <c r="E122" s="32" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="123" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="C123" s="25" t="s">
+        <v>962</v>
+      </c>
+      <c r="D123" s="32" t="s">
         <v>961</v>
       </c>
-      <c r="C123" s="25" t="s">
+      <c r="E123" s="32" t="s">
         <v>963</v>
-      </c>
-      <c r="D123" s="32" t="s">
-        <v>962</v>
-      </c>
-      <c r="E123" s="32" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.3">
@@ -24680,74 +24759,74 @@
   <sheetData>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B5" s="20"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B6" s="21"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B9" s="20"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B10" s="20"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B13" s="21"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B14" s="20"/>
     </row>
@@ -24776,7 +24855,7 @@
     </row>
     <row r="18" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -24784,157 +24863,157 @@
     </row>
     <row r="19" spans="1:23" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="F19" s="7"/>
     </row>
     <row r="20" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F20" s="7"/>
     </row>
     <row r="21" spans="1:23" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D23" s="17" t="s">
         <v>436</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>437</v>
       </c>
       <c r="F23" s="7"/>
     </row>
     <row r="24" spans="1:23" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>478</v>
-      </c>
       <c r="D24" s="17" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F24" s="7"/>
     </row>
     <row r="25" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:23" s="2" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="C26" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>482</v>
       </c>
       <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:23" s="2" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="E27" s="17" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F27" s="7"/>
     </row>
     <row r="28" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E28" s="17" t="s">
         <v>384</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>385</v>
       </c>
       <c r="F28" s="7"/>
     </row>
     <row r="29" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F29" s="7"/>
     </row>
     <row r="30" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -24961,19 +25040,19 @@
     </row>
     <row r="31" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="1"/>
@@ -24998,10 +25077,10 @@
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="7"/>
@@ -25027,10 +25106,10 @@
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="7"/>
@@ -25056,10 +25135,10 @@
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="7"/>
@@ -25085,10 +25164,10 @@
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>303</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="7"/>
@@ -25112,19 +25191,19 @@
     </row>
     <row r="36" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="E36" s="17" t="s">
         <v>408</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>409</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="1"/>
@@ -25149,10 +25228,10 @@
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="7"/>
@@ -25178,10 +25257,10 @@
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="7"/>
@@ -25207,10 +25286,10 @@
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="7"/>
@@ -25236,10 +25315,10 @@
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>303</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="7"/>
@@ -25263,19 +25342,19 @@
     </row>
     <row r="41" spans="1:23" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="E41" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="1"/>
@@ -25300,10 +25379,10 @@
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="7"/>
@@ -25329,10 +25408,10 @@
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="7"/>
@@ -25358,10 +25437,10 @@
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="7"/>
@@ -25387,10 +25466,10 @@
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>303</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="7"/>
@@ -25414,16 +25493,16 @@
     </row>
     <row r="46" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>412</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="7"/>
@@ -25447,16 +25526,16 @@
     </row>
     <row r="47" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>333</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="7"/>
@@ -25480,16 +25559,16 @@
     </row>
     <row r="48" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D48" s="17" t="s">
         <v>440</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>441</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="1"/>
@@ -25512,16 +25591,16 @@
     </row>
     <row r="49" spans="1:28" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B49" s="27" t="s">
+        <v>905</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="D49" s="17" t="s">
         <v>440</v>
-      </c>
-      <c r="B49" s="27" t="s">
-        <v>906</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>909</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>441</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="1"/>
@@ -25544,7 +25623,7 @@
     </row>
     <row r="50" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -25571,16 +25650,16 @@
     </row>
     <row r="51" spans="1:28" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B51" s="36" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B51" s="37" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>433</v>
       </c>
       <c r="E51" s="2"/>
       <c r="G51" s="1"/>
@@ -25608,17 +25687,17 @@
       <c r="A52" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B52" s="37" t="s">
-        <v>1085</v>
+      <c r="B52" s="36" t="s">
+        <v>1081</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="E52" s="36" t="s">
-        <v>336</v>
+        <v>339</v>
+      </c>
+      <c r="E52" s="35" t="s">
+        <v>335</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="1"/>
@@ -25641,19 +25720,19 @@
     </row>
     <row r="53" spans="1:28" s="4" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B53" s="37" t="s">
-        <v>1086</v>
+        <v>122</v>
+      </c>
+      <c r="B53" s="36" t="s">
+        <v>1082</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>435</v>
-      </c>
       <c r="E53" s="17" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="1"/>
@@ -25676,7 +25755,7 @@
     </row>
     <row r="54" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -25703,16 +25782,16 @@
     </row>
     <row r="55" spans="1:28" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="1"/>
@@ -25735,16 +25814,16 @@
     </row>
     <row r="56" spans="1:28" s="4" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="7"/>
@@ -25768,16 +25847,16 @@
     </row>
     <row r="57" spans="1:28" s="4" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="7"/>
@@ -25801,16 +25880,16 @@
     </row>
     <row r="58" spans="1:28" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="7"/>
@@ -25834,19 +25913,19 @@
     </row>
     <row r="59" spans="1:28" s="4" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A59" s="17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="1"/>
@@ -25869,19 +25948,19 @@
     </row>
     <row r="60" spans="1:28" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>448</v>
-      </c>
       <c r="E60" s="17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="1"/>
@@ -25904,19 +25983,19 @@
     </row>
     <row r="61" spans="1:28" s="4" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C61" s="2" t="s">
+      <c r="E61" s="17" t="s">
         <v>423</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="E61" s="17" t="s">
-        <v>424</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="1"/>
@@ -25939,22 +26018,22 @@
     </row>
     <row r="62" spans="1:28" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E62" s="2"/>
     </row>
     <row r="63" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -25984,13 +26063,13 @@
         <v>24</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="7"/>
@@ -26014,19 +26093,19 @@
     </row>
     <row r="65" spans="1:28" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>317</v>
-      </c>
       <c r="C65" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="1"/>
@@ -26051,11 +26130,11 @@
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="1"/>
@@ -26078,16 +26157,16 @@
     </row>
     <row r="67" spans="1:28" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E67" s="2"/>
       <c r="G67" s="1"/>
@@ -26113,117 +26192,117 @@
     </row>
     <row r="68" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="69" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>404</v>
-      </c>
       <c r="E69" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="70" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C70" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>416</v>
-      </c>
       <c r="E70" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="71" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A71" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
     </row>
     <row r="72" spans="1:28" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>360</v>
       </c>
       <c r="E72" s="2"/>
     </row>
     <row r="73" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="C73" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>451</v>
       </c>
       <c r="E73" s="2"/>
     </row>
     <row r="74" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A74" s="15" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="C75" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="E75" s="2"/>
     </row>
     <row r="76" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -26232,58 +26311,58 @@
     </row>
     <row r="77" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="E78" s="2"/>
     </row>
     <row r="79" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>389</v>
-      </c>
       <c r="E79" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="80" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A80" s="2"/>
       <c r="B80" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
@@ -26291,10 +26370,10 @@
     <row r="81" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A81" s="2"/>
       <c r="B81" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
@@ -26302,43 +26381,43 @@
     <row r="82" spans="1:28" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A82" s="2"/>
       <c r="B82" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>398</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
     </row>
     <row r="83" spans="1:28" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>1089</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:28" s="7" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="2"/>
@@ -26363,19 +26442,19 @@
     </row>
     <row r="85" spans="1:28" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E85" s="17" t="s">
         <v>346</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="E85" s="17" t="s">
-        <v>347</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="2"/>
@@ -26400,7 +26479,7 @@
     </row>
     <row r="86" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -26429,155 +26508,155 @@
     </row>
     <row r="87" spans="1:28" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" s="11" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="89" spans="1:28" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C89" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>295</v>
       </c>
       <c r="E89" s="2"/>
     </row>
     <row r="90" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A90" s="2"/>
       <c r="C90" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="E90" s="2"/>
     </row>
     <row r="91" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A91" s="2"/>
       <c r="C91" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>289</v>
       </c>
       <c r="E91" s="2"/>
     </row>
     <row r="92" spans="1:28" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A92" s="2"/>
       <c r="C92" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="E92" s="2"/>
     </row>
     <row r="93" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A93" s="2"/>
       <c r="C93" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="E93" s="2"/>
     </row>
     <row r="94" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E94" s="17" t="s">
         <v>459</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E94" s="17" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="95" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2"/>
       <c r="C95" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="E95" s="2"/>
     </row>
     <row r="96" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2"/>
       <c r="C96" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>289</v>
       </c>
       <c r="E96" s="2"/>
     </row>
     <row r="97" spans="1:5" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A97" s="2"/>
       <c r="C97" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="E97" s="2"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="2"/>
       <c r="C98" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="E98" s="2"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="11" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E100" s="2"/>
     </row>
@@ -26627,91 +26706,91 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B9" s="21"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B10" s="20"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B11" s="20"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B14" s="21"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B15" s="20"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B16" s="20"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B17" s="20"/>
     </row>
@@ -26740,7 +26819,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -26748,634 +26827,634 @@
     </row>
     <row r="22" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C23" s="25"/>
       <c r="D23" s="24"/>
     </row>
     <row r="24" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C24" s="25" t="s">
         <v>753</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>754</v>
-      </c>
       <c r="D24" s="24" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C25" s="25" t="s">
+        <v>754</v>
+      </c>
+      <c r="D25" s="24" t="s">
         <v>755</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C26" s="25"/>
       <c r="D26" s="24"/>
     </row>
     <row r="27" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C27" s="25" t="s">
         <v>747</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="C27" s="25" t="s">
+      <c r="D27" s="24" t="s">
         <v>748</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>799</v>
+      </c>
+      <c r="D28" s="27" t="s">
         <v>798</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>800</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>730</v>
+      </c>
+      <c r="D29" s="24" t="s">
         <v>729</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>731</v>
-      </c>
-      <c r="D29" s="24" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C30" s="25"/>
       <c r="D30" s="24"/>
     </row>
     <row r="31" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C31" s="29" t="s">
+        <v>888</v>
+      </c>
+      <c r="D31" s="24" t="s">
         <v>732</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C31" s="29" t="s">
-        <v>889</v>
-      </c>
-      <c r="D31" s="24" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>889</v>
+      </c>
+      <c r="D32" s="27" t="s">
         <v>813</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C32" s="25" t="s">
-        <v>890</v>
-      </c>
-      <c r="D32" s="27" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>759</v>
+      </c>
+      <c r="D33" s="24" t="s">
         <v>758</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C33" s="25" t="s">
-        <v>760</v>
-      </c>
-      <c r="D33" s="24" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>890</v>
+      </c>
+      <c r="D34" s="24" t="s">
         <v>742</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C34" s="25" t="s">
-        <v>891</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>868</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>869</v>
+      </c>
+      <c r="E37" s="27" t="s">
         <v>867</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>871</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>869</v>
-      </c>
-      <c r="D37" s="27" t="s">
-        <v>870</v>
-      </c>
-      <c r="E37" s="27" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>785</v>
+      </c>
+      <c r="D39" s="24" t="s">
         <v>784</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="C39" s="25" t="s">
-        <v>786</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="D40" s="24"/>
     </row>
     <row r="41" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D41" s="24" t="s">
         <v>787</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="C41" s="25" t="s">
-        <v>1078</v>
-      </c>
-      <c r="D41" s="24" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C42" s="25" t="s">
         <v>774</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>775</v>
-      </c>
       <c r="D42" s="24" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C44" s="25" t="s">
+        <v>751</v>
+      </c>
+      <c r="D44" s="24" t="s">
         <v>750</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>752</v>
-      </c>
-      <c r="D44" s="24" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>803</v>
+      </c>
+      <c r="D45" s="24" t="s">
         <v>789</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="C45" s="25" t="s">
-        <v>804</v>
-      </c>
-      <c r="D45" s="24" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>844</v>
+      </c>
+      <c r="D47" s="27" t="s">
         <v>842</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="C47" s="25" t="s">
-        <v>845</v>
-      </c>
-      <c r="D47" s="27" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>766</v>
+      </c>
+      <c r="D48" s="24" t="s">
         <v>765</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>767</v>
-      </c>
-      <c r="D48" s="24" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>769</v>
+      </c>
+      <c r="D49" s="24" t="s">
         <v>768</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>770</v>
-      </c>
-      <c r="D49" s="24" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>772</v>
+      </c>
+      <c r="D50" s="24" t="s">
         <v>771</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>773</v>
-      </c>
-      <c r="D50" s="24" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="27"/>
     </row>
     <row r="52" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B52" s="27" t="s">
         <v>829</v>
       </c>
-      <c r="B52" s="27" t="s">
-        <v>830</v>
-      </c>
       <c r="C52" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B54" s="27" t="s">
         <v>832</v>
       </c>
-      <c r="B54" s="27" t="s">
-        <v>833</v>
-      </c>
       <c r="C54" s="25" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D54" s="27" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>814</v>
+      </c>
+      <c r="C55" s="26" t="s">
         <v>717</v>
       </c>
-      <c r="B55" s="27" t="s">
-        <v>815</v>
-      </c>
-      <c r="C55" s="26" t="s">
+      <c r="D55" s="24" t="s">
         <v>718</v>
-      </c>
-      <c r="D55" s="24" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>826</v>
+      </c>
+      <c r="D57" s="27" t="s">
         <v>825</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="C57" s="25" t="s">
-        <v>827</v>
-      </c>
-      <c r="D57" s="27" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>874</v>
+      </c>
+      <c r="D59" s="27" t="s">
         <v>873</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="C59" s="25" t="s">
+      <c r="E59" s="27" t="s">
         <v>875</v>
-      </c>
-      <c r="D59" s="27" t="s">
-        <v>874</v>
-      </c>
-      <c r="E59" s="27" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>811</v>
+      </c>
+      <c r="D60" s="27" t="s">
         <v>809</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>812</v>
-      </c>
-      <c r="D60" s="27" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>706</v>
+      </c>
+      <c r="D61" s="24" t="s">
         <v>702</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>707</v>
-      </c>
-      <c r="D61" s="24" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C62" s="25"/>
       <c r="D62" s="27"/>
     </row>
     <row r="63" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>801</v>
+      </c>
+      <c r="D63" s="27" t="s">
         <v>795</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="C63" s="25" t="s">
-        <v>802</v>
-      </c>
-      <c r="D63" s="27" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>878</v>
+      </c>
+      <c r="D64" s="27" t="s">
         <v>877</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="E64" s="27" t="s">
         <v>880</v>
-      </c>
-      <c r="C64" s="25" t="s">
-        <v>879</v>
-      </c>
-      <c r="D64" s="27" t="s">
-        <v>878</v>
-      </c>
-      <c r="E64" s="27" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C65" s="25"/>
       <c r="D65" s="24"/>
     </row>
     <row r="66" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="C66" s="25" t="s">
+        <v>707</v>
+      </c>
+      <c r="D66" s="24" t="s">
         <v>699</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="C66" s="25" t="s">
-        <v>708</v>
-      </c>
-      <c r="D66" s="24" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>736</v>
+      </c>
+      <c r="D67" s="24" t="s">
         <v>734</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="C67" s="25" t="s">
-        <v>737</v>
-      </c>
-      <c r="D67" s="24" t="s">
+      <c r="E67" s="24" t="s">
         <v>735</v>
-      </c>
-      <c r="E67" s="24" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="C68" s="26" t="s">
+        <v>705</v>
+      </c>
+      <c r="D68" s="24" t="s">
         <v>704</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="C68" s="26" t="s">
-        <v>706</v>
-      </c>
-      <c r="D68" s="24" t="s">
-        <v>705</v>
-      </c>
       <c r="E68" s="24" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="C69" s="25" t="s">
         <v>710</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="C69" s="25" t="s">
-        <v>711</v>
-      </c>
       <c r="D69" s="24" t="s">
+        <v>713</v>
+      </c>
+      <c r="E69" s="24" t="s">
         <v>714</v>
-      </c>
-      <c r="E69" s="24" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>802</v>
+      </c>
+      <c r="D70" s="27" t="s">
         <v>792</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="C70" s="25" t="s">
-        <v>803</v>
-      </c>
-      <c r="D70" s="27" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="28" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B71" s="27"/>
       <c r="C71" s="26"/>
@@ -27383,91 +27462,91 @@
     </row>
     <row r="72" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="C72" s="25" t="s">
+        <v>860</v>
+      </c>
+      <c r="D72" s="27" t="s">
         <v>855</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>865</v>
-      </c>
-      <c r="C72" s="25" t="s">
-        <v>861</v>
-      </c>
-      <c r="D72" s="27" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="C73" s="25" t="s">
+        <v>859</v>
+      </c>
+      <c r="D73" s="27" t="s">
         <v>857</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>866</v>
-      </c>
-      <c r="C73" s="25" t="s">
-        <v>860</v>
-      </c>
-      <c r="D73" s="27" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>858</v>
+      </c>
+      <c r="D74" s="27" t="s">
         <v>806</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>864</v>
-      </c>
-      <c r="C74" s="25" t="s">
-        <v>859</v>
-      </c>
-      <c r="D74" s="27" t="s">
+      <c r="E74" s="27" t="s">
         <v>807</v>
-      </c>
-      <c r="E74" s="27" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>861</v>
+      </c>
+      <c r="D75" s="24" t="s">
         <v>780</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>863</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>862</v>
-      </c>
-      <c r="D75" s="24" t="s">
+      <c r="E75" s="24" t="s">
         <v>781</v>
-      </c>
-      <c r="E75" s="24" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C76" s="25"/>
       <c r="D76" s="24"/>
     </row>
     <row r="77" spans="1:5" ht="216" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C77" s="2" t="s">
+      <c r="D77" s="24" t="s">
         <v>745</v>
-      </c>
-      <c r="D77" s="24" t="s">
-        <v>746</v>
       </c>
       <c r="E77" s="24"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C78" s="25"/>
       <c r="D78" s="27"/>
@@ -27475,75 +27554,75 @@
     </row>
     <row r="79" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="C79" s="25" t="s">
+        <v>851</v>
+      </c>
+      <c r="D79" s="27" t="s">
         <v>846</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="C79" s="25" t="s">
-        <v>852</v>
-      </c>
-      <c r="D79" s="27" t="s">
-        <v>847</v>
-      </c>
       <c r="E79" s="27" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E80" s="27" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D82" s="27" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E82" s="27" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="28" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C83" s="25"/>
       <c r="D83" s="24"/>
@@ -27551,35 +27630,35 @@
     </row>
     <row r="84" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="C84" s="25" t="s">
+        <v>722</v>
+      </c>
+      <c r="D84" s="24" t="s">
         <v>721</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="C84" s="25" t="s">
-        <v>723</v>
-      </c>
-      <c r="D84" s="24" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="C85" s="25" t="s">
         <v>725</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="C85" s="25" t="s">
+      <c r="D85" s="24" t="s">
         <v>726</v>
-      </c>
-      <c r="D85" s="24" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -27587,16 +27666,16 @@
     </row>
     <row r="87" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="C87" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="D87" s="24" t="s">
         <v>738</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="C87" s="25" t="s">
-        <v>740</v>
-      </c>
-      <c r="D87" s="24" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -27682,76 +27761,76 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B9" s="21"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -27786,7 +27865,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -27794,114 +27873,114 @@
     </row>
     <row r="22" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>915</v>
+        <v>1034</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>914</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="D23" s="32" t="s">
         <v>986</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>988</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>990</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>989</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>991</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>995</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>997</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>993</v>
+      </c>
+      <c r="D26" s="32" t="s">
         <v>992</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>994</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="D28" s="32" t="s">
         <v>998</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>999</v>
       </c>
       <c r="E28" s="24"/>
     </row>
     <row r="29" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E29" s="32" t="s">
         <v>1002</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E29" s="32" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="28" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -27909,18 +27988,18 @@
     </row>
     <row r="31" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>920</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>919</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>921</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="34" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -27928,143 +28007,143 @@
     </row>
     <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C34" s="25"/>
       <c r="D34" s="32"/>
     </row>
     <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>942</v>
+      </c>
+      <c r="D36" s="32" t="s">
         <v>941</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>943</v>
-      </c>
-      <c r="D36" s="32" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C37" s="25"/>
       <c r="D37" s="32"/>
     </row>
     <row r="38" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>978</v>
+      </c>
+      <c r="D38" s="32" t="s">
         <v>936</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C38" s="25" t="s">
-        <v>979</v>
-      </c>
-      <c r="D38" s="32" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="D39" s="32" t="s">
         <v>976</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D39" s="32" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D40" s="32" t="s">
         <v>1014</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C40" s="25" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D40" s="32" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="D41" s="32"/>
     </row>
     <row r="42" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>939</v>
+      </c>
+      <c r="D42" s="32" t="s">
         <v>938</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>940</v>
-      </c>
-      <c r="D42" s="32" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C43" s="25"/>
       <c r="D43" s="32"/>
     </row>
     <row r="44" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="D44" s="32" t="s">
         <v>983</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>985</v>
-      </c>
-      <c r="D44" s="32" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C45" s="25"/>
       <c r="D45" s="32"/>
@@ -28072,88 +28151,88 @@
     </row>
     <row r="46" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D46" s="32" t="s">
         <v>1005</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D46" s="32" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="D47" s="32" t="s">
         <v>980</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>982</v>
-      </c>
-      <c r="D47" s="32" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="D48" s="32" t="s">
         <v>973</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>975</v>
-      </c>
-      <c r="D48" s="32" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D49" s="32" t="s">
         <v>1008</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>1010</v>
-      </c>
-      <c r="D49" s="32" t="s">
-        <v>1009</v>
       </c>
       <c r="E49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D50" s="32" t="s">
         <v>1011</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D50" s="32" t="s">
-        <v>1012</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>931</v>
+      </c>
+      <c r="D51" s="32" t="s">
         <v>930</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C51" s="25" t="s">
-        <v>932</v>
-      </c>
-      <c r="D51" s="32" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
@@ -29496,72 +29575,72 @@
     </row>
     <row r="21" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>1048</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>1050</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>1052</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D23" s="32" t="s">
         <v>1054</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>1057</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>1059</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>1060</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1062</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">

--- a/4 четверть_13_JavaScript_sugarJS.xlsx
+++ b/4 четверть_13_JavaScript_sugarJS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585B7D47-A702-413C-BA4D-66087824D8C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F0778A-5208-4EE8-95EE-CF2997BF0BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11730" yWindow="-18075" windowWidth="28770" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-12315" yWindow="-18960" windowWidth="28770" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sugarjs" sheetId="20" r:id="rId1"/>
@@ -1873,15 +1873,6 @@
     </r>
   </si>
   <si>
-    <t>[1,2,3].none(5) true
-['a','b','c'].none(/b/) false
-users.none(function(user) {
-  return user.name == 'Wolverine';
-});
-true
-users.none({ name: 'Wolverine' }); true</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Returns true if none of the elements in the array match search. 
 </t>
@@ -17762,13 +17753,6 @@
     </r>
   </si>
   <si>
-    <t>[1,2,3].includes(2) true
-[1,2,3].includes(4) false
-[1,2,3].includes(2, 3) false
-аналог includes
-tfaAccessChannel.filter(item =&gt; item.frontName === 'Max').length</t>
-  </si>
-  <si>
     <r>
       <t>create</t>
     </r>
@@ -18343,6 +18327,61 @@
 [{a:1},{b:2}].exclude(function(n) {
   return n['a'] == 1;
 }); [{"b":2}]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[1,2,3].includes(2) true
+[1,2,3].includes(4) false
+[1,2,3].includes(2, 3) false
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>аналог includes (не имеет смысла, тк includes может искать объекты в массвах объектов)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+tfaAccessChannel.filter(item =&gt; item.frontName === 'Max').length</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[1,2,3].none(5) true
+['a','b','c'].none(/b/) false
+users.none(function(user) {
+  return user.name == 'Wolverine';
+});
+true
+users.none({ name: 'Wolverine' }); true
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>none может искать объекты в массвах объектов</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -18780,13 +18819,13 @@
     <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -18818,7 +18857,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>3421380</xdr:colOff>
+      <xdr:colOff>3417570</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>840585</xdr:rowOff>
     </xdr:to>
@@ -19225,7 +19264,7 @@
     </row>
     <row r="4" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -19249,11 +19288,11 @@
     </row>
     <row r="5" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -19275,13 +19314,13 @@
     </row>
     <row r="6" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -19303,7 +19342,7 @@
     </row>
     <row r="7" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -19329,7 +19368,7 @@
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -20329,80 +20368,80 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C16" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="D16" s="17" t="s">
         <v>353</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -20440,7 +20479,7 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -20458,16 +20497,16 @@
     </row>
     <row r="20" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="36" t="s">
+        <v>909</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>910</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>911</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="1"/>
@@ -20482,7 +20521,7 @@
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="9"/>
@@ -20495,10 +20534,10 @@
         <v>0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>1</v>
@@ -20509,153 +20548,153 @@
     </row>
     <row r="23" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>1016</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>971</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>1017</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>1021</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>971</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>1022</v>
-      </c>
       <c r="E24" s="32" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>1067</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1073</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>1068</v>
-      </c>
       <c r="E25" s="32" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D26" s="32" t="s">
         <v>968</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>971</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D26" s="32" t="s">
+      <c r="E26" s="32" t="s">
         <v>969</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D31" s="32" t="s">
         <v>1067</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>1072</v>
-      </c>
-      <c r="D31" s="32" t="s">
-        <v>1068</v>
-      </c>
       <c r="E31" s="32" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>905</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="D32" s="17" t="s">
         <v>439</v>
-      </c>
-      <c r="B32" s="27" t="s">
-        <v>906</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
@@ -20663,10 +20702,10 @@
         <v>96</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>97</v>
@@ -20674,33 +20713,33 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>674</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>675</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -20708,10 +20747,10 @@
     <row r="37" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>677</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -20719,10 +20758,10 @@
     <row r="38" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>679</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -20732,7 +20771,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="2"/>
@@ -20743,7 +20782,7 @@
         <v>28</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>30</v>
@@ -20754,7 +20793,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
@@ -20773,7 +20812,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>76</v>
       </c>
@@ -20781,24 +20820,24 @@
         <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D45" s="14" t="s">
         <v>112</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>113</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>27</v>
@@ -20851,22 +20890,22 @@
     </row>
     <row r="49" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C49" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="D49" s="14" t="s">
         <v>133</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>134</v>
       </c>
       <c r="E49" s="14"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C50" s="10"/>
       <c r="D50" s="10"/>
@@ -20877,7 +20916,7 @@
         <v>16</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>14</v>
@@ -20891,10 +20930,10 @@
         <v>40</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>44</v>
@@ -20908,13 +20947,13 @@
         <v>17</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -20922,27 +20961,27 @@
         <v>22</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C55" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C55" s="14" t="s">
-        <v>123</v>
-      </c>
       <c r="D55" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>27</v>
@@ -20950,22 +20989,22 @@
     </row>
     <row r="56" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C56" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="D56" s="16" t="s">
         <v>186</v>
-      </c>
-      <c r="C56" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>187</v>
       </c>
       <c r="E56" s="14"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D57" s="10"/>
     </row>
@@ -20974,7 +21013,7 @@
         <v>23</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>20</v>
@@ -20988,10 +21027,10 @@
         <v>43</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>45</v>
@@ -21005,7 +21044,7 @@
         <v>77</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>79</v>
@@ -21019,7 +21058,7 @@
         <v>92</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>94</v>
@@ -21028,18 +21067,18 @@
         <v>93</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>27</v>
@@ -21050,7 +21089,7 @@
         <v>106</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>95</v>
@@ -21064,7 +21103,7 @@
         <v>111</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C64" s="14" t="s">
         <v>109</v>
@@ -21075,66 +21114,66 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D65" s="14"/>
     </row>
     <row r="66" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D66" s="14" t="s">
         <v>136</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="D66" s="14" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D67" s="14" t="s">
         <v>160</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D68" s="14" t="s">
         <v>163</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D68" s="14" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="144" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C69" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="D69" s="14" t="s">
         <v>165</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="2"/>
@@ -21145,7 +21184,7 @@
         <v>2</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>7</v>
@@ -21162,7 +21201,7 @@
         <v>6</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>9</v>
@@ -21174,7 +21213,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D73" s="10"/>
       <c r="E73" s="10"/>
@@ -21187,7 +21226,7 @@
         <v>49</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>48</v>
@@ -21201,7 +21240,7 @@
         <v>49</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>91</v>
@@ -21209,16 +21248,16 @@
     </row>
     <row r="76" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C76" s="37" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D76" s="14" t="s">
         <v>145</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C76" s="37" t="s">
-        <v>1088</v>
-      </c>
-      <c r="D76" s="14" t="s">
-        <v>146</v>
       </c>
       <c r="E76" s="14"/>
     </row>
@@ -21227,10 +21266,10 @@
         <v>65</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>66</v>
@@ -21238,7 +21277,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -21250,7 +21289,7 @@
         <v>64</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>62</v>
@@ -21267,10 +21306,10 @@
         <v>96</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>97</v>
@@ -21281,10 +21320,10 @@
         <v>41</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>42</v>
@@ -21328,7 +21367,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D85" s="14"/>
     </row>
@@ -21337,7 +21376,7 @@
         <v>33</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>31</v>
@@ -21351,10 +21390,10 @@
         <v>50</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>51</v>
@@ -21365,31 +21404,31 @@
     </row>
     <row r="88" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C88" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C88" s="14" t="s">
-        <v>158</v>
-      </c>
       <c r="D88" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E88" s="14"/>
     </row>
     <row r="89" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D89" s="14" t="s">
         <v>153</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D89" s="14" t="s">
-        <v>154</v>
       </c>
       <c r="E89" s="1"/>
     </row>
@@ -21398,7 +21437,7 @@
         <v>67</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>69</v>
@@ -21415,7 +21454,7 @@
         <v>71</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>72</v>
@@ -21429,18 +21468,18 @@
         <v>74</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D93" s="14"/>
     </row>
@@ -21449,7 +21488,7 @@
         <v>80</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>82</v>
@@ -21460,36 +21499,36 @@
     </row>
     <row r="95" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C95" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="D95" s="14" t="s">
         <v>139</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C95" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="D95" s="14" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="E96" s="1"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
@@ -21497,7 +21536,7 @@
         <v>105</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C98" s="14" t="s">
         <v>108</v>
@@ -21511,7 +21550,7 @@
         <v>104</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>102</v>
@@ -21528,7 +21567,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>100</v>
@@ -21542,36 +21581,36 @@
     </row>
     <row r="101" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="C101" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D101" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E101" s="14" t="s">
         <v>115</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="C101" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="D101" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E101" s="14" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="C102" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D102" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="C102" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D102" s="14" t="s">
-        <v>120</v>
-      </c>
       <c r="E102" s="14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
@@ -21579,7 +21618,7 @@
         <v>24</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>26</v>
@@ -21596,7 +21635,7 @@
         <v>34</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>36</v>
@@ -21610,22 +21649,22 @@
     </row>
     <row r="105" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D105" s="14" t="s">
         <v>142</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D105" s="14" t="s">
-        <v>143</v>
       </c>
       <c r="E105" s="14"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C106" s="10"/>
       <c r="D106" s="2"/>
@@ -21633,31 +21672,31 @@
     </row>
     <row r="107" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D107" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E107" s="14"/>
     </row>
     <row r="108" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C108" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D108" s="14" t="s">
         <v>128</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C108" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="D108" s="14" t="s">
-        <v>129</v>
       </c>
       <c r="E108" s="2"/>
     </row>
@@ -21861,88 +21900,88 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B11" s="1"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
@@ -21970,7 +22009,7 @@
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -21978,21 +22017,21 @@
     </row>
     <row r="23" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="27" t="s">
+        <v>913</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>914</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="24" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -22016,16 +22055,16 @@
     </row>
     <row r="25" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>603</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>604</v>
       </c>
       <c r="E25" s="2"/>
       <c r="G25" s="1"/>
@@ -22046,19 +22085,19 @@
     </row>
     <row r="26" spans="1:23" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>643</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="2"/>
@@ -22078,16 +22117,16 @@
     </row>
     <row r="27" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>645</v>
-      </c>
       <c r="C27" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="E27" s="2"/>
       <c r="G27" s="1"/>
@@ -22109,13 +22148,13 @@
     <row r="28" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E28" s="2"/>
       <c r="G28" s="1"/>
@@ -22137,13 +22176,13 @@
     <row r="29" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E29" s="2"/>
       <c r="G29" s="1"/>
@@ -22165,13 +22204,13 @@
     <row r="30" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="E30" s="2"/>
       <c r="G30" s="1"/>
@@ -22193,13 +22232,13 @@
     <row r="31" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E31" s="2"/>
       <c r="G31" s="1"/>
@@ -22221,13 +22260,13 @@
     <row r="32" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>220</v>
       </c>
       <c r="E32" s="2"/>
       <c r="G32" s="1"/>
@@ -22249,13 +22288,13 @@
     <row r="33" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="E33" s="2"/>
       <c r="G33" s="1"/>
@@ -22276,19 +22315,19 @@
     </row>
     <row r="34" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>509</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>510</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="2"/>
@@ -22308,12 +22347,12 @@
     </row>
     <row r="35" spans="1:23" s="7" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="22" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E35" s="4"/>
       <c r="G35" s="1"/>
@@ -22334,7 +22373,7 @@
     </row>
     <row r="36" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -22358,12 +22397,12 @@
     </row>
     <row r="37" spans="1:23" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="22" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E37" s="4"/>
       <c r="G37" s="1"/>
@@ -22384,12 +22423,12 @@
     </row>
     <row r="38" spans="1:23" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="22" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E38" s="4"/>
       <c r="G38" s="1"/>
@@ -22410,12 +22449,12 @@
     </row>
     <row r="39" spans="1:23" s="7" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="22" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E39" s="4"/>
       <c r="G39" s="1"/>
@@ -22436,12 +22475,12 @@
     </row>
     <row r="40" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="22" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E40" s="4"/>
       <c r="G40" s="1"/>
@@ -22462,12 +22501,12 @@
     </row>
     <row r="41" spans="1:23" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="22" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E41" s="4"/>
       <c r="G41" s="1"/>
@@ -22488,12 +22527,12 @@
     </row>
     <row r="42" spans="1:23" s="7" customFormat="1" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="22" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E42" s="4"/>
       <c r="G42" s="1"/>
@@ -22514,7 +22553,7 @@
     </row>
     <row r="43" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -22538,16 +22577,16 @@
     </row>
     <row r="44" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="D44" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E44" s="2"/>
       <c r="G44" s="1"/>
@@ -22568,16 +22607,16 @@
     </row>
     <row r="45" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="E45" s="2"/>
       <c r="G45" s="1"/>
@@ -22598,16 +22637,16 @@
     </row>
     <row r="46" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>493</v>
       </c>
       <c r="E46" s="2"/>
       <c r="G46" s="1"/>
@@ -22628,16 +22667,16 @@
     </row>
     <row r="47" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>497</v>
       </c>
       <c r="E47" s="2"/>
       <c r="G47" s="1"/>
@@ -22658,16 +22697,16 @@
     </row>
     <row r="48" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>607</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>608</v>
       </c>
       <c r="E48" s="2"/>
       <c r="G48" s="1"/>
@@ -22688,7 +22727,7 @@
     </row>
     <row r="49" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -22712,19 +22751,19 @@
     </row>
     <row r="50" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>234</v>
-      </c>
       <c r="D50" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="2"/>
@@ -22744,19 +22783,19 @@
     </row>
     <row r="51" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>953</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>626</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>627</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="2"/>
@@ -22776,19 +22815,19 @@
     </row>
     <row r="52" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>954</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>630</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>631</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="2"/>
@@ -22808,19 +22847,19 @@
     </row>
     <row r="53" spans="1:23" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="C53" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>635</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>636</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="2"/>
@@ -22840,19 +22879,19 @@
     </row>
     <row r="54" spans="1:23" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="E54" s="2" t="s">
         <v>639</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>640</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="2"/>
@@ -22872,7 +22911,7 @@
     </row>
     <row r="55" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="15" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -22896,19 +22935,19 @@
     </row>
     <row r="56" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="D56" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="2"/>
@@ -22928,16 +22967,16 @@
     </row>
     <row r="57" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="E57" s="2"/>
       <c r="G57" s="1"/>
@@ -22958,16 +22997,16 @@
     </row>
     <row r="58" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>582</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>583</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="7"/>
@@ -22991,37 +23030,37 @@
     </row>
     <row r="59" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>586</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>587</v>
       </c>
       <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>611</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>612</v>
       </c>
       <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -23045,19 +23084,19 @@
     </row>
     <row r="62" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="D62" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>682</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="2"/>
@@ -23077,10 +23116,10 @@
     </row>
     <row r="63" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -23103,10 +23142,10 @@
     </row>
     <row r="64" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -23129,10 +23168,10 @@
     </row>
     <row r="65" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -23155,10 +23194,10 @@
     </row>
     <row r="66" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
@@ -23181,13 +23220,13 @@
     </row>
     <row r="67" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
@@ -23209,10 +23248,10 @@
     </row>
     <row r="68" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
@@ -23235,10 +23274,10 @@
     </row>
     <row r="69" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -23261,13 +23300,13 @@
     </row>
     <row r="70" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="C70" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
@@ -23289,16 +23328,16 @@
     </row>
     <row r="71" spans="1:23" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>275</v>
-      </c>
       <c r="D71" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E71" s="2"/>
       <c r="G71" s="1"/>
@@ -23319,16 +23358,16 @@
     </row>
     <row r="72" spans="1:23" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>602</v>
-      </c>
       <c r="D72" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E72" s="2"/>
       <c r="G72" s="1"/>
@@ -23349,19 +23388,19 @@
     </row>
     <row r="73" spans="1:23" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="C73" s="27" t="s">
+        <v>901</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="C73" s="27" t="s">
-        <v>902</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>591</v>
-      </c>
       <c r="E73" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="2"/>
@@ -23381,16 +23420,16 @@
     </row>
     <row r="74" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>592</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>593</v>
       </c>
       <c r="E74" s="2"/>
       <c r="G74" s="1"/>
@@ -23411,16 +23450,16 @@
     </row>
     <row r="75" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>596</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>597</v>
       </c>
       <c r="E75" s="2"/>
       <c r="G75" s="1"/>
@@ -23441,7 +23480,7 @@
     </row>
     <row r="76" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="15" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -23468,13 +23507,13 @@
         <v>28</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>488</v>
-      </c>
       <c r="D77" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E77" s="2"/>
       <c r="G77" s="1"/>
@@ -23495,7 +23534,7 @@
     </row>
     <row r="78" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="15" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -23519,16 +23558,16 @@
     </row>
     <row r="79" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>491</v>
-      </c>
       <c r="D79" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E79" s="2"/>
       <c r="G79" s="1"/>
@@ -23549,21 +23588,21 @@
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="81" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>515</v>
       </c>
       <c r="E81" s="2"/>
       <c r="G81" s="1"/>
@@ -23584,7 +23623,7 @@
     </row>
     <row r="82" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="15" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -23608,16 +23647,16 @@
     </row>
     <row r="83" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="7"/>
@@ -23641,21 +23680,21 @@
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A84" s="11" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="85" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>522</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>523</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="7"/>
@@ -23679,16 +23718,16 @@
     </row>
     <row r="86" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="C86" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D86" s="2" t="s">
         <v>527</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>528</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="7"/>
@@ -23712,7 +23751,7 @@
     </row>
     <row r="87" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -23739,16 +23778,16 @@
     </row>
     <row r="88" spans="1:23" s="4" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>529</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>530</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="7"/>
@@ -23772,16 +23811,16 @@
     </row>
     <row r="89" spans="1:23" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>533</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>534</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="7"/>
@@ -23805,16 +23844,16 @@
     </row>
     <row r="90" spans="1:23" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>538</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="7"/>
@@ -23838,19 +23877,19 @@
     </row>
     <row r="91" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>542</v>
-      </c>
       <c r="E91" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F91" s="7"/>
       <c r="G91" s="1"/>
@@ -23873,19 +23912,19 @@
     </row>
     <row r="92" spans="1:23" s="4" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="C92" s="2" t="s">
+      <c r="E92" s="2" t="s">
         <v>547</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>548</v>
       </c>
       <c r="F92" s="7"/>
       <c r="G92" s="1"/>
@@ -23908,16 +23947,16 @@
     </row>
     <row r="93" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="7"/>
@@ -23941,16 +23980,16 @@
     </row>
     <row r="94" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D94" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>565</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="7"/>
@@ -23974,19 +24013,19 @@
     </row>
     <row r="95" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="E95" s="2" t="s">
         <v>562</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>563</v>
       </c>
       <c r="F95" s="7"/>
       <c r="G95" s="1"/>
@@ -24009,19 +24048,19 @@
     </row>
     <row r="96" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="C96" s="2" t="s">
+      <c r="E96" s="2" t="s">
         <v>570</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>571</v>
       </c>
       <c r="F96" s="7"/>
       <c r="G96" s="1"/>
@@ -24044,19 +24083,19 @@
     </row>
     <row r="97" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="C97" s="2" t="s">
+      <c r="E97" s="2" t="s">
         <v>555</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>556</v>
       </c>
       <c r="F97" s="7"/>
       <c r="G97" s="1"/>
@@ -24079,16 +24118,16 @@
     </row>
     <row r="98" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>558</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="7"/>
@@ -24112,16 +24151,16 @@
     </row>
     <row r="99" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>572</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>573</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="7"/>
@@ -24145,7 +24184,7 @@
     </row>
     <row r="100" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="15" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -24172,16 +24211,16 @@
     </row>
     <row r="101" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D101" s="2" t="s">
         <v>575</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>576</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="7"/>
@@ -24205,16 +24244,16 @@
     </row>
     <row r="102" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="D102" s="2" t="s">
         <v>578</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>579</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="7"/>
@@ -24238,63 +24277,63 @@
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A103" s="15" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
     </row>
     <row r="104" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>615</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>616</v>
       </c>
       <c r="E104" s="2"/>
     </row>
     <row r="105" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="D105" s="2" t="s">
+      <c r="E105" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A106" s="15" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="107" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>236</v>
       </c>
       <c r="G107" s="1"/>
       <c r="H107" s="2"/>
@@ -24315,10 +24354,10 @@
     <row r="108" spans="1:23" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A108" s="2"/>
       <c r="B108" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>674</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>675</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
@@ -24341,10 +24380,10 @@
     <row r="109" spans="1:23" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A109" s="2"/>
       <c r="B109" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>677</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
@@ -24367,10 +24406,10 @@
     <row r="110" spans="1:23" s="7" customFormat="1" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A110" s="2"/>
       <c r="B110" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>679</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
@@ -24392,22 +24431,22 @@
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A111" s="11" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="112" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G112" s="1"/>
       <c r="H112" s="2"/>
@@ -24427,19 +24466,19 @@
     </row>
     <row r="113" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="C113" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>225</v>
-      </c>
       <c r="D113" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G113" s="1"/>
       <c r="H113" s="2"/>
@@ -24459,19 +24498,19 @@
     </row>
     <row r="114" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="C114" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C114" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="D114" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G114" s="1"/>
       <c r="H114" s="2"/>
@@ -24491,19 +24530,19 @@
     </row>
     <row r="115" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="C115" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>231</v>
-      </c>
       <c r="D115" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="2"/>
@@ -24523,19 +24562,19 @@
     </row>
     <row r="116" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="C116" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="D116" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D116" s="2" t="s">
+      <c r="E116" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="2"/>
@@ -24555,19 +24594,19 @@
     </row>
     <row r="117" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>250</v>
-      </c>
       <c r="E117" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G117" s="1"/>
       <c r="H117" s="2"/>
@@ -24587,75 +24626,75 @@
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A118" s="15" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="119" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="D119" s="32" t="s">
+        <v>943</v>
+      </c>
+      <c r="E119" s="32" t="s">
         <v>945</v>
-      </c>
-      <c r="D119" s="32" t="s">
-        <v>944</v>
-      </c>
-      <c r="E119" s="32" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="120" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="C120" s="25" t="s">
+        <v>948</v>
+      </c>
+      <c r="D120" s="32" t="s">
         <v>947</v>
       </c>
-      <c r="C120" s="25" t="s">
+      <c r="E120" s="32" t="s">
         <v>949</v>
-      </c>
-      <c r="D120" s="32" t="s">
-        <v>948</v>
-      </c>
-      <c r="E120" s="32" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="121" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A121" s="25" t="s">
+        <v>950</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="D121" s="32" t="s">
         <v>951</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>955</v>
-      </c>
-      <c r="D121" s="32" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="122" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="C122" s="33" t="s">
+        <v>957</v>
+      </c>
+      <c r="D122" s="32" t="s">
         <v>956</v>
       </c>
-      <c r="C122" s="33" t="s">
+      <c r="E122" s="32" t="s">
         <v>958</v>
-      </c>
-      <c r="D122" s="32" t="s">
-        <v>957</v>
-      </c>
-      <c r="E122" s="32" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="123" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="C123" s="25" t="s">
+        <v>961</v>
+      </c>
+      <c r="D123" s="32" t="s">
         <v>960</v>
       </c>
-      <c r="C123" s="25" t="s">
+      <c r="E123" s="32" t="s">
         <v>962</v>
-      </c>
-      <c r="D123" s="32" t="s">
-        <v>961</v>
-      </c>
-      <c r="E123" s="32" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.3">
@@ -24759,74 +24798,74 @@
   <sheetData>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B5" s="20"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B6" s="21"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B9" s="20"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B10" s="20"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B13" s="21"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B14" s="20"/>
     </row>
@@ -24855,7 +24894,7 @@
     </row>
     <row r="18" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -24863,157 +24902,157 @@
     </row>
     <row r="19" spans="1:23" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>311</v>
       </c>
       <c r="F19" s="7"/>
     </row>
     <row r="20" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F20" s="7"/>
     </row>
     <row r="21" spans="1:23" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>441</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>442</v>
       </c>
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D23" s="17" t="s">
         <v>435</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>436</v>
       </c>
       <c r="F23" s="7"/>
     </row>
     <row r="24" spans="1:23" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="D24" s="17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F24" s="7"/>
     </row>
     <row r="25" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:23" s="2" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="C26" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>481</v>
-      </c>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:23" s="2" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" s="2" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="E27" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F27" s="7"/>
     </row>
     <row r="28" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E28" s="17" t="s">
         <v>383</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>384</v>
       </c>
       <c r="F28" s="7"/>
     </row>
     <row r="29" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F29" s="7"/>
     </row>
     <row r="30" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -25040,19 +25079,19 @@
     </row>
     <row r="31" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="1"/>
@@ -25077,10 +25116,10 @@
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="7"/>
@@ -25106,10 +25145,10 @@
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="7"/>
@@ -25135,10 +25174,10 @@
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="7"/>
@@ -25164,10 +25203,10 @@
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="7"/>
@@ -25191,19 +25230,19 @@
     </row>
     <row r="36" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="E36" s="17" t="s">
         <v>407</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>408</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="1"/>
@@ -25228,10 +25267,10 @@
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="7"/>
@@ -25257,10 +25296,10 @@
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="7"/>
@@ -25286,10 +25325,10 @@
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="7"/>
@@ -25315,10 +25354,10 @@
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="7"/>
@@ -25342,19 +25381,19 @@
     </row>
     <row r="41" spans="1:23" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>306</v>
-      </c>
       <c r="E41" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="1"/>
@@ -25379,10 +25418,10 @@
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="7"/>
@@ -25408,10 +25447,10 @@
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="7"/>
@@ -25437,10 +25476,10 @@
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="7"/>
@@ -25466,10 +25505,10 @@
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="7"/>
@@ -25493,16 +25532,16 @@
     </row>
     <row r="46" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>411</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="7"/>
@@ -25526,16 +25565,16 @@
     </row>
     <row r="47" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>332</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="7"/>
@@ -25559,16 +25598,16 @@
     </row>
     <row r="48" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D48" s="17" t="s">
         <v>439</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>440</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="1"/>
@@ -25591,16 +25630,16 @@
     </row>
     <row r="49" spans="1:28" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B49" s="27" t="s">
+        <v>904</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="D49" s="17" t="s">
         <v>439</v>
-      </c>
-      <c r="B49" s="27" t="s">
-        <v>905</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>908</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>440</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="1"/>
@@ -25623,7 +25662,7 @@
     </row>
     <row r="50" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="15" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -25650,16 +25689,16 @@
     </row>
     <row r="51" spans="1:28" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B51" s="36" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="B51" s="36" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="E51" s="2"/>
       <c r="G51" s="1"/>
@@ -25683,21 +25722,21 @@
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
     </row>
-    <row r="52" spans="1:28" s="4" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:28" s="4" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E52" s="35" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="1"/>
@@ -25718,21 +25757,21 @@
       <c r="V52" s="2"/>
       <c r="W52" s="1"/>
     </row>
-    <row r="53" spans="1:28" s="4" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:28" s="4" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>434</v>
-      </c>
       <c r="E53" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="1"/>
@@ -25755,7 +25794,7 @@
     </row>
     <row r="54" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -25788,10 +25827,10 @@
         <v>13</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="1"/>
@@ -25814,16 +25853,16 @@
     </row>
     <row r="56" spans="1:28" s="4" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="7"/>
@@ -25847,16 +25886,16 @@
     </row>
     <row r="57" spans="1:28" s="4" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="7"/>
@@ -25880,16 +25919,16 @@
     </row>
     <row r="58" spans="1:28" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="7"/>
@@ -25911,21 +25950,21 @@
       <c r="V58" s="2"/>
       <c r="W58" s="1"/>
     </row>
-    <row r="59" spans="1:28" s="4" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:28" s="4" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A59" s="17" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="1"/>
@@ -25948,19 +25987,19 @@
     </row>
     <row r="60" spans="1:28" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>447</v>
-      </c>
       <c r="E60" s="17" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="1"/>
@@ -25983,19 +26022,19 @@
     </row>
     <row r="61" spans="1:28" s="4" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C61" s="2" t="s">
+      <c r="E61" s="17" t="s">
         <v>422</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="E61" s="17" t="s">
-        <v>423</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="1"/>
@@ -26018,22 +26057,22 @@
     </row>
     <row r="62" spans="1:28" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E62" s="2"/>
     </row>
     <row r="63" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -26063,13 +26102,13 @@
         <v>24</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="7"/>
@@ -26093,19 +26132,19 @@
     </row>
     <row r="65" spans="1:28" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>316</v>
-      </c>
       <c r="C65" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="1"/>
@@ -26130,11 +26169,11 @@
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="17" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="1"/>
@@ -26157,16 +26196,16 @@
     </row>
     <row r="67" spans="1:28" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E67" s="2"/>
       <c r="G67" s="1"/>
@@ -26192,19 +26231,19 @@
     </row>
     <row r="68" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="69" spans="1:28" ht="72" x14ac:dyDescent="0.3">
@@ -26212,97 +26251,97 @@
         <v>99</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>403</v>
-      </c>
       <c r="E69" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="70" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C70" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>415</v>
-      </c>
       <c r="E70" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="71" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A71" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
     </row>
     <row r="72" spans="1:28" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="E72" s="2"/>
     </row>
     <row r="73" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C73" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="E73" s="2"/>
     </row>
     <row r="74" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A74" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="C75" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="E75" s="2"/>
     </row>
     <row r="76" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -26311,58 +26350,58 @@
     </row>
     <row r="77" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>466</v>
       </c>
       <c r="E78" s="2"/>
     </row>
     <row r="79" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>388</v>
-      </c>
       <c r="E79" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="80" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A80" s="2"/>
       <c r="B80" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>393</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
@@ -26370,10 +26409,10 @@
     <row r="81" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A81" s="2"/>
       <c r="B81" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
@@ -26381,43 +26420,43 @@
     <row r="82" spans="1:28" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A82" s="2"/>
       <c r="B82" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>397</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
     </row>
     <row r="83" spans="1:28" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>1085</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:28" s="7" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="2"/>
@@ -26442,19 +26481,19 @@
     </row>
     <row r="85" spans="1:28" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E85" s="17" t="s">
         <v>345</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="E85" s="17" t="s">
-        <v>346</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="2"/>
@@ -26479,7 +26518,7 @@
     </row>
     <row r="86" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -26508,155 +26547,155 @@
     </row>
     <row r="87" spans="1:28" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" s="11" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="89" spans="1:28" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C89" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="E89" s="2"/>
     </row>
     <row r="90" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A90" s="2"/>
       <c r="C90" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="E90" s="2"/>
     </row>
     <row r="91" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A91" s="2"/>
       <c r="C91" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="E91" s="2"/>
     </row>
     <row r="92" spans="1:28" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A92" s="2"/>
       <c r="C92" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="E92" s="2"/>
     </row>
     <row r="93" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A93" s="2"/>
       <c r="C93" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="E93" s="2"/>
     </row>
     <row r="94" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E94" s="17" t="s">
         <v>458</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="E94" s="17" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="95" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2"/>
       <c r="C95" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="E95" s="2"/>
     </row>
     <row r="96" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2"/>
       <c r="C96" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="E96" s="2"/>
     </row>
     <row r="97" spans="1:5" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A97" s="2"/>
       <c r="C97" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="E97" s="2"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="2"/>
       <c r="C98" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="E98" s="2"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E100" s="2"/>
     </row>
@@ -26706,91 +26745,91 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B9" s="21"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B10" s="20"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B11" s="20"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B14" s="21"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B15" s="20"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B16" s="20"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B17" s="20"/>
     </row>
@@ -26819,7 +26858,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -26827,37 +26866,37 @@
     </row>
     <row r="22" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C23" s="25"/>
       <c r="D23" s="24"/>
     </row>
     <row r="24" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C24" s="25" t="s">
         <v>752</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>753</v>
-      </c>
       <c r="D24" s="24" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
@@ -26865,596 +26904,596 @@
         <v>83</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C25" s="25" t="s">
+        <v>753</v>
+      </c>
+      <c r="D25" s="24" t="s">
         <v>754</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C26" s="25"/>
       <c r="D26" s="24"/>
     </row>
     <row r="27" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C27" s="25" t="s">
         <v>746</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="C27" s="25" t="s">
+      <c r="D27" s="24" t="s">
         <v>747</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>798</v>
+      </c>
+      <c r="D28" s="27" t="s">
         <v>797</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>799</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>729</v>
+      </c>
+      <c r="D29" s="24" t="s">
         <v>728</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>730</v>
-      </c>
-      <c r="D29" s="24" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C30" s="25"/>
       <c r="D30" s="24"/>
     </row>
     <row r="31" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C31" s="29" t="s">
+        <v>887</v>
+      </c>
+      <c r="D31" s="24" t="s">
         <v>731</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C31" s="29" t="s">
-        <v>888</v>
-      </c>
-      <c r="D31" s="24" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>888</v>
+      </c>
+      <c r="D32" s="27" t="s">
         <v>812</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C32" s="25" t="s">
-        <v>889</v>
-      </c>
-      <c r="D32" s="27" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>758</v>
+      </c>
+      <c r="D33" s="24" t="s">
         <v>757</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C33" s="25" t="s">
-        <v>759</v>
-      </c>
-      <c r="D33" s="24" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>889</v>
+      </c>
+      <c r="D34" s="24" t="s">
         <v>741</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C34" s="25" t="s">
-        <v>890</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>867</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>868</v>
+      </c>
+      <c r="E37" s="27" t="s">
         <v>866</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>870</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>868</v>
-      </c>
-      <c r="D37" s="27" t="s">
-        <v>869</v>
-      </c>
-      <c r="E37" s="27" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>784</v>
+      </c>
+      <c r="D39" s="24" t="s">
         <v>783</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="C39" s="25" t="s">
-        <v>785</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="D40" s="24"/>
     </row>
     <row r="41" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D41" s="24" t="s">
         <v>786</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="C41" s="25" t="s">
-        <v>1077</v>
-      </c>
-      <c r="D41" s="24" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C42" s="25" t="s">
         <v>773</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>774</v>
-      </c>
       <c r="D42" s="24" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C44" s="25" t="s">
+        <v>750</v>
+      </c>
+      <c r="D44" s="24" t="s">
         <v>749</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>751</v>
-      </c>
-      <c r="D44" s="24" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>802</v>
+      </c>
+      <c r="D45" s="24" t="s">
         <v>788</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="C45" s="25" t="s">
-        <v>803</v>
-      </c>
-      <c r="D45" s="24" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>843</v>
+      </c>
+      <c r="D47" s="27" t="s">
         <v>841</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="C47" s="25" t="s">
-        <v>844</v>
-      </c>
-      <c r="D47" s="27" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>765</v>
+      </c>
+      <c r="D48" s="24" t="s">
         <v>764</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>766</v>
-      </c>
-      <c r="D48" s="24" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>768</v>
+      </c>
+      <c r="D49" s="24" t="s">
         <v>767</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>769</v>
-      </c>
-      <c r="D49" s="24" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>771</v>
+      </c>
+      <c r="D50" s="24" t="s">
         <v>770</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>772</v>
-      </c>
-      <c r="D50" s="24" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="27"/>
     </row>
     <row r="52" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B52" s="27" t="s">
         <v>828</v>
       </c>
-      <c r="B52" s="27" t="s">
-        <v>829</v>
-      </c>
       <c r="C52" s="25" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B54" s="27" t="s">
         <v>831</v>
       </c>
-      <c r="B54" s="27" t="s">
-        <v>832</v>
-      </c>
       <c r="C54" s="25" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D54" s="27" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>813</v>
+      </c>
+      <c r="C55" s="26" t="s">
         <v>716</v>
       </c>
-      <c r="B55" s="27" t="s">
-        <v>814</v>
-      </c>
-      <c r="C55" s="26" t="s">
+      <c r="D55" s="24" t="s">
         <v>717</v>
-      </c>
-      <c r="D55" s="24" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>825</v>
+      </c>
+      <c r="D57" s="27" t="s">
         <v>824</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="C57" s="25" t="s">
-        <v>826</v>
-      </c>
-      <c r="D57" s="27" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>873</v>
+      </c>
+      <c r="D59" s="27" t="s">
         <v>872</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="C59" s="25" t="s">
+      <c r="E59" s="27" t="s">
         <v>874</v>
-      </c>
-      <c r="D59" s="27" t="s">
-        <v>873</v>
-      </c>
-      <c r="E59" s="27" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>810</v>
+      </c>
+      <c r="D60" s="27" t="s">
         <v>808</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>811</v>
-      </c>
-      <c r="D60" s="27" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>705</v>
+      </c>
+      <c r="D61" s="24" t="s">
         <v>701</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>706</v>
-      </c>
-      <c r="D61" s="24" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C62" s="25"/>
       <c r="D62" s="27"/>
     </row>
     <row r="63" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>800</v>
+      </c>
+      <c r="D63" s="27" t="s">
         <v>794</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="C63" s="25" t="s">
-        <v>801</v>
-      </c>
-      <c r="D63" s="27" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>877</v>
+      </c>
+      <c r="D64" s="27" t="s">
         <v>876</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="E64" s="27" t="s">
         <v>879</v>
-      </c>
-      <c r="C64" s="25" t="s">
-        <v>878</v>
-      </c>
-      <c r="D64" s="27" t="s">
-        <v>877</v>
-      </c>
-      <c r="E64" s="27" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C65" s="25"/>
       <c r="D65" s="24"/>
     </row>
     <row r="66" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="C66" s="25" t="s">
+        <v>706</v>
+      </c>
+      <c r="D66" s="24" t="s">
         <v>698</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="C66" s="25" t="s">
-        <v>707</v>
-      </c>
-      <c r="D66" s="24" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>735</v>
+      </c>
+      <c r="D67" s="24" t="s">
         <v>733</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="C67" s="25" t="s">
-        <v>736</v>
-      </c>
-      <c r="D67" s="24" t="s">
+      <c r="E67" s="24" t="s">
         <v>734</v>
-      </c>
-      <c r="E67" s="24" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="C68" s="26" t="s">
+        <v>704</v>
+      </c>
+      <c r="D68" s="24" t="s">
         <v>703</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="C68" s="26" t="s">
-        <v>705</v>
-      </c>
-      <c r="D68" s="24" t="s">
-        <v>704</v>
-      </c>
       <c r="E68" s="24" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C69" s="25" t="s">
         <v>709</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="C69" s="25" t="s">
-        <v>710</v>
-      </c>
       <c r="D69" s="24" t="s">
+        <v>712</v>
+      </c>
+      <c r="E69" s="24" t="s">
         <v>713</v>
-      </c>
-      <c r="E69" s="24" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>801</v>
+      </c>
+      <c r="D70" s="27" t="s">
         <v>791</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="C70" s="25" t="s">
-        <v>802</v>
-      </c>
-      <c r="D70" s="27" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="28" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B71" s="27"/>
       <c r="C71" s="26"/>
@@ -27462,91 +27501,91 @@
     </row>
     <row r="72" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="C72" s="25" t="s">
+        <v>859</v>
+      </c>
+      <c r="D72" s="27" t="s">
         <v>854</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>864</v>
-      </c>
-      <c r="C72" s="25" t="s">
-        <v>860</v>
-      </c>
-      <c r="D72" s="27" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="C73" s="25" t="s">
+        <v>858</v>
+      </c>
+      <c r="D73" s="27" t="s">
         <v>856</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>865</v>
-      </c>
-      <c r="C73" s="25" t="s">
-        <v>859</v>
-      </c>
-      <c r="D73" s="27" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>857</v>
+      </c>
+      <c r="D74" s="27" t="s">
         <v>805</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>863</v>
-      </c>
-      <c r="C74" s="25" t="s">
-        <v>858</v>
-      </c>
-      <c r="D74" s="27" t="s">
+      <c r="E74" s="27" t="s">
         <v>806</v>
-      </c>
-      <c r="E74" s="27" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>860</v>
+      </c>
+      <c r="D75" s="24" t="s">
         <v>779</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>862</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>861</v>
-      </c>
-      <c r="D75" s="24" t="s">
+      <c r="E75" s="24" t="s">
         <v>780</v>
-      </c>
-      <c r="E75" s="24" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C76" s="25"/>
       <c r="D76" s="24"/>
     </row>
     <row r="77" spans="1:5" ht="216" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C77" s="2" t="s">
+      <c r="D77" s="24" t="s">
         <v>744</v>
-      </c>
-      <c r="D77" s="24" t="s">
-        <v>745</v>
       </c>
       <c r="E77" s="24"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C78" s="25"/>
       <c r="D78" s="27"/>
@@ -27554,75 +27593,75 @@
     </row>
     <row r="79" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="C79" s="25" t="s">
+        <v>850</v>
+      </c>
+      <c r="D79" s="27" t="s">
         <v>845</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>850</v>
-      </c>
-      <c r="C79" s="25" t="s">
-        <v>851</v>
-      </c>
-      <c r="D79" s="27" t="s">
-        <v>846</v>
-      </c>
       <c r="E79" s="27" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E80" s="27" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D82" s="27" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E82" s="27" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="28" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C83" s="25"/>
       <c r="D83" s="24"/>
@@ -27630,35 +27669,35 @@
     </row>
     <row r="84" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="C84" s="25" t="s">
+        <v>721</v>
+      </c>
+      <c r="D84" s="24" t="s">
         <v>720</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="C84" s="25" t="s">
-        <v>722</v>
-      </c>
-      <c r="D84" s="24" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="C85" s="25" t="s">
         <v>724</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="C85" s="25" t="s">
+      <c r="D85" s="24" t="s">
         <v>725</v>
-      </c>
-      <c r="D85" s="24" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -27666,16 +27705,16 @@
     </row>
     <row r="87" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="C87" s="25" t="s">
+        <v>738</v>
+      </c>
+      <c r="D87" s="24" t="s">
         <v>737</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="C87" s="25" t="s">
-        <v>739</v>
-      </c>
-      <c r="D87" s="24" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -27761,76 +27800,76 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B9" s="21"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -27865,7 +27904,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -27873,114 +27912,114 @@
     </row>
     <row r="22" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="D23" s="32" t="s">
         <v>985</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>987</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>989</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>988</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>990</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>994</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>996</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>992</v>
+      </c>
+      <c r="D26" s="32" t="s">
         <v>991</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>993</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="D28" s="32" t="s">
         <v>997</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>999</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>998</v>
       </c>
       <c r="E28" s="24"/>
     </row>
     <row r="29" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>999</v>
+      </c>
+      <c r="E29" s="32" t="s">
         <v>1001</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>1000</v>
-      </c>
-      <c r="E29" s="32" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="28" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -27988,18 +28027,18 @@
     </row>
     <row r="31" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>918</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>920</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="34" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -28007,143 +28046,143 @@
     </row>
     <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C34" s="25"/>
       <c r="D34" s="32"/>
     </row>
     <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>941</v>
+      </c>
+      <c r="D36" s="32" t="s">
         <v>940</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>942</v>
-      </c>
-      <c r="D36" s="32" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C37" s="25"/>
       <c r="D37" s="32"/>
     </row>
     <row r="38" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>977</v>
+      </c>
+      <c r="D38" s="32" t="s">
         <v>935</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C38" s="25" t="s">
-        <v>978</v>
-      </c>
-      <c r="D38" s="32" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="D39" s="32" t="s">
         <v>975</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>977</v>
-      </c>
-      <c r="D39" s="32" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D40" s="32" t="s">
         <v>1013</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C40" s="25" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D40" s="32" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D41" s="32"/>
     </row>
     <row r="42" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>938</v>
+      </c>
+      <c r="D42" s="32" t="s">
         <v>937</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>939</v>
-      </c>
-      <c r="D42" s="32" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C43" s="25"/>
       <c r="D43" s="32"/>
     </row>
     <row r="44" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="D44" s="32" t="s">
         <v>982</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>984</v>
-      </c>
-      <c r="D44" s="32" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C45" s="25"/>
       <c r="D45" s="32"/>
@@ -28151,88 +28190,88 @@
     </row>
     <row r="46" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D46" s="32" t="s">
         <v>1004</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D46" s="32" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="D47" s="32" t="s">
         <v>979</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>981</v>
-      </c>
-      <c r="D47" s="32" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="D48" s="32" t="s">
         <v>972</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>974</v>
-      </c>
-      <c r="D48" s="32" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D49" s="32" t="s">
         <v>1007</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>1009</v>
-      </c>
-      <c r="D49" s="32" t="s">
-        <v>1008</v>
       </c>
       <c r="E49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D50" s="32" t="s">
         <v>1010</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D50" s="32" t="s">
-        <v>1011</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>930</v>
+      </c>
+      <c r="D51" s="32" t="s">
         <v>929</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C51" s="25" t="s">
-        <v>931</v>
-      </c>
-      <c r="D51" s="32" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
@@ -29575,72 +29614,72 @@
     </row>
     <row r="21" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>1047</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1052</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>1049</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D23" s="32" t="s">
         <v>1053</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>1056</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>1058</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>1059</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1061</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">

--- a/4 четверть_13_JavaScript_sugarJS.xlsx
+++ b/4 четверть_13_JavaScript_sugarJS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F0778A-5208-4EE8-95EE-CF2997BF0BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F35D37-D427-4191-9ED9-5E9D52B741D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-12315" yWindow="-18960" windowWidth="28770" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sugarjs" sheetId="20" r:id="rId1"/>
@@ -21067,7 +21067,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>46</v>
       </c>
@@ -24434,7 +24434,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="112" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>205</v>
       </c>
@@ -24996,7 +24996,7 @@
       </c>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:23" s="2" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" s="2" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>341</v>
       </c>
@@ -25722,7 +25722,7 @@
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
     </row>
-    <row r="52" spans="1:28" s="4" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:28" s="4" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>40</v>
       </c>
@@ -25757,7 +25757,7 @@
       <c r="V52" s="2"/>
       <c r="W52" s="1"/>
     </row>
-    <row r="53" spans="1:28" s="4" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:28" s="4" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>121</v>
       </c>
@@ -25950,7 +25950,7 @@
       <c r="V58" s="2"/>
       <c r="W58" s="1"/>
     </row>
-    <row r="59" spans="1:28" s="4" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:28" s="4" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A59" s="17" t="s">
         <v>332</v>
       </c>

--- a/4 четверть_13_JavaScript_sugarJS.xlsx
+++ b/4 четверть_13_JavaScript_sugarJS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F35D37-D427-4191-9ED9-5E9D52B741D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4076AF5E-4899-4403-A5E0-02054CBCB8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sugarjs" sheetId="20" r:id="rId1"/>
@@ -301,11 +301,6 @@
 boolean</t>
   </si>
   <si>
-    <t>[1,2,3,4].add(5) [1, 2, 3, 4, 5]
-[1,2,3,4].add(8, 1) [1, 8, 2, 3, 4]
-[1,2,3,4].add([5,6,7]) [1, 2, 3, 4, 5, 6, 7]</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Adds item to the array and returns the result as a </t>
     </r>
@@ -3071,9 +3066,6 @@
 </t>
   </si>
   <si>
-    <t>create Array - add</t>
-  </si>
-  <si>
     <t xml:space="preserve">create Array
 </t>
   </si>
@@ -18322,13 +18314,6 @@
     </r>
   </si>
   <si>
-    <t>[1,2,3].exclude(3) [1, 2]
-['a','b','c'].exclude(/b/) ["a", "c"] //только для строк
-[{a:1},{b:2}].exclude(function(n) {
-  return n['a'] == 1;
-}); [{"b":2}]</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">[1,2,3].includes(2) true
 [1,2,3].includes(4) false
@@ -18382,6 +18367,24 @@
       </rPr>
       <t>none может искать объекты в массвах объектов</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">create Array - add
+</t>
+  </si>
+  <si>
+    <t>[1,2,3,4].add(5) [1, 2, 3, 4, 5]
+[1,2,3,4].add(8, 1) [1, 8, 2, 3, 4]
+[1,2,3,4].add([5,6,7]) [1, 2, 3, 4, 5, 6, 7]
+[{a:1},{b:2}].add({c:3}) [{a:1},{b:2},{c:3}]</t>
+  </si>
+  <si>
+    <t>[1,2,3].exclude(3) [1, 2]
+['a','b','c'].exclude(/b/) ["a", "c"] //только для строк
+[{a:1},{b:2}].exclude(function(item) {
+  return item['a'] == 1;
+}); [{"b":2}]
+[{a:1},{b:2}].exclude({b:2}) [{a:1}]</t>
   </si>
 </sst>
 </file>
@@ -18830,8 +18833,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7B23FFB3-A72F-409B-B670-C03B7A66220A}"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -19264,7 +19267,7 @@
     </row>
     <row r="4" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -19288,11 +19291,11 @@
     </row>
     <row r="5" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -19314,13 +19317,13 @@
     </row>
     <row r="6" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -19342,7 +19345,7 @@
     </row>
     <row r="7" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -19368,7 +19371,7 @@
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -20368,80 +20371,80 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C16" s="19" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -20479,7 +20482,7 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -20497,16 +20500,16 @@
     </row>
     <row r="20" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="1"/>
@@ -20521,7 +20524,7 @@
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="9"/>
@@ -20534,10 +20537,10 @@
         <v>0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>1</v>
@@ -20548,198 +20551,198 @@
     </row>
     <row r="23" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>1015</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>970</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="C24" s="25" t="s">
         <v>1020</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>970</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>1022</v>
-      </c>
       <c r="D24" s="32" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E24" s="32" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C25" s="25" t="s">
         <v>1066</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>1068</v>
-      </c>
       <c r="D25" s="32" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>966</v>
+      </c>
+      <c r="E26" s="32" t="s">
         <v>967</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>970</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>968</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="D31" s="32" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="E31" s="32" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="D33" s="14" t="s">
         <v>96</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>1070</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>908</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>670</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -20747,10 +20750,10 @@
     <row r="37" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -20758,10 +20761,10 @@
     <row r="38" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -20771,7 +20774,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="2"/>
@@ -20779,21 +20782,21 @@
     </row>
     <row r="41" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
@@ -20814,98 +20817,98 @@
     </row>
     <row r="44" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="D46" s="14" t="s">
         <v>85</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C47" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D47" s="14" t="s">
         <v>88</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C49" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D49" s="14" t="s">
         <v>132</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>133</v>
       </c>
       <c r="E49" s="14"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C50" s="10"/>
       <c r="D50" s="10"/>
@@ -20913,267 +20916,267 @@
     </row>
     <row r="51" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>202</v>
+        <v>1089</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D51" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D51" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D53" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C55" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C55" s="14" t="s">
-        <v>122</v>
-      </c>
       <c r="D55" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C56" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="D56" s="16" t="s">
         <v>185</v>
-      </c>
-      <c r="C56" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>186</v>
       </c>
       <c r="E56" s="14"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D57" s="10"/>
     </row>
     <row r="58" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" s="10" t="s">
         <v>20</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D60" s="14" t="s">
         <v>77</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D60" s="14" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D61" s="14" t="s">
         <v>92</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D63" s="14" t="s">
         <v>106</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C64" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D64" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="D64" s="14" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D65" s="14"/>
     </row>
     <row r="66" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D66" s="14" t="s">
         <v>135</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="D66" s="14" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D67" s="14" t="s">
         <v>159</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D68" s="14" t="s">
         <v>162</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D68" s="14" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="144" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C69" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D69" s="14" t="s">
         <v>164</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="2"/>
@@ -21184,7 +21187,7 @@
         <v>2</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>7</v>
@@ -21201,7 +21204,7 @@
         <v>6</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>9</v>
@@ -21213,71 +21216,71 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D73" s="10"/>
       <c r="E73" s="10"/>
     </row>
     <row r="74" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D74" s="10" t="s">
         <v>47</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D74" s="10" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D75" s="14" t="s">
         <v>90</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>1088</v>
-      </c>
-      <c r="D75" s="14" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C76" s="37" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D76" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C76" s="37" t="s">
-        <v>1086</v>
-      </c>
-      <c r="D76" s="14" t="s">
-        <v>145</v>
       </c>
       <c r="E76" s="14"/>
     </row>
     <row r="77" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D77" s="13" t="s">
         <v>65</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="D77" s="13" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -21286,385 +21289,385 @@
     </row>
     <row r="79" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C79" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D79" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D79" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="E79" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="D80" s="14" t="s">
         <v>96</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>908</v>
-      </c>
-      <c r="D80" s="14" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="D81" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>903</v>
-      </c>
-      <c r="D81" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="E81" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D82" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="C82" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D82" s="10" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="C83" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="C84" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="D84" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D85" s="14"/>
     </row>
     <row r="86" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C86" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D86" s="10" t="s">
         <v>31</v>
-      </c>
-      <c r="D86" s="10" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D87" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D87" s="10" t="s">
+      <c r="E87" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C88" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C88" s="14" t="s">
-        <v>157</v>
-      </c>
       <c r="D88" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E88" s="14"/>
     </row>
     <row r="89" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D89" s="14" t="s">
         <v>152</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D89" s="14" t="s">
-        <v>153</v>
       </c>
       <c r="E89" s="1"/>
     </row>
     <row r="90" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E90" s="13" t="s">
         <v>67</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D90" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E90" s="13" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C91" s="2" t="s">
+      <c r="D91" s="13" t="s">
         <v>72</v>
-      </c>
-      <c r="D91" s="13" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D93" s="14"/>
     </row>
     <row r="94" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D94" s="14" t="s">
         <v>80</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D94" s="14" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C95" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="D95" s="14" t="s">
         <v>138</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C95" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="D95" s="14" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="E96" s="1"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C99" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D99" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="14" t="s">
-        <v>103</v>
-      </c>
       <c r="E99" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C100" s="2" t="s">
+      <c r="D100" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D100" s="14" t="s">
-        <v>101</v>
-      </c>
       <c r="E100" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="C101" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="D101" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E101" s="14" t="s">
         <v>114</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="C101" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D101" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="E101" s="14" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="C102" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D102" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="C102" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="D102" s="14" t="s">
-        <v>119</v>
-      </c>
       <c r="E102" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D103" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C103" s="2" t="s">
+      <c r="E103" s="10" t="s">
         <v>26</v>
-      </c>
-      <c r="D103" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E103" s="10" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D104" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D104" s="10" t="s">
-        <v>35</v>
-      </c>
       <c r="E104" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D105" s="14" t="s">
         <v>141</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D105" s="14" t="s">
-        <v>142</v>
       </c>
       <c r="E105" s="14"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C106" s="10"/>
       <c r="D106" s="2"/>
@@ -21672,31 +21675,31 @@
     </row>
     <row r="107" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D107" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E107" s="14"/>
     </row>
     <row r="108" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C108" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D108" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C108" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="D108" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="E108" s="2"/>
     </row>
@@ -21900,88 +21903,88 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B11" s="1"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
@@ -22009,7 +22012,7 @@
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -22017,21 +22020,21 @@
     </row>
     <row r="23" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="24" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -22055,16 +22058,16 @@
     </row>
     <row r="25" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>604</v>
-      </c>
       <c r="C25" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E25" s="2"/>
       <c r="G25" s="1"/>
@@ -22085,19 +22088,19 @@
     </row>
     <row r="26" spans="1:23" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="2"/>
@@ -22117,16 +22120,16 @@
     </row>
     <row r="27" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E27" s="2"/>
       <c r="G27" s="1"/>
@@ -22148,13 +22151,13 @@
     <row r="28" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E28" s="2"/>
       <c r="G28" s="1"/>
@@ -22176,13 +22179,13 @@
     <row r="29" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E29" s="2"/>
       <c r="G29" s="1"/>
@@ -22204,13 +22207,13 @@
     <row r="30" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E30" s="2"/>
       <c r="G30" s="1"/>
@@ -22232,13 +22235,13 @@
     <row r="31" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E31" s="2"/>
       <c r="G31" s="1"/>
@@ -22260,13 +22263,13 @@
     <row r="32" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E32" s="2"/>
       <c r="G32" s="1"/>
@@ -22288,13 +22291,13 @@
     <row r="33" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E33" s="2"/>
       <c r="G33" s="1"/>
@@ -22315,19 +22318,19 @@
     </row>
     <row r="34" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>510</v>
-      </c>
       <c r="E34" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="2"/>
@@ -22347,12 +22350,12 @@
     </row>
     <row r="35" spans="1:23" s="7" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="22" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E35" s="4"/>
       <c r="G35" s="1"/>
@@ -22373,7 +22376,7 @@
     </row>
     <row r="36" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -22397,12 +22400,12 @@
     </row>
     <row r="37" spans="1:23" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="22" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E37" s="4"/>
       <c r="G37" s="1"/>
@@ -22423,12 +22426,12 @@
     </row>
     <row r="38" spans="1:23" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="22" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E38" s="4"/>
       <c r="G38" s="1"/>
@@ -22449,12 +22452,12 @@
     </row>
     <row r="39" spans="1:23" s="7" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="22" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E39" s="4"/>
       <c r="G39" s="1"/>
@@ -22475,12 +22478,12 @@
     </row>
     <row r="40" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="22" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E40" s="4"/>
       <c r="G40" s="1"/>
@@ -22501,12 +22504,12 @@
     </row>
     <row r="41" spans="1:23" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="22" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E41" s="4"/>
       <c r="G41" s="1"/>
@@ -22527,12 +22530,12 @@
     </row>
     <row r="42" spans="1:23" s="7" customFormat="1" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="22" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E42" s="4"/>
       <c r="G42" s="1"/>
@@ -22553,7 +22556,7 @@
     </row>
     <row r="43" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -22577,16 +22580,16 @@
     </row>
     <row r="44" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>277</v>
-      </c>
       <c r="D44" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E44" s="2"/>
       <c r="G44" s="1"/>
@@ -22607,16 +22610,16 @@
     </row>
     <row r="45" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>280</v>
-      </c>
       <c r="C45" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E45" s="2"/>
       <c r="G45" s="1"/>
@@ -22637,16 +22640,16 @@
     </row>
     <row r="46" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>493</v>
-      </c>
       <c r="C46" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E46" s="2"/>
       <c r="G46" s="1"/>
@@ -22667,16 +22670,16 @@
     </row>
     <row r="47" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>497</v>
-      </c>
       <c r="C47" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E47" s="2"/>
       <c r="G47" s="1"/>
@@ -22697,16 +22700,16 @@
     </row>
     <row r="48" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>608</v>
-      </c>
       <c r="C48" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E48" s="2"/>
       <c r="G48" s="1"/>
@@ -22727,7 +22730,7 @@
     </row>
     <row r="49" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -22751,19 +22754,19 @@
     </row>
     <row r="50" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="D50" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="2"/>
@@ -22783,19 +22786,19 @@
     </row>
     <row r="51" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>952</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>625</v>
-      </c>
       <c r="D51" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>624</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>626</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="2"/>
@@ -22815,19 +22818,19 @@
     </row>
     <row r="52" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>953</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>629</v>
-      </c>
       <c r="D52" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>628</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>630</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="2"/>
@@ -22847,19 +22850,19 @@
     </row>
     <row r="53" spans="1:23" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>635</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="2"/>
@@ -22879,19 +22882,19 @@
     </row>
     <row r="54" spans="1:23" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>640</v>
-      </c>
       <c r="D54" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>637</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>639</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="2"/>
@@ -22911,7 +22914,7 @@
     </row>
     <row r="55" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="15" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -22935,19 +22938,19 @@
     </row>
     <row r="56" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>501</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="2"/>
@@ -22967,16 +22970,16 @@
     </row>
     <row r="57" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>506</v>
-      </c>
       <c r="C57" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E57" s="2"/>
       <c r="G57" s="1"/>
@@ -22997,16 +23000,16 @@
     </row>
     <row r="58" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>583</v>
-      </c>
       <c r="C58" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="7"/>
@@ -23030,37 +23033,37 @@
     </row>
     <row r="59" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>587</v>
-      </c>
       <c r="C59" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>612</v>
-      </c>
       <c r="C60" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -23084,19 +23087,19 @@
     </row>
     <row r="62" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>681</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="2"/>
@@ -23116,10 +23119,10 @@
     </row>
     <row r="63" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -23142,10 +23145,10 @@
     </row>
     <row r="64" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -23168,10 +23171,10 @@
     </row>
     <row r="65" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -23194,10 +23197,10 @@
     </row>
     <row r="66" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
@@ -23220,13 +23223,13 @@
     </row>
     <row r="67" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
@@ -23248,10 +23251,10 @@
     </row>
     <row r="68" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
@@ -23274,10 +23277,10 @@
     </row>
     <row r="69" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -23300,13 +23303,13 @@
     </row>
     <row r="70" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
@@ -23328,16 +23331,16 @@
     </row>
     <row r="71" spans="1:23" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="E71" s="2"/>
       <c r="G71" s="1"/>
@@ -23358,16 +23361,16 @@
     </row>
     <row r="72" spans="1:23" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>601</v>
-      </c>
       <c r="D72" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E72" s="2"/>
       <c r="G72" s="1"/>
@@ -23388,19 +23391,19 @@
     </row>
     <row r="73" spans="1:23" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C73" s="27" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="2"/>
@@ -23420,16 +23423,16 @@
     </row>
     <row r="74" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B74" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>593</v>
-      </c>
       <c r="C74" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E74" s="2"/>
       <c r="G74" s="1"/>
@@ -23450,16 +23453,16 @@
     </row>
     <row r="75" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>597</v>
-      </c>
       <c r="C75" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E75" s="2"/>
       <c r="G75" s="1"/>
@@ -23480,7 +23483,7 @@
     </row>
     <row r="76" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="15" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -23504,16 +23507,16 @@
     </row>
     <row r="77" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E77" s="2"/>
       <c r="G77" s="1"/>
@@ -23534,7 +23537,7 @@
     </row>
     <row r="78" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="15" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -23558,16 +23561,16 @@
     </row>
     <row r="79" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>490</v>
-      </c>
       <c r="D79" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E79" s="2"/>
       <c r="G79" s="1"/>
@@ -23588,21 +23591,21 @@
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="81" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>515</v>
-      </c>
       <c r="C81" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E81" s="2"/>
       <c r="G81" s="1"/>
@@ -23623,7 +23626,7 @@
     </row>
     <row r="82" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="15" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -23647,16 +23650,16 @@
     </row>
     <row r="83" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>519</v>
-      </c>
       <c r="C83" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="7"/>
@@ -23680,21 +23683,21 @@
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A84" s="11" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="85" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>523</v>
-      </c>
       <c r="C85" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="7"/>
@@ -23718,16 +23721,16 @@
     </row>
     <row r="86" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D86" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>527</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="7"/>
@@ -23751,7 +23754,7 @@
     </row>
     <row r="87" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -23778,16 +23781,16 @@
     </row>
     <row r="88" spans="1:23" s="4" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>530</v>
-      </c>
       <c r="C88" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="7"/>
@@ -23811,16 +23814,16 @@
     </row>
     <row r="89" spans="1:23" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="C89" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="7"/>
@@ -23844,16 +23847,16 @@
     </row>
     <row r="90" spans="1:23" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>538</v>
-      </c>
       <c r="C90" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="7"/>
@@ -23877,19 +23880,19 @@
     </row>
     <row r="91" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>542</v>
-      </c>
       <c r="C91" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="D91" s="2" t="s">
-        <v>541</v>
-      </c>
       <c r="E91" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F91" s="7"/>
       <c r="G91" s="1"/>
@@ -23912,19 +23915,19 @@
     </row>
     <row r="92" spans="1:23" s="4" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="C92" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E92" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>547</v>
       </c>
       <c r="F92" s="7"/>
       <c r="G92" s="1"/>
@@ -23947,16 +23950,16 @@
     </row>
     <row r="93" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>550</v>
-      </c>
       <c r="C93" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="7"/>
@@ -23980,16 +23983,16 @@
     </row>
     <row r="94" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>565</v>
-      </c>
       <c r="C94" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="7"/>
@@ -24013,19 +24016,19 @@
     </row>
     <row r="95" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>561</v>
-      </c>
       <c r="C95" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D95" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>562</v>
       </c>
       <c r="F95" s="7"/>
       <c r="G95" s="1"/>
@@ -24048,19 +24051,19 @@
     </row>
     <row r="96" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="C96" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>570</v>
       </c>
       <c r="F96" s="7"/>
       <c r="G96" s="1"/>
@@ -24083,19 +24086,19 @@
     </row>
     <row r="97" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="C97" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>555</v>
       </c>
       <c r="F97" s="7"/>
       <c r="G97" s="1"/>
@@ -24118,16 +24121,16 @@
     </row>
     <row r="98" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="C98" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="7"/>
@@ -24151,16 +24154,16 @@
     </row>
     <row r="99" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>573</v>
-      </c>
       <c r="C99" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="7"/>
@@ -24184,7 +24187,7 @@
     </row>
     <row r="100" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="15" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -24211,16 +24214,16 @@
     </row>
     <row r="101" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="C101" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="7"/>
@@ -24244,16 +24247,16 @@
     </row>
     <row r="102" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>579</v>
-      </c>
       <c r="C102" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="7"/>
@@ -24277,63 +24280,63 @@
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A103" s="15" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
     </row>
     <row r="104" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>616</v>
-      </c>
       <c r="C104" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E104" s="2"/>
     </row>
     <row r="105" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A106" s="15" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="107" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B107" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="C107" s="2" t="s">
-        <v>670</v>
-      </c>
       <c r="D107" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G107" s="1"/>
       <c r="H107" s="2"/>
@@ -24354,10 +24357,10 @@
     <row r="108" spans="1:23" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A108" s="2"/>
       <c r="B108" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
@@ -24380,10 +24383,10 @@
     <row r="109" spans="1:23" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A109" s="2"/>
       <c r="B109" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
@@ -24406,10 +24409,10 @@
     <row r="110" spans="1:23" s="7" customFormat="1" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A110" s="2"/>
       <c r="B110" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
@@ -24431,22 +24434,22 @@
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A111" s="11" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="112" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G112" s="1"/>
       <c r="H112" s="2"/>
@@ -24466,19 +24469,19 @@
     </row>
     <row r="113" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="D113" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G113" s="1"/>
       <c r="H113" s="2"/>
@@ -24498,19 +24501,19 @@
     </row>
     <row r="114" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="D114" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G114" s="1"/>
       <c r="H114" s="2"/>
@@ -24530,19 +24533,19 @@
     </row>
     <row r="115" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="D115" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G115" s="1"/>
       <c r="H115" s="2"/>
@@ -24562,19 +24565,19 @@
     </row>
     <row r="116" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="D116" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="E116" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="2"/>
@@ -24594,19 +24597,19 @@
     </row>
     <row r="117" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>250</v>
-      </c>
       <c r="C117" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G117" s="1"/>
       <c r="H117" s="2"/>
@@ -24626,75 +24629,75 @@
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A118" s="15" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="119" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="2" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="D119" s="32" t="s">
+        <v>941</v>
+      </c>
+      <c r="E119" s="32" t="s">
         <v>943</v>
-      </c>
-      <c r="E119" s="32" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="120" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="C120" s="25" t="s">
         <v>946</v>
       </c>
-      <c r="C120" s="25" t="s">
-        <v>948</v>
-      </c>
       <c r="D120" s="32" t="s">
+        <v>945</v>
+      </c>
+      <c r="E120" s="32" t="s">
         <v>947</v>
-      </c>
-      <c r="E120" s="32" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="121" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A121" s="25" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D121" s="32" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="122" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="C122" s="33" t="s">
         <v>955</v>
       </c>
-      <c r="C122" s="33" t="s">
-        <v>957</v>
-      </c>
       <c r="D122" s="32" t="s">
+        <v>954</v>
+      </c>
+      <c r="E122" s="32" t="s">
         <v>956</v>
-      </c>
-      <c r="E122" s="32" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="123" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="C123" s="25" t="s">
         <v>959</v>
       </c>
-      <c r="C123" s="25" t="s">
-        <v>961</v>
-      </c>
       <c r="D123" s="32" t="s">
+        <v>958</v>
+      </c>
+      <c r="E123" s="32" t="s">
         <v>960</v>
-      </c>
-      <c r="E123" s="32" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.3">
@@ -24798,74 +24801,74 @@
   <sheetData>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B5" s="20"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B6" s="21"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B9" s="20"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B10" s="20"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B13" s="21"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B14" s="20"/>
     </row>
@@ -24894,7 +24897,7 @@
     </row>
     <row r="18" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -24902,157 +24905,157 @@
     </row>
     <row r="19" spans="1:23" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>311</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F19" s="7"/>
     </row>
     <row r="20" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F20" s="7"/>
     </row>
     <row r="21" spans="1:23" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>442</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>436</v>
-      </c>
       <c r="C23" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F23" s="7"/>
     </row>
     <row r="24" spans="1:23" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F24" s="7"/>
     </row>
     <row r="25" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:23" s="2" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="C26" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:23" s="2" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F27" s="7"/>
     </row>
     <row r="28" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="D28" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F28" s="7"/>
     </row>
     <row r="29" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F29" s="7"/>
     </row>
     <row r="30" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -25079,19 +25082,19 @@
     </row>
     <row r="31" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="1"/>
@@ -25116,10 +25119,10 @@
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="7"/>
@@ -25145,10 +25148,10 @@
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="7"/>
@@ -25174,10 +25177,10 @@
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="7"/>
@@ -25203,10 +25206,10 @@
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="7"/>
@@ -25230,19 +25233,19 @@
     </row>
     <row r="36" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>406</v>
-      </c>
       <c r="D36" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E36" s="17" t="s">
         <v>405</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>407</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="1"/>
@@ -25267,10 +25270,10 @@
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="7"/>
@@ -25296,10 +25299,10 @@
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="7"/>
@@ -25325,10 +25328,10 @@
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="7"/>
@@ -25354,10 +25357,10 @@
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="7"/>
@@ -25381,19 +25384,19 @@
     </row>
     <row r="41" spans="1:23" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="1"/>
@@ -25418,10 +25421,10 @@
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="7"/>
@@ -25447,10 +25450,10 @@
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="7"/>
@@ -25476,10 +25479,10 @@
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="7"/>
@@ -25505,10 +25508,10 @@
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="7"/>
@@ -25532,16 +25535,16 @@
     </row>
     <row r="46" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="7"/>
@@ -25565,16 +25568,16 @@
     </row>
     <row r="47" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="7"/>
@@ -25598,16 +25601,16 @@
     </row>
     <row r="48" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="1"/>
@@ -25630,16 +25633,16 @@
     </row>
     <row r="49" spans="1:28" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="1"/>
@@ -25662,7 +25665,7 @@
     </row>
     <row r="50" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="15" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -25689,16 +25692,16 @@
     </row>
     <row r="51" spans="1:28" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B51" s="36" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="B51" s="36" t="s">
-        <v>1079</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>431</v>
       </c>
       <c r="E51" s="2"/>
       <c r="G51" s="1"/>
@@ -25724,19 +25727,19 @@
     </row>
     <row r="52" spans="1:28" s="4" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>338</v>
-      </c>
       <c r="E52" s="35" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="1"/>
@@ -25759,19 +25762,19 @@
     </row>
     <row r="53" spans="1:28" s="4" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="1"/>
@@ -25794,7 +25797,7 @@
     </row>
     <row r="54" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -25821,16 +25824,16 @@
     </row>
     <row r="55" spans="1:28" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="1"/>
@@ -25853,16 +25856,16 @@
     </row>
     <row r="56" spans="1:28" s="4" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>372</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="7"/>
@@ -25886,16 +25889,16 @@
     </row>
     <row r="57" spans="1:28" s="4" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="7"/>
@@ -25919,16 +25922,16 @@
     </row>
     <row r="58" spans="1:28" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="7"/>
@@ -25952,19 +25955,19 @@
     </row>
     <row r="59" spans="1:28" s="4" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A59" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C59" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="D59" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="E59" s="17" t="s">
         <v>332</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C59" s="17" t="s">
-        <v>335</v>
-      </c>
-      <c r="D59" s="17" t="s">
-        <v>337</v>
-      </c>
-      <c r="E59" s="17" t="s">
-        <v>334</v>
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="1"/>
@@ -25987,19 +25990,19 @@
     </row>
     <row r="60" spans="1:28" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>446</v>
-      </c>
       <c r="E60" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="1"/>
@@ -26022,19 +26025,19 @@
     </row>
     <row r="61" spans="1:28" s="4" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="1"/>
@@ -26057,22 +26060,22 @@
     </row>
     <row r="62" spans="1:28" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E62" s="2"/>
     </row>
     <row r="63" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -26099,16 +26102,16 @@
     </row>
     <row r="64" spans="1:28" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="7"/>
@@ -26132,19 +26135,19 @@
     </row>
     <row r="65" spans="1:28" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="1"/>
@@ -26169,11 +26172,11 @@
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="1"/>
@@ -26196,16 +26199,16 @@
     </row>
     <row r="67" spans="1:28" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E67" s="2"/>
       <c r="G67" s="1"/>
@@ -26231,117 +26234,117 @@
     </row>
     <row r="68" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="69" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E69" s="17" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="70" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="71" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A71" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
     </row>
     <row r="72" spans="1:28" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>359</v>
-      </c>
       <c r="D72" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E72" s="2"/>
     </row>
     <row r="73" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>449</v>
       </c>
       <c r="E73" s="2"/>
     </row>
     <row r="74" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A74" s="15" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="E75" s="2"/>
     </row>
     <row r="76" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -26350,58 +26353,58 @@
     </row>
     <row r="77" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="C78" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E78" s="2"/>
     </row>
     <row r="79" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>388</v>
-      </c>
       <c r="D79" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="80" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A80" s="2"/>
       <c r="B80" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
@@ -26409,10 +26412,10 @@
     <row r="81" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A81" s="2"/>
       <c r="B81" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
@@ -26420,43 +26423,43 @@
     <row r="82" spans="1:28" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A82" s="2"/>
       <c r="B82" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
     </row>
     <row r="83" spans="1:28" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="84" spans="1:28" s="7" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="2"/>
@@ -26481,19 +26484,19 @@
     </row>
     <row r="85" spans="1:28" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>346</v>
-      </c>
       <c r="D85" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="2"/>
@@ -26518,7 +26521,7 @@
     </row>
     <row r="86" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -26547,155 +26550,155 @@
     </row>
     <row r="87" spans="1:28" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D87" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>454</v>
-      </c>
       <c r="E87" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" s="11" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="89" spans="1:28" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E89" s="2"/>
     </row>
     <row r="90" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A90" s="2"/>
       <c r="C90" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E90" s="2"/>
     </row>
     <row r="91" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A91" s="2"/>
       <c r="C91" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E91" s="2"/>
     </row>
     <row r="92" spans="1:28" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A92" s="2"/>
       <c r="C92" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E92" s="2"/>
     </row>
     <row r="93" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A93" s="2"/>
       <c r="C93" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E93" s="2"/>
     </row>
     <row r="94" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>459</v>
-      </c>
       <c r="D94" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E94" s="17" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="95" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2"/>
       <c r="C95" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E95" s="2"/>
     </row>
     <row r="96" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2"/>
       <c r="C96" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E96" s="2"/>
     </row>
     <row r="97" spans="1:5" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A97" s="2"/>
       <c r="C97" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E97" s="2"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="2"/>
       <c r="C98" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E98" s="2"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="11" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E100" s="2"/>
     </row>
@@ -26745,91 +26748,91 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B9" s="21"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B10" s="20"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B11" s="20"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B14" s="21"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B15" s="20"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B16" s="20"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B17" s="20"/>
     </row>
@@ -26858,7 +26861,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -26866,634 +26869,634 @@
     </row>
     <row r="22" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C23" s="25"/>
       <c r="D23" s="24"/>
     </row>
     <row r="24" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C26" s="25"/>
       <c r="D26" s="24"/>
     </row>
     <row r="27" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>744</v>
+      </c>
+      <c r="D27" s="24" t="s">
         <v>745</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="C27" s="25" t="s">
-        <v>746</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C28" s="25" t="s">
         <v>796</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>798</v>
-      </c>
       <c r="D28" s="27" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C29" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>729</v>
-      </c>
       <c r="D29" s="24" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C30" s="25"/>
       <c r="D30" s="24"/>
     </row>
     <row r="31" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C33" s="25" t="s">
         <v>756</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C33" s="25" t="s">
-        <v>758</v>
-      </c>
       <c r="D33" s="24" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="C37" s="25" t="s">
         <v>865</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>869</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>867</v>
-      </c>
       <c r="D37" s="27" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C39" s="25" t="s">
         <v>782</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="C39" s="25" t="s">
-        <v>784</v>
-      </c>
       <c r="D39" s="24" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="D40" s="24"/>
     </row>
     <row r="41" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C42" s="25" t="s">
+        <v>771</v>
+      </c>
+      <c r="D42" s="24" t="s">
         <v>773</v>
-      </c>
-      <c r="D42" s="24" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C43" s="25" t="s">
+        <v>775</v>
+      </c>
+      <c r="D43" s="24" t="s">
         <v>774</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="C43" s="25" t="s">
-        <v>777</v>
-      </c>
-      <c r="D43" s="24" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C44" s="25" t="s">
         <v>748</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>750</v>
-      </c>
       <c r="D44" s="24" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="C48" s="25" t="s">
         <v>763</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>765</v>
-      </c>
       <c r="D48" s="24" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="C49" s="25" t="s">
         <v>766</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>768</v>
-      </c>
       <c r="D49" s="24" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="C50" s="25" t="s">
         <v>769</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>771</v>
-      </c>
       <c r="D50" s="24" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="27"/>
     </row>
     <row r="52" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B53" s="27" t="s">
         <v>829</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="C53" s="25" t="s">
         <v>831</v>
       </c>
-      <c r="C53" s="25" t="s">
-        <v>833</v>
-      </c>
       <c r="D53" s="27" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B54" s="27" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C54" s="25" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="D54" s="27" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>811</v>
+      </c>
+      <c r="C55" s="26" t="s">
+        <v>714</v>
+      </c>
+      <c r="D55" s="24" t="s">
         <v>715</v>
-      </c>
-      <c r="B55" s="27" t="s">
-        <v>813</v>
-      </c>
-      <c r="C55" s="26" t="s">
-        <v>716</v>
-      </c>
-      <c r="D55" s="24" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C57" s="25" t="s">
         <v>823</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="C57" s="25" t="s">
-        <v>825</v>
-      </c>
       <c r="D57" s="27" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C59" s="25" t="s">
         <v>871</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="C59" s="25" t="s">
-        <v>873</v>
-      </c>
       <c r="D59" s="27" t="s">
+        <v>870</v>
+      </c>
+      <c r="E59" s="27" t="s">
         <v>872</v>
-      </c>
-      <c r="E59" s="27" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>809</v>
-      </c>
       <c r="C60" s="25" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C61" s="25" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D61" s="24" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C62" s="25"/>
       <c r="D62" s="27"/>
     </row>
     <row r="63" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C63" s="25" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D63" s="27" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="C64" s="25" t="s">
         <v>875</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="C64" s="25" t="s">
+      <c r="D64" s="27" t="s">
+        <v>874</v>
+      </c>
+      <c r="E64" s="27" t="s">
         <v>877</v>
-      </c>
-      <c r="D64" s="27" t="s">
-        <v>876</v>
-      </c>
-      <c r="E64" s="27" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C65" s="25"/>
       <c r="D65" s="24"/>
     </row>
     <row r="66" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C66" s="25" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D66" s="24" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>733</v>
+      </c>
+      <c r="D67" s="24" t="s">
+        <v>731</v>
+      </c>
+      <c r="E67" s="24" t="s">
         <v>732</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="C67" s="25" t="s">
-        <v>735</v>
-      </c>
-      <c r="D67" s="24" t="s">
-        <v>733</v>
-      </c>
-      <c r="E67" s="24" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C68" s="26" t="s">
         <v>702</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="C68" s="26" t="s">
-        <v>704</v>
-      </c>
       <c r="D68" s="24" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E68" s="24" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="C69" s="25" t="s">
+        <v>707</v>
+      </c>
+      <c r="D69" s="24" t="s">
         <v>710</v>
       </c>
-      <c r="C69" s="25" t="s">
-        <v>709</v>
-      </c>
-      <c r="D69" s="24" t="s">
-        <v>712</v>
-      </c>
       <c r="E69" s="24" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>792</v>
-      </c>
       <c r="C70" s="25" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D70" s="27" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="28" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B71" s="27"/>
       <c r="C71" s="26"/>
@@ -27501,91 +27504,91 @@
     </row>
     <row r="72" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C72" s="25" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>855</v>
+      </c>
+      <c r="D74" s="27" t="s">
+        <v>803</v>
+      </c>
+      <c r="E74" s="27" t="s">
         <v>804</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>862</v>
-      </c>
-      <c r="C74" s="25" t="s">
-        <v>857</v>
-      </c>
-      <c r="D74" s="27" t="s">
-        <v>805</v>
-      </c>
-      <c r="E74" s="27" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>858</v>
+      </c>
+      <c r="D75" s="24" t="s">
+        <v>777</v>
+      </c>
+      <c r="E75" s="24" t="s">
         <v>778</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>860</v>
-      </c>
-      <c r="D75" s="24" t="s">
-        <v>779</v>
-      </c>
-      <c r="E75" s="24" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C76" s="25"/>
       <c r="D76" s="24"/>
     </row>
     <row r="77" spans="1:5" ht="216" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="D77" s="24" t="s">
         <v>742</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="D77" s="24" t="s">
-        <v>744</v>
       </c>
       <c r="E77" s="24"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C78" s="25"/>
       <c r="D78" s="27"/>
@@ -27593,75 +27596,75 @@
     </row>
     <row r="79" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C79" s="25" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="E79" s="27" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E80" s="27" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="D82" s="27" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="E82" s="27" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="28" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C83" s="25"/>
       <c r="D83" s="24"/>
@@ -27669,35 +27672,35 @@
     </row>
     <row r="84" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="C84" s="25" t="s">
         <v>719</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="C84" s="25" t="s">
-        <v>721</v>
-      </c>
       <c r="D84" s="24" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="C85" s="25" t="s">
+        <v>722</v>
+      </c>
+      <c r="D85" s="24" t="s">
         <v>723</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="C85" s="25" t="s">
-        <v>724</v>
-      </c>
-      <c r="D85" s="24" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -27705,16 +27708,16 @@
     </row>
     <row r="87" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="C87" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="C87" s="25" t="s">
-        <v>738</v>
-      </c>
       <c r="D87" s="24" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -27800,76 +27803,76 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B9" s="21"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -27904,7 +27907,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -27912,114 +27915,114 @@
     </row>
     <row r="22" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>986</v>
-      </c>
       <c r="D23" s="32" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C24" s="25" t="s">
         <v>987</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>989</v>
-      </c>
       <c r="D24" s="32" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>993</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>995</v>
-      </c>
       <c r="D25" s="32" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C26" s="25" t="s">
         <v>990</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>992</v>
-      </c>
       <c r="D26" s="32" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>996</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>998</v>
-      </c>
       <c r="D28" s="32" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="E28" s="24"/>
     </row>
     <row r="29" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C29" s="25" t="s">
         <v>1000</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>1002</v>
-      </c>
       <c r="D29" s="32" t="s">
+        <v>997</v>
+      </c>
+      <c r="E29" s="32" t="s">
         <v>999</v>
-      </c>
-      <c r="E29" s="32" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="28" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -28027,18 +28030,18 @@
     </row>
     <row r="31" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="C31" s="32" t="s">
         <v>917</v>
       </c>
-      <c r="C31" s="32" t="s">
-        <v>919</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="34" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -28046,143 +28049,143 @@
     </row>
     <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C34" s="25"/>
       <c r="D34" s="32"/>
     </row>
     <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C36" s="25" t="s">
         <v>939</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>941</v>
-      </c>
       <c r="D36" s="32" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C37" s="25"/>
       <c r="D37" s="32"/>
     </row>
     <row r="38" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="D38" s="32" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>976</v>
-      </c>
       <c r="D39" s="32" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C40" s="25" t="s">
         <v>1012</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C40" s="25" t="s">
-        <v>1014</v>
-      </c>
       <c r="D40" s="32" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D41" s="32"/>
     </row>
     <row r="42" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C42" s="25" t="s">
         <v>936</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>938</v>
-      </c>
       <c r="D42" s="32" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C43" s="25"/>
       <c r="D43" s="32"/>
     </row>
     <row r="44" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>983</v>
-      </c>
       <c r="D44" s="32" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C45" s="25"/>
       <c r="D45" s="32"/>
@@ -28190,88 +28193,88 @@
     </row>
     <row r="46" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>1003</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>1005</v>
-      </c>
       <c r="D46" s="32" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>978</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>980</v>
-      </c>
       <c r="D47" s="32" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>971</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>973</v>
-      </c>
       <c r="D48" s="32" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C49" s="25" t="s">
         <v>1006</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>1008</v>
-      </c>
       <c r="D49" s="32" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C50" s="25" t="s">
         <v>1009</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>1011</v>
-      </c>
       <c r="D50" s="32" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C51" s="25" t="s">
         <v>928</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C51" s="25" t="s">
-        <v>930</v>
-      </c>
       <c r="D51" s="32" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
@@ -29614,72 +29617,72 @@
     </row>
     <row r="21" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C22" s="32" t="s">
         <v>1048</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>1050</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>1052</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1054</v>
-      </c>
       <c r="D23" s="32" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C24" s="25" t="s">
         <v>1055</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>1057</v>
-      </c>
       <c r="D24" s="32" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1060</v>
-      </c>
       <c r="D25" s="32" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">

--- a/4 четверть_13_JavaScript_sugarJS.xlsx
+++ b/4 четверть_13_JavaScript_sugarJS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4076AF5E-4899-4403-A5E0-02054CBCB8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222BE0F7-74AC-4F78-AA53-464D5A9E87C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sugarjs" sheetId="20" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="1092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="1094">
   <si>
     <t>construct(n,indexMapFn)</t>
   </si>
@@ -14787,117 +14787,6 @@
   </si>
   <si>
     <r>
-      <t>[1,2,3].filter(function(n) {
-  return n &gt; 1;
-});</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> //[2, 3]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-[1,2,2,4].filter(2) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">//[2, 2]
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>regexp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-users.filter({ name: /^H/ }) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>//[&lt;User:Harry&gt;]</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">names.filter(/^H/) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>//["Harry", "Holly"]</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>update</t>
     </r>
     <r>
@@ -18385,6 +18274,238 @@
   return item['a'] == 1;
 }); [{"b":2}]
 [{a:1},{b:2}].exclude({b:2}) [{a:1}]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Boolean - Check if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Empty</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>аналог length</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Примечание!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Может быть использован взамен isBlank для строк не созданных пользователем</t>
+    </r>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <r>
+      <t>[1,2,3].filter(function(n) {
+  return n &gt; 1;
+});</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> //[2, 3]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+[1,2,2,4].filter(2) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">//[2, 2]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>users.filter({ SMMTelegramAccept: true });</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> //[&lt;User:Harry&gt;]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>regexp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+users.filter({ name: /^H/ }) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>//[&lt;User:Harry&gt;]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">names.filter(/^H/) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>//["Harry", "Holly"]</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -20371,7 +20492,7 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -20482,7 +20603,7 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -20506,10 +20627,10 @@
         <v>13</v>
       </c>
       <c r="C20" s="36" t="s">
+        <v>906</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>907</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>908</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="1"/>
@@ -20540,7 +20661,7 @@
         <v>202</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>1</v>
@@ -20551,139 +20672,139 @@
     </row>
     <row r="23" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>1013</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>968</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>1014</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>1018</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>968</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>1019</v>
-      </c>
       <c r="E24" s="32" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>1064</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1070</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>1065</v>
-      </c>
       <c r="E25" s="32" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D26" s="32" t="s">
         <v>965</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>968</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="D26" s="32" t="s">
+      <c r="E26" s="32" t="s">
         <v>966</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D31" s="32" t="s">
         <v>1064</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D31" s="32" t="s">
-        <v>1065</v>
-      </c>
       <c r="E31" s="32" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="144" x14ac:dyDescent="0.3">
@@ -20691,10 +20812,10 @@
         <v>436</v>
       </c>
       <c r="B32" s="27" t="s">
+        <v>902</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>903</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>904</v>
       </c>
       <c r="D32" s="17" t="s">
         <v>437</v>
@@ -20705,10 +20826,10 @@
         <v>95</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>96</v>
@@ -20823,7 +20944,7 @@
         <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>74</v>
@@ -20837,7 +20958,7 @@
         <v>13</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>111</v>
@@ -20919,10 +21040,10 @@
         <v>15</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>1089</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>1090</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>14</v>
@@ -20936,7 +21057,7 @@
         <v>200</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>43</v>
@@ -21030,7 +21151,7 @@
         <v>42</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>900</v>
@@ -21229,7 +21350,7 @@
         <v>48</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>47</v>
@@ -21243,7 +21364,7 @@
         <v>48</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>90</v>
@@ -21257,7 +21378,7 @@
         <v>196</v>
       </c>
       <c r="C76" s="37" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="D76" s="14" t="s">
         <v>144</v>
@@ -21272,7 +21393,7 @@
         <v>196</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>65</v>
@@ -21309,16 +21430,16 @@
         <v>95</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>40</v>
       </c>
@@ -21326,7 +21447,7 @@
         <v>388</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>901</v>
+        <v>1093</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>41</v>
@@ -21869,1050 +21990,1102 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:W151"/>
+  <dimension ref="A2:X151"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="3" width="50.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="71.21875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="36.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.21875" style="7" customWidth="1"/>
-    <col min="7" max="7" width="43.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="55.109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="67.88671875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="64.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.77734375" style="7" customWidth="1"/>
-    <col min="12" max="12" width="39.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="48.88671875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="72.6640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="43.88671875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="7.77734375" style="7" customWidth="1"/>
-    <col min="17" max="17" width="56.77734375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="46.77734375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="62.88671875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="49.21875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="8.77734375" style="8"/>
-    <col min="22" max="22" width="67.77734375" style="2" customWidth="1"/>
-    <col min="23" max="23" width="68.33203125" style="1" customWidth="1"/>
-    <col min="24" max="25" width="59.33203125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="59.6640625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="99.44140625" style="1" customWidth="1"/>
-    <col min="28" max="28" width="41.21875" style="1" customWidth="1"/>
-    <col min="29" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="2" width="36" style="1" customWidth="1"/>
+    <col min="3" max="4" width="50.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="71.21875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="36.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.21875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="55.109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="67.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="64.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.77734375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="48.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="72.6640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="43.88671875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="7.77734375" style="7" customWidth="1"/>
+    <col min="18" max="18" width="56.77734375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="46.77734375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="62.88671875" style="2" customWidth="1"/>
+    <col min="21" max="21" width="49.21875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="8.77734375" style="8"/>
+    <col min="23" max="23" width="67.77734375" style="2" customWidth="1"/>
+    <col min="24" max="24" width="68.33203125" style="1" customWidth="1"/>
+    <col min="25" max="26" width="59.33203125" style="1" customWidth="1"/>
+    <col min="27" max="27" width="59.6640625" style="1" customWidth="1"/>
+    <col min="28" max="28" width="99.44140625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="41.21875" style="1" customWidth="1"/>
+    <col min="30" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>909</v>
+      </c>
+      <c r="B2" s="11"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>922</v>
+      </c>
+      <c r="B3" s="15"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="15"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" s="15"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>963</v>
+      </c>
+      <c r="B6" s="15"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>962</v>
+      </c>
+      <c r="B7" s="15"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" s="15"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" s="23"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" s="15"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>684</v>
       </c>
-      <c r="B11" s="1"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B11" s="15"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" s="11"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13" s="15"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B14" s="11"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B15" s="15"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B16" s="15"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B17" s="15"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B18" s="11"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
-      <c r="B20" s="5"/>
+      <c r="B20" s="3"/>
       <c r="C20" s="5"/>
-      <c r="D20" s="6"/>
+      <c r="D20" s="5"/>
       <c r="E20" s="6"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="3"/>
+      <c r="F20" s="6"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="5"/>
       <c r="J20" s="3"/>
-      <c r="L20" s="3"/>
+      <c r="K20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
-      <c r="Q20" s="5"/>
+      <c r="P20" s="3"/>
       <c r="R20" s="5"/>
       <c r="S20" s="5"/>
       <c r="T20" s="5"/>
-      <c r="V20" s="5"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="U20" s="5"/>
+      <c r="W20" s="5"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>910</v>
-      </c>
-      <c r="B22" s="1"/>
+        <v>909</v>
+      </c>
+      <c r="B22" s="20"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
-    </row>
-    <row r="23" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="1:24" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="21"/>
+      <c r="C23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="D23" s="27" t="s">
+        <v>910</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>911</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>650</v>
       </c>
-      <c r="B24" s="2"/>
+      <c r="B24" s="21"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="1"/>
+      <c r="F24" s="2"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="2"/>
       <c r="J24" s="1"/>
-      <c r="L24" s="1"/>
+      <c r="K24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
-      <c r="Q24" s="2"/>
+      <c r="P24" s="1"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="8"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="1"/>
-    </row>
-    <row r="25" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="T24" s="2"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="8"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="1"/>
+    </row>
+    <row r="25" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="21"/>
+      <c r="C25" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="E25" s="2"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="1"/>
+      <c r="F25" s="2"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="2"/>
       <c r="J25" s="1"/>
-      <c r="L25" s="1"/>
+      <c r="K25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
-      <c r="Q25" s="2"/>
+      <c r="P25" s="1"/>
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="8"/>
-      <c r="V25" s="2"/>
-      <c r="W25" s="1"/>
-    </row>
-    <row r="26" spans="1:23" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="T25" s="2"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="8"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="1"/>
+    </row>
+    <row r="26" spans="1:24" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="21"/>
+      <c r="C26" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="G26" s="1"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="2"/>
       <c r="J26" s="1"/>
-      <c r="L26" s="1"/>
+      <c r="K26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
-      <c r="Q26" s="2"/>
+      <c r="P26" s="1"/>
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="8"/>
-      <c r="V26" s="2"/>
-      <c r="W26" s="1"/>
-    </row>
-    <row r="27" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T26" s="2"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="8"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="1"/>
+    </row>
+    <row r="27" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="2"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="1"/>
+      <c r="F27" s="2"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="2"/>
       <c r="J27" s="1"/>
-      <c r="L27" s="1"/>
+      <c r="K27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
-      <c r="Q27" s="2"/>
+      <c r="P27" s="1"/>
       <c r="R27" s="2"/>
       <c r="S27" s="2"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="8"/>
-      <c r="V27" s="2"/>
-      <c r="W27" s="1"/>
-    </row>
-    <row r="28" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T27" s="2"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="8"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="1"/>
+    </row>
+    <row r="28" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E28" s="2"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="1"/>
+      <c r="F28" s="2"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="2"/>
       <c r="J28" s="1"/>
-      <c r="L28" s="1"/>
+      <c r="K28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
-      <c r="Q28" s="2"/>
+      <c r="P28" s="1"/>
       <c r="R28" s="2"/>
       <c r="S28" s="2"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="8"/>
-      <c r="V28" s="2"/>
-      <c r="W28" s="1"/>
-    </row>
-    <row r="29" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T28" s="2"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="8"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="1"/>
+    </row>
+    <row r="29" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E29" s="2"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="1"/>
+      <c r="F29" s="2"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="2"/>
       <c r="J29" s="1"/>
-      <c r="L29" s="1"/>
+      <c r="K29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
-      <c r="Q29" s="2"/>
+      <c r="P29" s="1"/>
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="8"/>
-      <c r="V29" s="2"/>
-      <c r="W29" s="1"/>
-    </row>
-    <row r="30" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="T29" s="2"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="8"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="1"/>
+    </row>
+    <row r="30" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="E30" s="2"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="1"/>
+      <c r="F30" s="2"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="2"/>
       <c r="J30" s="1"/>
-      <c r="L30" s="1"/>
+      <c r="K30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
-      <c r="Q30" s="2"/>
+      <c r="P30" s="1"/>
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="8"/>
-      <c r="V30" s="2"/>
-      <c r="W30" s="1"/>
-    </row>
-    <row r="31" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="T30" s="2"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="8"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="1"/>
+    </row>
+    <row r="31" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E31" s="2"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="1"/>
+      <c r="F31" s="2"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="2"/>
       <c r="J31" s="1"/>
-      <c r="L31" s="1"/>
+      <c r="K31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
-      <c r="Q31" s="2"/>
+      <c r="P31" s="1"/>
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="8"/>
-      <c r="V31" s="2"/>
-      <c r="W31" s="1"/>
-    </row>
-    <row r="32" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T31" s="2"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="8"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="1"/>
+    </row>
+    <row r="32" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="E32" s="2"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="1"/>
+      <c r="F32" s="2"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="2"/>
       <c r="J32" s="1"/>
-      <c r="L32" s="1"/>
+      <c r="K32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
-      <c r="Q32" s="2"/>
+      <c r="P32" s="1"/>
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="8"/>
-      <c r="V32" s="2"/>
-      <c r="W32" s="1"/>
-    </row>
-    <row r="33" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T32" s="2"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="8"/>
+      <c r="W32" s="2"/>
+      <c r="X32" s="1"/>
+    </row>
+    <row r="33" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E33" s="2"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="1"/>
+      <c r="F33" s="2"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="2"/>
       <c r="J33" s="1"/>
-      <c r="L33" s="1"/>
+      <c r="K33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
-      <c r="Q33" s="2"/>
+      <c r="P33" s="1"/>
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="8"/>
-      <c r="V33" s="2"/>
-      <c r="W33" s="1"/>
-    </row>
-    <row r="34" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="T33" s="2"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="8"/>
+      <c r="W33" s="2"/>
+      <c r="X33" s="1"/>
+    </row>
+    <row r="34" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="2"/>
+      <c r="C34" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="G34" s="1"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="2"/>
       <c r="J34" s="1"/>
-      <c r="L34" s="1"/>
+      <c r="K34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
-      <c r="Q34" s="2"/>
+      <c r="P34" s="1"/>
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="8"/>
-      <c r="V34" s="2"/>
-      <c r="W34" s="1"/>
-    </row>
-    <row r="35" spans="1:23" s="7" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="T34" s="2"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="8"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="1"/>
+    </row>
+    <row r="35" spans="1:24" s="7" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="B35" s="2"/>
+      <c r="B35" s="1"/>
       <c r="C35" s="2"/>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="2"/>
+      <c r="E35" s="22" t="s">
         <v>652</v>
       </c>
-      <c r="E35" s="4"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="1"/>
+      <c r="F35" s="4"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="2"/>
       <c r="J35" s="1"/>
-      <c r="L35" s="1"/>
+      <c r="K35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
-      <c r="Q35" s="2"/>
+      <c r="P35" s="1"/>
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="8"/>
-      <c r="V35" s="2"/>
-      <c r="W35" s="1"/>
-    </row>
-    <row r="36" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T35" s="2"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="8"/>
+      <c r="W35" s="2"/>
+      <c r="X35" s="1"/>
+    </row>
+    <row r="36" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="B36" s="2"/>
+      <c r="B36" s="1"/>
       <c r="C36" s="2"/>
-      <c r="D36" s="4"/>
+      <c r="D36" s="2"/>
       <c r="E36" s="4"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="1"/>
+      <c r="F36" s="4"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="2"/>
       <c r="J36" s="1"/>
-      <c r="L36" s="1"/>
+      <c r="K36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
-      <c r="Q36" s="2"/>
+      <c r="P36" s="1"/>
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
-      <c r="T36" s="1"/>
-      <c r="U36" s="8"/>
-      <c r="V36" s="2"/>
-      <c r="W36" s="1"/>
-    </row>
-    <row r="37" spans="1:23" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="T36" s="2"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="8"/>
+      <c r="W36" s="2"/>
+      <c r="X36" s="1"/>
+    </row>
+    <row r="37" spans="1:24" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="B37" s="2"/>
+      <c r="B37" s="1"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="22" t="s">
+      <c r="D37" s="2"/>
+      <c r="E37" s="22" t="s">
         <v>654</v>
       </c>
-      <c r="E37" s="4"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="1"/>
+      <c r="F37" s="4"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="2"/>
       <c r="J37" s="1"/>
-      <c r="L37" s="1"/>
+      <c r="K37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
-      <c r="Q37" s="2"/>
+      <c r="P37" s="1"/>
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="8"/>
-      <c r="V37" s="2"/>
-      <c r="W37" s="1"/>
-    </row>
-    <row r="38" spans="1:23" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="T37" s="2"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="8"/>
+      <c r="W37" s="2"/>
+      <c r="X37" s="1"/>
+    </row>
+    <row r="38" spans="1:24" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="B38" s="2"/>
+      <c r="B38" s="1"/>
       <c r="C38" s="2"/>
-      <c r="D38" s="22" t="s">
+      <c r="D38" s="2"/>
+      <c r="E38" s="22" t="s">
         <v>657</v>
       </c>
-      <c r="E38" s="4"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="1"/>
+      <c r="F38" s="4"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="2"/>
       <c r="J38" s="1"/>
-      <c r="L38" s="1"/>
+      <c r="K38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
-      <c r="Q38" s="2"/>
+      <c r="P38" s="1"/>
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
-      <c r="T38" s="1"/>
-      <c r="U38" s="8"/>
-      <c r="V38" s="2"/>
-      <c r="W38" s="1"/>
-    </row>
-    <row r="39" spans="1:23" s="7" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+      <c r="T38" s="2"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="8"/>
+      <c r="W38" s="2"/>
+      <c r="X38" s="1"/>
+    </row>
+    <row r="39" spans="1:24" s="7" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="B39" s="2"/>
+      <c r="B39" s="1"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="22" t="s">
+      <c r="D39" s="2"/>
+      <c r="E39" s="22" t="s">
         <v>659</v>
       </c>
-      <c r="E39" s="4"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="1"/>
+      <c r="F39" s="4"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="2"/>
       <c r="J39" s="1"/>
-      <c r="L39" s="1"/>
+      <c r="K39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
-      <c r="Q39" s="2"/>
+      <c r="P39" s="1"/>
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
-      <c r="T39" s="1"/>
-      <c r="U39" s="8"/>
-      <c r="V39" s="2"/>
-      <c r="W39" s="1"/>
-    </row>
-    <row r="40" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="T39" s="2"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="8"/>
+      <c r="W39" s="2"/>
+      <c r="X39" s="1"/>
+    </row>
+    <row r="40" spans="1:24" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="B40" s="2"/>
+      <c r="B40" s="1"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="22" t="s">
+      <c r="D40" s="2"/>
+      <c r="E40" s="22" t="s">
         <v>661</v>
       </c>
-      <c r="E40" s="4"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="1"/>
+      <c r="F40" s="4"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="2"/>
       <c r="J40" s="1"/>
-      <c r="L40" s="1"/>
+      <c r="K40" s="1"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
-      <c r="Q40" s="2"/>
+      <c r="P40" s="1"/>
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
-      <c r="T40" s="1"/>
-      <c r="U40" s="8"/>
-      <c r="V40" s="2"/>
-      <c r="W40" s="1"/>
-    </row>
-    <row r="41" spans="1:23" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="T40" s="2"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="8"/>
+      <c r="W40" s="2"/>
+      <c r="X40" s="1"/>
+    </row>
+    <row r="41" spans="1:24" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="B41" s="2"/>
+      <c r="B41" s="1"/>
       <c r="C41" s="2"/>
-      <c r="D41" s="22" t="s">
+      <c r="D41" s="2"/>
+      <c r="E41" s="22" t="s">
         <v>663</v>
       </c>
-      <c r="E41" s="4"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="1"/>
+      <c r="F41" s="4"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="2"/>
       <c r="J41" s="1"/>
-      <c r="L41" s="1"/>
+      <c r="K41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
-      <c r="Q41" s="2"/>
+      <c r="P41" s="1"/>
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
-      <c r="T41" s="1"/>
-      <c r="U41" s="8"/>
-      <c r="V41" s="2"/>
-      <c r="W41" s="1"/>
-    </row>
-    <row r="42" spans="1:23" s="7" customFormat="1" ht="331.2" x14ac:dyDescent="0.3">
+      <c r="T41" s="2"/>
+      <c r="U41" s="1"/>
+      <c r="V41" s="8"/>
+      <c r="W41" s="2"/>
+      <c r="X41" s="1"/>
+    </row>
+    <row r="42" spans="1:24" s="7" customFormat="1" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="B42" s="2"/>
+      <c r="B42" s="1"/>
       <c r="C42" s="2"/>
-      <c r="D42" s="22" t="s">
+      <c r="D42" s="2"/>
+      <c r="E42" s="22" t="s">
         <v>665</v>
       </c>
-      <c r="E42" s="4"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="1"/>
+      <c r="F42" s="4"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="2"/>
       <c r="J42" s="1"/>
-      <c r="L42" s="1"/>
+      <c r="K42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
-      <c r="Q42" s="2"/>
+      <c r="P42" s="1"/>
       <c r="R42" s="2"/>
       <c r="S42" s="2"/>
-      <c r="T42" s="1"/>
-      <c r="U42" s="8"/>
-      <c r="V42" s="2"/>
-      <c r="W42" s="1"/>
-    </row>
-    <row r="43" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T42" s="2"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="8"/>
+      <c r="W42" s="2"/>
+      <c r="X42" s="1"/>
+    </row>
+    <row r="43" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
         <v>681</v>
       </c>
-      <c r="B43" s="2"/>
+      <c r="B43" s="15"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="1"/>
+      <c r="F43" s="2"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="2"/>
       <c r="J43" s="1"/>
-      <c r="L43" s="1"/>
+      <c r="K43" s="1"/>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
-      <c r="Q43" s="2"/>
+      <c r="P43" s="1"/>
       <c r="R43" s="2"/>
       <c r="S43" s="2"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="8"/>
-      <c r="V43" s="2"/>
-      <c r="W43" s="1"/>
-    </row>
-    <row r="44" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="T43" s="2"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="8"/>
+      <c r="W43" s="2"/>
+      <c r="X43" s="1"/>
+    </row>
+    <row r="44" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="2"/>
+      <c r="C44" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="E44" s="2"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="1"/>
+      <c r="F44" s="2"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="2"/>
       <c r="J44" s="1"/>
-      <c r="L44" s="1"/>
+      <c r="K44" s="1"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
-      <c r="Q44" s="2"/>
+      <c r="P44" s="1"/>
       <c r="R44" s="2"/>
       <c r="S44" s="2"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="8"/>
-      <c r="V44" s="2"/>
-      <c r="W44" s="1"/>
-    </row>
-    <row r="45" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="T44" s="2"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="8"/>
+      <c r="W44" s="2"/>
+      <c r="X44" s="1"/>
+    </row>
+    <row r="45" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="2"/>
+      <c r="C45" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="E45" s="2"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="1"/>
+      <c r="F45" s="2"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="2"/>
       <c r="J45" s="1"/>
-      <c r="L45" s="1"/>
+      <c r="K45" s="1"/>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
-      <c r="Q45" s="2"/>
+      <c r="P45" s="1"/>
       <c r="R45" s="2"/>
       <c r="S45" s="2"/>
-      <c r="T45" s="1"/>
-      <c r="U45" s="8"/>
-      <c r="V45" s="2"/>
-      <c r="W45" s="1"/>
-    </row>
-    <row r="46" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="T45" s="2"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="8"/>
+      <c r="W45" s="2"/>
+      <c r="X45" s="1"/>
+    </row>
+    <row r="46" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="2"/>
+      <c r="C46" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="E46" s="2"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="1"/>
+      <c r="F46" s="2"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="2"/>
       <c r="J46" s="1"/>
-      <c r="L46" s="1"/>
+      <c r="K46" s="1"/>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
-      <c r="Q46" s="2"/>
+      <c r="P46" s="1"/>
       <c r="R46" s="2"/>
       <c r="S46" s="2"/>
-      <c r="T46" s="1"/>
-      <c r="U46" s="8"/>
-      <c r="V46" s="2"/>
-      <c r="W46" s="1"/>
-    </row>
-    <row r="47" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="T46" s="2"/>
+      <c r="U46" s="1"/>
+      <c r="V46" s="8"/>
+      <c r="W46" s="2"/>
+      <c r="X46" s="1"/>
+    </row>
+    <row r="47" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="2"/>
+      <c r="C47" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="E47" s="2"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="1"/>
+      <c r="F47" s="2"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="2"/>
       <c r="J47" s="1"/>
-      <c r="L47" s="1"/>
+      <c r="K47" s="1"/>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
-      <c r="Q47" s="2"/>
+      <c r="P47" s="1"/>
       <c r="R47" s="2"/>
       <c r="S47" s="2"/>
-      <c r="T47" s="1"/>
-      <c r="U47" s="8"/>
-      <c r="V47" s="2"/>
-      <c r="W47" s="1"/>
-    </row>
-    <row r="48" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T47" s="2"/>
+      <c r="U47" s="1"/>
+      <c r="V47" s="8"/>
+      <c r="W47" s="2"/>
+      <c r="X47" s="1"/>
+    </row>
+    <row r="48" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="2"/>
+      <c r="C48" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="E48" s="2"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="1"/>
+      <c r="F48" s="2"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="2"/>
       <c r="J48" s="1"/>
-      <c r="L48" s="1"/>
+      <c r="K48" s="1"/>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
-      <c r="Q48" s="2"/>
+      <c r="P48" s="1"/>
       <c r="R48" s="2"/>
       <c r="S48" s="2"/>
-      <c r="T48" s="1"/>
-      <c r="U48" s="8"/>
-      <c r="V48" s="2"/>
-      <c r="W48" s="1"/>
-    </row>
-    <row r="49" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T48" s="2"/>
+      <c r="U48" s="1"/>
+      <c r="V48" s="8"/>
+      <c r="W48" s="2"/>
+      <c r="X48" s="1"/>
+    </row>
+    <row r="49" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15" t="s">
-        <v>961</v>
-      </c>
-      <c r="B49" s="2"/>
+        <v>960</v>
+      </c>
+      <c r="B49" s="21"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="1"/>
+      <c r="F49" s="2"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="2"/>
       <c r="J49" s="1"/>
-      <c r="L49" s="1"/>
+      <c r="K49" s="1"/>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
-      <c r="Q49" s="2"/>
+      <c r="P49" s="1"/>
       <c r="R49" s="2"/>
       <c r="S49" s="2"/>
-      <c r="T49" s="1"/>
-      <c r="U49" s="8"/>
-      <c r="V49" s="2"/>
-      <c r="W49" s="1"/>
-    </row>
-    <row r="50" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T49" s="2"/>
+      <c r="U49" s="1"/>
+      <c r="V49" s="8"/>
+      <c r="W49" s="2"/>
+      <c r="X49" s="1"/>
+    </row>
+    <row r="50" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="2"/>
+      <c r="C50" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="F50" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="G50" s="1"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="2"/>
       <c r="J50" s="1"/>
-      <c r="L50" s="1"/>
+      <c r="K50" s="1"/>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
-      <c r="Q50" s="2"/>
+      <c r="P50" s="1"/>
       <c r="R50" s="2"/>
       <c r="S50" s="2"/>
-      <c r="T50" s="1"/>
-      <c r="U50" s="8"/>
-      <c r="V50" s="2"/>
-      <c r="W50" s="1"/>
-    </row>
-    <row r="51" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="T50" s="2"/>
+      <c r="U50" s="1"/>
+      <c r="V50" s="8"/>
+      <c r="W50" s="2"/>
+      <c r="X50" s="1"/>
+    </row>
+    <row r="51" spans="1:24" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>950</v>
-      </c>
+      <c r="B51" s="2"/>
       <c r="C51" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="F51" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="G51" s="1"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="2"/>
       <c r="J51" s="1"/>
-      <c r="L51" s="1"/>
+      <c r="K51" s="1"/>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
-      <c r="Q51" s="2"/>
+      <c r="P51" s="1"/>
       <c r="R51" s="2"/>
       <c r="S51" s="2"/>
-      <c r="T51" s="1"/>
-      <c r="U51" s="8"/>
-      <c r="V51" s="2"/>
-      <c r="W51" s="1"/>
-    </row>
-    <row r="52" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="T51" s="2"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="8"/>
+      <c r="W51" s="2"/>
+      <c r="X51" s="1"/>
+    </row>
+    <row r="52" spans="1:24" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>951</v>
-      </c>
+      <c r="B52" s="2"/>
       <c r="C52" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="F52" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="G52" s="1"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="2"/>
       <c r="J52" s="1"/>
-      <c r="L52" s="1"/>
+      <c r="K52" s="1"/>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
-      <c r="Q52" s="2"/>
+      <c r="P52" s="1"/>
       <c r="R52" s="2"/>
       <c r="S52" s="2"/>
-      <c r="T52" s="1"/>
-      <c r="U52" s="8"/>
-      <c r="V52" s="2"/>
-      <c r="W52" s="1"/>
-    </row>
-    <row r="53" spans="1:23" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="T52" s="2"/>
+      <c r="U52" s="1"/>
+      <c r="V52" s="8"/>
+      <c r="W52" s="2"/>
+      <c r="X52" s="1"/>
+    </row>
+    <row r="53" spans="1:24" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="2"/>
+      <c r="C53" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="D53" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="F53" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="G53" s="1"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="2"/>
       <c r="J53" s="1"/>
-      <c r="L53" s="1"/>
+      <c r="K53" s="1"/>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
-      <c r="Q53" s="2"/>
+      <c r="P53" s="1"/>
       <c r="R53" s="2"/>
       <c r="S53" s="2"/>
-      <c r="T53" s="1"/>
-      <c r="U53" s="8"/>
-      <c r="V53" s="2"/>
-      <c r="W53" s="1"/>
-    </row>
-    <row r="54" spans="1:23" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="T53" s="2"/>
+      <c r="U53" s="1"/>
+      <c r="V53" s="8"/>
+      <c r="W53" s="2"/>
+      <c r="X53" s="1"/>
+    </row>
+    <row r="54" spans="1:24" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="2"/>
+      <c r="C54" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="D54" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="E54" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="F54" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="G54" s="1"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="2"/>
       <c r="J54" s="1"/>
-      <c r="L54" s="1"/>
+      <c r="K54" s="1"/>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
-      <c r="Q54" s="2"/>
+      <c r="P54" s="1"/>
       <c r="R54" s="2"/>
       <c r="S54" s="2"/>
-      <c r="T54" s="1"/>
-      <c r="U54" s="8"/>
-      <c r="V54" s="2"/>
-      <c r="W54" s="1"/>
-    </row>
-    <row r="55" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T54" s="2"/>
+      <c r="U54" s="1"/>
+      <c r="V54" s="8"/>
+      <c r="W54" s="2"/>
+      <c r="X54" s="1"/>
+    </row>
+    <row r="55" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="15" t="s">
         <v>685</v>
       </c>
@@ -22920,148 +23093,164 @@
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="1"/>
+      <c r="F55" s="2"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="2"/>
       <c r="J55" s="1"/>
-      <c r="L55" s="1"/>
+      <c r="K55" s="1"/>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
-      <c r="Q55" s="2"/>
+      <c r="P55" s="1"/>
       <c r="R55" s="2"/>
       <c r="S55" s="2"/>
-      <c r="T55" s="1"/>
-      <c r="U55" s="8"/>
-      <c r="V55" s="2"/>
-      <c r="W55" s="1"/>
-    </row>
-    <row r="56" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="T55" s="2"/>
+      <c r="U55" s="1"/>
+      <c r="V55" s="8"/>
+      <c r="W55" s="2"/>
+      <c r="X55" s="1"/>
+    </row>
+    <row r="56" spans="1:24" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>497</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="F56" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="G56" s="1"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="2"/>
       <c r="J56" s="1"/>
-      <c r="L56" s="1"/>
+      <c r="K56" s="1"/>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
-      <c r="Q56" s="2"/>
+      <c r="P56" s="1"/>
       <c r="R56" s="2"/>
       <c r="S56" s="2"/>
-      <c r="T56" s="1"/>
-      <c r="U56" s="8"/>
-      <c r="V56" s="2"/>
-      <c r="W56" s="1"/>
-    </row>
-    <row r="57" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T56" s="2"/>
+      <c r="U56" s="1"/>
+      <c r="V56" s="8"/>
+      <c r="W56" s="2"/>
+      <c r="X56" s="1"/>
+    </row>
+    <row r="57" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>502</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="E57" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="E57" s="2"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="1"/>
+      <c r="F57" s="2"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="2"/>
       <c r="J57" s="1"/>
-      <c r="L57" s="1"/>
+      <c r="K57" s="1"/>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
-      <c r="Q57" s="2"/>
+      <c r="P57" s="1"/>
       <c r="R57" s="2"/>
       <c r="S57" s="2"/>
-      <c r="T57" s="1"/>
-      <c r="U57" s="8"/>
-      <c r="V57" s="2"/>
-      <c r="W57" s="1"/>
-    </row>
-    <row r="58" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T57" s="2"/>
+      <c r="U57" s="1"/>
+      <c r="V57" s="8"/>
+      <c r="W57" s="2"/>
+      <c r="X57" s="1"/>
+    </row>
+    <row r="58" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>579</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="D58" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="E58" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="E58" s="2"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="1"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="2"/>
       <c r="J58" s="1"/>
-      <c r="K58" s="7"/>
-      <c r="L58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="7"/>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="2"/>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="7"/>
       <c r="R58" s="2"/>
       <c r="S58" s="2"/>
-      <c r="T58" s="1"/>
-      <c r="U58" s="8"/>
-      <c r="V58" s="2"/>
-      <c r="W58" s="1"/>
-    </row>
-    <row r="59" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T58" s="2"/>
+      <c r="U58" s="1"/>
+      <c r="V58" s="8"/>
+      <c r="W58" s="2"/>
+      <c r="X58" s="1"/>
+    </row>
+    <row r="59" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>583</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="E59" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="E59" s="2"/>
-    </row>
-    <row r="60" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F59" s="2"/>
+    </row>
+    <row r="60" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>608</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="E60" s="2"/>
-    </row>
-    <row r="61" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F60" s="2"/>
+    </row>
+    <row r="61" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
         <v>693</v>
       </c>
@@ -23069,1690 +23258,1753 @@
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="1"/>
+      <c r="F61" s="2"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="2"/>
       <c r="J61" s="1"/>
-      <c r="L61" s="1"/>
+      <c r="K61" s="1"/>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
-      <c r="Q61" s="2"/>
+      <c r="P61" s="1"/>
       <c r="R61" s="2"/>
       <c r="S61" s="2"/>
-      <c r="T61" s="1"/>
-      <c r="U61" s="8"/>
-      <c r="V61" s="2"/>
-      <c r="W61" s="1"/>
-    </row>
-    <row r="62" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="T61" s="2"/>
+      <c r="U61" s="1"/>
+      <c r="V61" s="8"/>
+      <c r="W61" s="2"/>
+      <c r="X61" s="1"/>
+    </row>
+    <row r="62" spans="1:24" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="2"/>
+      <c r="C62" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="D62" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="E62" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="F62" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="G62" s="1"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="2"/>
       <c r="J62" s="1"/>
-      <c r="L62" s="1"/>
+      <c r="K62" s="1"/>
       <c r="M62" s="1"/>
       <c r="N62" s="1"/>
       <c r="O62" s="1"/>
-      <c r="Q62" s="2"/>
+      <c r="P62" s="1"/>
       <c r="R62" s="2"/>
       <c r="S62" s="2"/>
-      <c r="T62" s="1"/>
-      <c r="U62" s="8"/>
-      <c r="V62" s="2"/>
-      <c r="W62" s="1"/>
-    </row>
-    <row r="63" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T62" s="2"/>
+      <c r="U62" s="1"/>
+      <c r="V62" s="8"/>
+      <c r="W62" s="2"/>
+      <c r="X62" s="1"/>
+    </row>
+    <row r="63" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="2"/>
+      <c r="C63" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C63" s="2"/>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="1"/>
+      <c r="F63" s="2"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="2"/>
       <c r="J63" s="1"/>
-      <c r="L63" s="1"/>
+      <c r="K63" s="1"/>
       <c r="M63" s="1"/>
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
-      <c r="Q63" s="2"/>
+      <c r="P63" s="1"/>
       <c r="R63" s="2"/>
       <c r="S63" s="2"/>
-      <c r="T63" s="1"/>
-      <c r="U63" s="8"/>
-      <c r="V63" s="2"/>
-      <c r="W63" s="1"/>
-    </row>
-    <row r="64" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T63" s="2"/>
+      <c r="U63" s="1"/>
+      <c r="V63" s="8"/>
+      <c r="W63" s="2"/>
+      <c r="X63" s="1"/>
+    </row>
+    <row r="64" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="2"/>
+      <c r="C64" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C64" s="2"/>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="1"/>
+      <c r="F64" s="2"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="2"/>
       <c r="J64" s="1"/>
-      <c r="L64" s="1"/>
+      <c r="K64" s="1"/>
       <c r="M64" s="1"/>
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
-      <c r="Q64" s="2"/>
+      <c r="P64" s="1"/>
       <c r="R64" s="2"/>
       <c r="S64" s="2"/>
-      <c r="T64" s="1"/>
-      <c r="U64" s="8"/>
-      <c r="V64" s="2"/>
-      <c r="W64" s="1"/>
-    </row>
-    <row r="65" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T64" s="2"/>
+      <c r="U64" s="1"/>
+      <c r="V64" s="8"/>
+      <c r="W64" s="2"/>
+      <c r="X64" s="1"/>
+    </row>
+    <row r="65" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="2"/>
+      <c r="C65" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="1"/>
+      <c r="F65" s="2"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="2"/>
       <c r="J65" s="1"/>
-      <c r="L65" s="1"/>
+      <c r="K65" s="1"/>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
-      <c r="Q65" s="2"/>
+      <c r="P65" s="1"/>
       <c r="R65" s="2"/>
       <c r="S65" s="2"/>
-      <c r="T65" s="1"/>
-      <c r="U65" s="8"/>
-      <c r="V65" s="2"/>
-      <c r="W65" s="1"/>
-    </row>
-    <row r="66" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T65" s="2"/>
+      <c r="U65" s="1"/>
+      <c r="V65" s="8"/>
+      <c r="W65" s="2"/>
+      <c r="X65" s="1"/>
+    </row>
+    <row r="66" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="2"/>
+      <c r="C66" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="1"/>
+      <c r="F66" s="2"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="2"/>
       <c r="J66" s="1"/>
-      <c r="L66" s="1"/>
+      <c r="K66" s="1"/>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
-      <c r="Q66" s="2"/>
+      <c r="P66" s="1"/>
       <c r="R66" s="2"/>
       <c r="S66" s="2"/>
-      <c r="T66" s="1"/>
-      <c r="U66" s="8"/>
-      <c r="V66" s="2"/>
-      <c r="W66" s="1"/>
-    </row>
-    <row r="67" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T66" s="2"/>
+      <c r="U66" s="1"/>
+      <c r="V66" s="8"/>
+      <c r="W66" s="2"/>
+      <c r="X66" s="1"/>
+    </row>
+    <row r="67" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="2"/>
+      <c r="C67" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="D67" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D67" s="2"/>
       <c r="E67" s="2"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="1"/>
+      <c r="F67" s="2"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="2"/>
       <c r="J67" s="1"/>
-      <c r="L67" s="1"/>
+      <c r="K67" s="1"/>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
-      <c r="Q67" s="2"/>
+      <c r="P67" s="1"/>
       <c r="R67" s="2"/>
       <c r="S67" s="2"/>
-      <c r="T67" s="1"/>
-      <c r="U67" s="8"/>
-      <c r="V67" s="2"/>
-      <c r="W67" s="1"/>
-    </row>
-    <row r="68" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T67" s="2"/>
+      <c r="U67" s="1"/>
+      <c r="V67" s="8"/>
+      <c r="W67" s="2"/>
+      <c r="X67" s="1"/>
+    </row>
+    <row r="68" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="2"/>
+      <c r="C68" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C68" s="2"/>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="1"/>
+      <c r="F68" s="2"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="2"/>
       <c r="J68" s="1"/>
-      <c r="L68" s="1"/>
+      <c r="K68" s="1"/>
       <c r="M68" s="1"/>
       <c r="N68" s="1"/>
       <c r="O68" s="1"/>
-      <c r="Q68" s="2"/>
+      <c r="P68" s="1"/>
       <c r="R68" s="2"/>
       <c r="S68" s="2"/>
-      <c r="T68" s="1"/>
-      <c r="U68" s="8"/>
-      <c r="V68" s="2"/>
-      <c r="W68" s="1"/>
-    </row>
-    <row r="69" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T68" s="2"/>
+      <c r="U68" s="1"/>
+      <c r="V68" s="8"/>
+      <c r="W68" s="2"/>
+      <c r="X68" s="1"/>
+    </row>
+    <row r="69" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="2"/>
+      <c r="C69" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C69" s="2"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="1"/>
+      <c r="F69" s="2"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="2"/>
       <c r="J69" s="1"/>
-      <c r="L69" s="1"/>
+      <c r="K69" s="1"/>
       <c r="M69" s="1"/>
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
-      <c r="Q69" s="2"/>
+      <c r="P69" s="1"/>
       <c r="R69" s="2"/>
       <c r="S69" s="2"/>
-      <c r="T69" s="1"/>
-      <c r="U69" s="8"/>
-      <c r="V69" s="2"/>
-      <c r="W69" s="1"/>
-    </row>
-    <row r="70" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T69" s="2"/>
+      <c r="U69" s="1"/>
+      <c r="V69" s="8"/>
+      <c r="W69" s="2"/>
+      <c r="X69" s="1"/>
+    </row>
+    <row r="70" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="2"/>
+      <c r="C70" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="D70" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="D70" s="2"/>
       <c r="E70" s="2"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="1"/>
+      <c r="F70" s="2"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="2"/>
       <c r="J70" s="1"/>
-      <c r="L70" s="1"/>
+      <c r="K70" s="1"/>
       <c r="M70" s="1"/>
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
-      <c r="Q70" s="2"/>
+      <c r="P70" s="1"/>
       <c r="R70" s="2"/>
       <c r="S70" s="2"/>
-      <c r="T70" s="1"/>
-      <c r="U70" s="8"/>
-      <c r="V70" s="2"/>
-      <c r="W70" s="1"/>
-    </row>
-    <row r="71" spans="1:23" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="T70" s="2"/>
+      <c r="U70" s="1"/>
+      <c r="V70" s="8"/>
+      <c r="W70" s="2"/>
+      <c r="X70" s="1"/>
+    </row>
+    <row r="71" spans="1:24" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="2"/>
+      <c r="C71" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="D71" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="E71" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E71" s="2"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="1"/>
+      <c r="F71" s="2"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="2"/>
       <c r="J71" s="1"/>
-      <c r="L71" s="1"/>
+      <c r="K71" s="1"/>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
       <c r="O71" s="1"/>
-      <c r="Q71" s="2"/>
+      <c r="P71" s="1"/>
       <c r="R71" s="2"/>
       <c r="S71" s="2"/>
-      <c r="T71" s="1"/>
-      <c r="U71" s="8"/>
-      <c r="V71" s="2"/>
-      <c r="W71" s="1"/>
-    </row>
-    <row r="72" spans="1:23" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="T71" s="2"/>
+      <c r="U71" s="1"/>
+      <c r="V71" s="8"/>
+      <c r="W71" s="2"/>
+      <c r="X71" s="1"/>
+    </row>
+    <row r="72" spans="1:24" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="2"/>
+      <c r="C72" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="D72" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="E72" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="E72" s="2"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="1"/>
+      <c r="F72" s="2"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="2"/>
       <c r="J72" s="1"/>
-      <c r="L72" s="1"/>
+      <c r="K72" s="1"/>
       <c r="M72" s="1"/>
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
-      <c r="Q72" s="2"/>
+      <c r="P72" s="1"/>
       <c r="R72" s="2"/>
       <c r="S72" s="2"/>
-      <c r="T72" s="1"/>
-      <c r="U72" s="8"/>
-      <c r="V72" s="2"/>
-      <c r="W72" s="1"/>
-    </row>
-    <row r="73" spans="1:23" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="T72" s="2"/>
+      <c r="U72" s="1"/>
+      <c r="V72" s="8"/>
+      <c r="W72" s="2"/>
+      <c r="X72" s="1"/>
+    </row>
+    <row r="73" spans="1:24" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="2"/>
+      <c r="C73" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="C73" s="27" t="s">
+      <c r="D73" s="27" t="s">
         <v>899</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="F73" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="G73" s="1"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="2"/>
       <c r="J73" s="1"/>
-      <c r="L73" s="1"/>
+      <c r="K73" s="1"/>
       <c r="M73" s="1"/>
       <c r="N73" s="1"/>
       <c r="O73" s="1"/>
-      <c r="Q73" s="2"/>
+      <c r="P73" s="1"/>
       <c r="R73" s="2"/>
       <c r="S73" s="2"/>
-      <c r="T73" s="1"/>
-      <c r="U73" s="8"/>
-      <c r="V73" s="2"/>
-      <c r="W73" s="1"/>
-    </row>
-    <row r="74" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="T73" s="2"/>
+      <c r="U73" s="1"/>
+      <c r="V73" s="8"/>
+      <c r="W73" s="2"/>
+      <c r="X73" s="1"/>
+    </row>
+    <row r="74" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="2"/>
+      <c r="C74" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="E74" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="E74" s="2"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="1"/>
+      <c r="F74" s="2"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="2"/>
       <c r="J74" s="1"/>
-      <c r="L74" s="1"/>
+      <c r="K74" s="1"/>
       <c r="M74" s="1"/>
       <c r="N74" s="1"/>
       <c r="O74" s="1"/>
-      <c r="Q74" s="2"/>
+      <c r="P74" s="1"/>
       <c r="R74" s="2"/>
       <c r="S74" s="2"/>
-      <c r="T74" s="1"/>
-      <c r="U74" s="8"/>
-      <c r="V74" s="2"/>
-      <c r="W74" s="1"/>
-    </row>
-    <row r="75" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="T74" s="2"/>
+      <c r="U74" s="1"/>
+      <c r="V74" s="8"/>
+      <c r="W74" s="2"/>
+      <c r="X74" s="1"/>
+    </row>
+    <row r="75" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="21"/>
+      <c r="C75" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="E75" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="E75" s="2"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="1"/>
+      <c r="F75" s="2"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="2"/>
       <c r="J75" s="1"/>
-      <c r="L75" s="1"/>
+      <c r="K75" s="1"/>
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
-      <c r="Q75" s="2"/>
+      <c r="P75" s="1"/>
       <c r="R75" s="2"/>
       <c r="S75" s="2"/>
-      <c r="T75" s="1"/>
-      <c r="U75" s="8"/>
-      <c r="V75" s="2"/>
-      <c r="W75" s="1"/>
-    </row>
-    <row r="76" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T75" s="2"/>
+      <c r="U75" s="1"/>
+      <c r="V75" s="8"/>
+      <c r="W75" s="2"/>
+      <c r="X75" s="1"/>
+    </row>
+    <row r="76" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="15" t="s">
         <v>682</v>
       </c>
-      <c r="B76" s="2"/>
+      <c r="B76" s="21"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="1"/>
+      <c r="F76" s="2"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="2"/>
       <c r="J76" s="1"/>
-      <c r="L76" s="1"/>
+      <c r="K76" s="1"/>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
       <c r="O76" s="1"/>
-      <c r="Q76" s="2"/>
+      <c r="P76" s="1"/>
       <c r="R76" s="2"/>
       <c r="S76" s="2"/>
-      <c r="T76" s="1"/>
-      <c r="U76" s="8"/>
-      <c r="V76" s="2"/>
-      <c r="W76" s="1"/>
-    </row>
-    <row r="77" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T76" s="2"/>
+      <c r="U76" s="1"/>
+      <c r="V76" s="8"/>
+      <c r="W76" s="2"/>
+      <c r="X76" s="1"/>
+    </row>
+    <row r="77" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="21"/>
+      <c r="C77" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="D77" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="E77" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="E77" s="2"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="1"/>
+      <c r="F77" s="2"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="2"/>
       <c r="J77" s="1"/>
-      <c r="L77" s="1"/>
+      <c r="K77" s="1"/>
       <c r="M77" s="1"/>
       <c r="N77" s="1"/>
       <c r="O77" s="1"/>
-      <c r="Q77" s="2"/>
+      <c r="P77" s="1"/>
       <c r="R77" s="2"/>
       <c r="S77" s="2"/>
-      <c r="T77" s="1"/>
-      <c r="U77" s="8"/>
-      <c r="V77" s="2"/>
-      <c r="W77" s="1"/>
-    </row>
-    <row r="78" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T77" s="2"/>
+      <c r="U77" s="1"/>
+      <c r="V77" s="8"/>
+      <c r="W77" s="2"/>
+      <c r="X77" s="1"/>
+    </row>
+    <row r="78" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="15" t="s">
         <v>684</v>
       </c>
-      <c r="B78" s="2"/>
+      <c r="B78" s="21"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="1"/>
+      <c r="F78" s="2"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="2"/>
       <c r="J78" s="1"/>
-      <c r="L78" s="1"/>
+      <c r="K78" s="1"/>
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
       <c r="O78" s="1"/>
-      <c r="Q78" s="2"/>
+      <c r="P78" s="1"/>
       <c r="R78" s="2"/>
       <c r="S78" s="2"/>
-      <c r="T78" s="1"/>
-      <c r="U78" s="8"/>
-      <c r="V78" s="2"/>
-      <c r="W78" s="1"/>
-    </row>
-    <row r="79" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T78" s="2"/>
+      <c r="U78" s="1"/>
+      <c r="V78" s="8"/>
+      <c r="W78" s="2"/>
+      <c r="X78" s="1"/>
+    </row>
+    <row r="79" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="21"/>
+      <c r="C79" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="E79" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="E79" s="2"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="1"/>
+      <c r="F79" s="2"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="2"/>
       <c r="J79" s="1"/>
-      <c r="L79" s="1"/>
+      <c r="K79" s="1"/>
       <c r="M79" s="1"/>
       <c r="N79" s="1"/>
       <c r="O79" s="1"/>
-      <c r="Q79" s="2"/>
+      <c r="P79" s="1"/>
       <c r="R79" s="2"/>
       <c r="S79" s="2"/>
-      <c r="T79" s="1"/>
-      <c r="U79" s="8"/>
-      <c r="V79" s="2"/>
-      <c r="W79" s="1"/>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="T79" s="2"/>
+      <c r="U79" s="1"/>
+      <c r="V79" s="8"/>
+      <c r="W79" s="2"/>
+      <c r="X79" s="1"/>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="81" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B80" s="20"/>
+    </row>
+    <row r="81" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="21"/>
+      <c r="C81" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="D81" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="E81" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="E81" s="2"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="1"/>
+      <c r="F81" s="2"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="2"/>
       <c r="J81" s="1"/>
-      <c r="L81" s="1"/>
+      <c r="K81" s="1"/>
       <c r="M81" s="1"/>
       <c r="N81" s="1"/>
       <c r="O81" s="1"/>
-      <c r="Q81" s="2"/>
+      <c r="P81" s="1"/>
       <c r="R81" s="2"/>
       <c r="S81" s="2"/>
-      <c r="T81" s="1"/>
-      <c r="U81" s="8"/>
-      <c r="V81" s="2"/>
-      <c r="W81" s="1"/>
-    </row>
-    <row r="82" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T81" s="2"/>
+      <c r="U81" s="1"/>
+      <c r="V81" s="8"/>
+      <c r="W81" s="2"/>
+      <c r="X81" s="1"/>
+    </row>
+    <row r="82" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="15" t="s">
         <v>687</v>
       </c>
-      <c r="B82" s="2"/>
+      <c r="B82" s="21"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="1"/>
+      <c r="F82" s="2"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="2"/>
       <c r="J82" s="1"/>
-      <c r="L82" s="1"/>
+      <c r="K82" s="1"/>
       <c r="M82" s="1"/>
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
-      <c r="Q82" s="2"/>
+      <c r="P82" s="1"/>
       <c r="R82" s="2"/>
       <c r="S82" s="2"/>
-      <c r="T82" s="1"/>
-      <c r="U82" s="8"/>
-      <c r="V82" s="2"/>
-      <c r="W82" s="1"/>
-    </row>
-    <row r="83" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T82" s="2"/>
+      <c r="U82" s="1"/>
+      <c r="V82" s="8"/>
+      <c r="W82" s="2"/>
+      <c r="X82" s="1"/>
+    </row>
+    <row r="83" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="21"/>
+      <c r="C83" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="D83" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="E83" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="E83" s="2"/>
-      <c r="F83" s="7"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="1"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="7"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="2"/>
       <c r="J83" s="1"/>
-      <c r="K83" s="7"/>
-      <c r="L83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="7"/>
       <c r="M83" s="1"/>
       <c r="N83" s="1"/>
       <c r="O83" s="1"/>
-      <c r="P83" s="7"/>
-      <c r="Q83" s="2"/>
+      <c r="P83" s="1"/>
+      <c r="Q83" s="7"/>
       <c r="R83" s="2"/>
       <c r="S83" s="2"/>
-      <c r="T83" s="1"/>
-      <c r="U83" s="8"/>
-      <c r="V83" s="2"/>
-      <c r="W83" s="1"/>
-    </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="T83" s="2"/>
+      <c r="U83" s="1"/>
+      <c r="V83" s="8"/>
+      <c r="W83" s="2"/>
+      <c r="X83" s="1"/>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A84" s="11" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="85" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B84" s="20"/>
+    </row>
+    <row r="85" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="21"/>
+      <c r="C85" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="D85" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="E85" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="E85" s="2"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="1"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="7"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="2"/>
       <c r="J85" s="1"/>
-      <c r="K85" s="7"/>
-      <c r="L85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="7"/>
       <c r="M85" s="1"/>
       <c r="N85" s="1"/>
       <c r="O85" s="1"/>
-      <c r="P85" s="7"/>
-      <c r="Q85" s="2"/>
+      <c r="P85" s="1"/>
+      <c r="Q85" s="7"/>
       <c r="R85" s="2"/>
       <c r="S85" s="2"/>
-      <c r="T85" s="1"/>
-      <c r="U85" s="8"/>
-      <c r="V85" s="2"/>
-      <c r="W85" s="1"/>
-    </row>
-    <row r="86" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T85" s="2"/>
+      <c r="U85" s="1"/>
+      <c r="V85" s="8"/>
+      <c r="W85" s="2"/>
+      <c r="X85" s="1"/>
+    </row>
+    <row r="86" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="21"/>
+      <c r="C86" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="D86" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="E86" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="E86" s="2"/>
-      <c r="F86" s="7"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="1"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="7"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="2"/>
       <c r="J86" s="1"/>
-      <c r="K86" s="7"/>
-      <c r="L86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="7"/>
       <c r="M86" s="1"/>
       <c r="N86" s="1"/>
       <c r="O86" s="1"/>
-      <c r="P86" s="7"/>
-      <c r="Q86" s="2"/>
+      <c r="P86" s="1"/>
+      <c r="Q86" s="7"/>
       <c r="R86" s="2"/>
       <c r="S86" s="2"/>
-      <c r="T86" s="1"/>
-      <c r="U86" s="8"/>
-      <c r="V86" s="2"/>
-      <c r="W86" s="1"/>
-    </row>
-    <row r="87" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T86" s="2"/>
+      <c r="U86" s="1"/>
+      <c r="V86" s="8"/>
+      <c r="W86" s="2"/>
+      <c r="X86" s="1"/>
+    </row>
+    <row r="87" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B87" s="2"/>
+      <c r="B87" s="21"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
-      <c r="F87" s="7"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="1"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="7"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="2"/>
       <c r="J87" s="1"/>
-      <c r="K87" s="7"/>
-      <c r="L87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="L87" s="7"/>
       <c r="M87" s="1"/>
       <c r="N87" s="1"/>
       <c r="O87" s="1"/>
-      <c r="P87" s="7"/>
-      <c r="Q87" s="2"/>
+      <c r="P87" s="1"/>
+      <c r="Q87" s="7"/>
       <c r="R87" s="2"/>
       <c r="S87" s="2"/>
-      <c r="T87" s="1"/>
-      <c r="U87" s="8"/>
-      <c r="V87" s="2"/>
-      <c r="W87" s="1"/>
-    </row>
-    <row r="88" spans="1:23" s="4" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="T87" s="2"/>
+      <c r="U87" s="1"/>
+      <c r="V87" s="8"/>
+      <c r="W87" s="2"/>
+      <c r="X87" s="1"/>
+    </row>
+    <row r="88" spans="1:24" s="4" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B88" s="21"/>
+      <c r="C88" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="E88" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="E88" s="2"/>
-      <c r="F88" s="7"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="1"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="7"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="2"/>
       <c r="J88" s="1"/>
-      <c r="K88" s="7"/>
-      <c r="L88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="7"/>
       <c r="M88" s="1"/>
       <c r="N88" s="1"/>
       <c r="O88" s="1"/>
-      <c r="P88" s="7"/>
-      <c r="Q88" s="2"/>
+      <c r="P88" s="1"/>
+      <c r="Q88" s="7"/>
       <c r="R88" s="2"/>
       <c r="S88" s="2"/>
-      <c r="T88" s="1"/>
-      <c r="U88" s="8"/>
-      <c r="V88" s="2"/>
-      <c r="W88" s="1"/>
-    </row>
-    <row r="89" spans="1:23" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="T88" s="2"/>
+      <c r="U88" s="1"/>
+      <c r="V88" s="8"/>
+      <c r="W88" s="2"/>
+      <c r="X88" s="1"/>
+    </row>
+    <row r="89" spans="1:24" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B89" s="2"/>
+      <c r="C89" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="D89" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="E89" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="E89" s="2"/>
-      <c r="F89" s="7"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="1"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="7"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="2"/>
       <c r="J89" s="1"/>
-      <c r="K89" s="7"/>
-      <c r="L89" s="1"/>
+      <c r="K89" s="1"/>
+      <c r="L89" s="7"/>
       <c r="M89" s="1"/>
       <c r="N89" s="1"/>
       <c r="O89" s="1"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="2"/>
+      <c r="P89" s="1"/>
+      <c r="Q89" s="7"/>
       <c r="R89" s="2"/>
       <c r="S89" s="2"/>
-      <c r="T89" s="1"/>
-      <c r="U89" s="8"/>
-      <c r="V89" s="2"/>
-      <c r="W89" s="1"/>
-    </row>
-    <row r="90" spans="1:23" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="T89" s="2"/>
+      <c r="U89" s="1"/>
+      <c r="V89" s="8"/>
+      <c r="W89" s="2"/>
+      <c r="X89" s="1"/>
+    </row>
+    <row r="90" spans="1:24" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B90" s="2"/>
+      <c r="C90" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="D90" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="E90" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E90" s="2"/>
-      <c r="F90" s="7"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="1"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="7"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="2"/>
       <c r="J90" s="1"/>
-      <c r="K90" s="7"/>
-      <c r="L90" s="1"/>
+      <c r="K90" s="1"/>
+      <c r="L90" s="7"/>
       <c r="M90" s="1"/>
       <c r="N90" s="1"/>
       <c r="O90" s="1"/>
-      <c r="P90" s="7"/>
-      <c r="Q90" s="2"/>
+      <c r="P90" s="1"/>
+      <c r="Q90" s="7"/>
       <c r="R90" s="2"/>
       <c r="S90" s="2"/>
-      <c r="T90" s="1"/>
-      <c r="U90" s="8"/>
-      <c r="V90" s="2"/>
-      <c r="W90" s="1"/>
-    </row>
-    <row r="91" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="T90" s="2"/>
+      <c r="U90" s="1"/>
+      <c r="V90" s="8"/>
+      <c r="W90" s="2"/>
+      <c r="X90" s="1"/>
+    </row>
+    <row r="91" spans="1:24" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B91" s="2"/>
+      <c r="C91" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="D91" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="E91" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="E91" s="2" t="s">
+      <c r="F91" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="F91" s="7"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="1"/>
+      <c r="G91" s="7"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="2"/>
       <c r="J91" s="1"/>
-      <c r="K91" s="7"/>
-      <c r="L91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="7"/>
       <c r="M91" s="1"/>
       <c r="N91" s="1"/>
       <c r="O91" s="1"/>
-      <c r="P91" s="7"/>
-      <c r="Q91" s="2"/>
+      <c r="P91" s="1"/>
+      <c r="Q91" s="7"/>
       <c r="R91" s="2"/>
       <c r="S91" s="2"/>
-      <c r="T91" s="1"/>
-      <c r="U91" s="8"/>
-      <c r="V91" s="2"/>
-      <c r="W91" s="1"/>
-    </row>
-    <row r="92" spans="1:23" s="4" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="T91" s="2"/>
+      <c r="U91" s="1"/>
+      <c r="V91" s="8"/>
+      <c r="W91" s="2"/>
+      <c r="X91" s="1"/>
+    </row>
+    <row r="92" spans="1:24" s="4" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="2"/>
+      <c r="C92" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="D92" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="E92" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="E92" s="2" t="s">
+      <c r="F92" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="F92" s="7"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="1"/>
+      <c r="G92" s="7"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="2"/>
       <c r="J92" s="1"/>
-      <c r="K92" s="7"/>
-      <c r="L92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="7"/>
       <c r="M92" s="1"/>
       <c r="N92" s="1"/>
       <c r="O92" s="1"/>
-      <c r="P92" s="7"/>
-      <c r="Q92" s="2"/>
+      <c r="P92" s="1"/>
+      <c r="Q92" s="7"/>
       <c r="R92" s="2"/>
       <c r="S92" s="2"/>
-      <c r="T92" s="1"/>
-      <c r="U92" s="8"/>
-      <c r="V92" s="2"/>
-      <c r="W92" s="1"/>
-    </row>
-    <row r="93" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T92" s="2"/>
+      <c r="U92" s="1"/>
+      <c r="V92" s="8"/>
+      <c r="W92" s="2"/>
+      <c r="X92" s="1"/>
+    </row>
+    <row r="93" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="2"/>
+      <c r="C93" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="D93" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="E93" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="E93" s="2"/>
-      <c r="F93" s="7"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="1"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="7"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="2"/>
       <c r="J93" s="1"/>
-      <c r="K93" s="7"/>
-      <c r="L93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="7"/>
       <c r="M93" s="1"/>
       <c r="N93" s="1"/>
       <c r="O93" s="1"/>
-      <c r="P93" s="7"/>
-      <c r="Q93" s="2"/>
+      <c r="P93" s="1"/>
+      <c r="Q93" s="7"/>
       <c r="R93" s="2"/>
       <c r="S93" s="2"/>
-      <c r="T93" s="1"/>
-      <c r="U93" s="8"/>
-      <c r="V93" s="2"/>
-      <c r="W93" s="1"/>
-    </row>
-    <row r="94" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T93" s="2"/>
+      <c r="U93" s="1"/>
+      <c r="V93" s="8"/>
+      <c r="W93" s="2"/>
+      <c r="X93" s="1"/>
+    </row>
+    <row r="94" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B94" s="2"/>
+      <c r="C94" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="D94" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="E94" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="E94" s="2"/>
-      <c r="F94" s="7"/>
-      <c r="G94" s="1"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="1"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="7"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="2"/>
       <c r="J94" s="1"/>
-      <c r="K94" s="7"/>
-      <c r="L94" s="1"/>
+      <c r="K94" s="1"/>
+      <c r="L94" s="7"/>
       <c r="M94" s="1"/>
       <c r="N94" s="1"/>
       <c r="O94" s="1"/>
-      <c r="P94" s="7"/>
-      <c r="Q94" s="2"/>
+      <c r="P94" s="1"/>
+      <c r="Q94" s="7"/>
       <c r="R94" s="2"/>
       <c r="S94" s="2"/>
-      <c r="T94" s="1"/>
-      <c r="U94" s="8"/>
-      <c r="V94" s="2"/>
-      <c r="W94" s="1"/>
-    </row>
-    <row r="95" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="T94" s="2"/>
+      <c r="U94" s="1"/>
+      <c r="V94" s="8"/>
+      <c r="W94" s="2"/>
+      <c r="X94" s="1"/>
+    </row>
+    <row r="95" spans="1:24" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" s="2"/>
+      <c r="C95" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="D95" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="E95" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="E95" s="2" t="s">
+      <c r="F95" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="F95" s="7"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="1"/>
+      <c r="G95" s="7"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="2"/>
       <c r="J95" s="1"/>
-      <c r="K95" s="7"/>
-      <c r="L95" s="1"/>
+      <c r="K95" s="1"/>
+      <c r="L95" s="7"/>
       <c r="M95" s="1"/>
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
-      <c r="P95" s="7"/>
-      <c r="Q95" s="2"/>
+      <c r="P95" s="1"/>
+      <c r="Q95" s="7"/>
       <c r="R95" s="2"/>
       <c r="S95" s="2"/>
-      <c r="T95" s="1"/>
-      <c r="U95" s="8"/>
-      <c r="V95" s="2"/>
-      <c r="W95" s="1"/>
-    </row>
-    <row r="96" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="T95" s="2"/>
+      <c r="U95" s="1"/>
+      <c r="V95" s="8"/>
+      <c r="W95" s="2"/>
+      <c r="X95" s="1"/>
+    </row>
+    <row r="96" spans="1:24" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B96" s="2"/>
+      <c r="C96" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="D96" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="E96" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="E96" s="2" t="s">
+      <c r="F96" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="F96" s="7"/>
-      <c r="G96" s="1"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="1"/>
+      <c r="G96" s="7"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="2"/>
       <c r="J96" s="1"/>
-      <c r="K96" s="7"/>
-      <c r="L96" s="1"/>
+      <c r="K96" s="1"/>
+      <c r="L96" s="7"/>
       <c r="M96" s="1"/>
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
-      <c r="P96" s="7"/>
-      <c r="Q96" s="2"/>
+      <c r="P96" s="1"/>
+      <c r="Q96" s="7"/>
       <c r="R96" s="2"/>
       <c r="S96" s="2"/>
-      <c r="T96" s="1"/>
-      <c r="U96" s="8"/>
-      <c r="V96" s="2"/>
-      <c r="W96" s="1"/>
-    </row>
-    <row r="97" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="T96" s="2"/>
+      <c r="U96" s="1"/>
+      <c r="V96" s="8"/>
+      <c r="W96" s="2"/>
+      <c r="X96" s="1"/>
+    </row>
+    <row r="97" spans="1:24" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B97" s="2"/>
+      <c r="C97" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="D97" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="E97" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="E97" s="2" t="s">
+      <c r="F97" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="F97" s="7"/>
-      <c r="G97" s="1"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="1"/>
+      <c r="G97" s="7"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="2"/>
       <c r="J97" s="1"/>
-      <c r="K97" s="7"/>
-      <c r="L97" s="1"/>
+      <c r="K97" s="1"/>
+      <c r="L97" s="7"/>
       <c r="M97" s="1"/>
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
-      <c r="P97" s="7"/>
-      <c r="Q97" s="2"/>
+      <c r="P97" s="1"/>
+      <c r="Q97" s="7"/>
       <c r="R97" s="2"/>
       <c r="S97" s="2"/>
-      <c r="T97" s="1"/>
-      <c r="U97" s="8"/>
-      <c r="V97" s="2"/>
-      <c r="W97" s="1"/>
-    </row>
-    <row r="98" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T97" s="2"/>
+      <c r="U97" s="1"/>
+      <c r="V97" s="8"/>
+      <c r="W97" s="2"/>
+      <c r="X97" s="1"/>
+    </row>
+    <row r="98" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B98" s="2"/>
+      <c r="C98" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="D98" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="E98" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="E98" s="2"/>
-      <c r="F98" s="7"/>
-      <c r="G98" s="1"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="1"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="7"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="2"/>
       <c r="J98" s="1"/>
-      <c r="K98" s="7"/>
-      <c r="L98" s="1"/>
+      <c r="K98" s="1"/>
+      <c r="L98" s="7"/>
       <c r="M98" s="1"/>
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
-      <c r="P98" s="7"/>
-      <c r="Q98" s="2"/>
+      <c r="P98" s="1"/>
+      <c r="Q98" s="7"/>
       <c r="R98" s="2"/>
       <c r="S98" s="2"/>
-      <c r="T98" s="1"/>
-      <c r="U98" s="8"/>
-      <c r="V98" s="2"/>
-      <c r="W98" s="1"/>
-    </row>
-    <row r="99" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="T98" s="2"/>
+      <c r="U98" s="1"/>
+      <c r="V98" s="8"/>
+      <c r="W98" s="2"/>
+      <c r="X98" s="1"/>
+    </row>
+    <row r="99" spans="1:24" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B99" s="21"/>
+      <c r="C99" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="D99" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="E99" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E99" s="2"/>
-      <c r="F99" s="7"/>
-      <c r="G99" s="1"/>
-      <c r="H99" s="2"/>
-      <c r="I99" s="1"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="7"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="2"/>
       <c r="J99" s="1"/>
-      <c r="K99" s="7"/>
-      <c r="L99" s="1"/>
+      <c r="K99" s="1"/>
+      <c r="L99" s="7"/>
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
-      <c r="P99" s="7"/>
-      <c r="Q99" s="2"/>
+      <c r="P99" s="1"/>
+      <c r="Q99" s="7"/>
       <c r="R99" s="2"/>
       <c r="S99" s="2"/>
-      <c r="T99" s="1"/>
-      <c r="U99" s="8"/>
-      <c r="V99" s="2"/>
-      <c r="W99" s="1"/>
-    </row>
-    <row r="100" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T99" s="2"/>
+      <c r="U99" s="1"/>
+      <c r="V99" s="8"/>
+      <c r="W99" s="2"/>
+      <c r="X99" s="1"/>
+    </row>
+    <row r="100" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="15" t="s">
         <v>689</v>
       </c>
-      <c r="B100" s="2"/>
+      <c r="B100" s="21"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
-      <c r="F100" s="7"/>
-      <c r="G100" s="1"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="1"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="7"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="2"/>
       <c r="J100" s="1"/>
-      <c r="K100" s="7"/>
-      <c r="L100" s="1"/>
+      <c r="K100" s="1"/>
+      <c r="L100" s="7"/>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
       <c r="O100" s="1"/>
-      <c r="P100" s="7"/>
-      <c r="Q100" s="2"/>
+      <c r="P100" s="1"/>
+      <c r="Q100" s="7"/>
       <c r="R100" s="2"/>
       <c r="S100" s="2"/>
-      <c r="T100" s="1"/>
-      <c r="U100" s="8"/>
-      <c r="V100" s="2"/>
-      <c r="W100" s="1"/>
-    </row>
-    <row r="101" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T100" s="2"/>
+      <c r="U100" s="1"/>
+      <c r="V100" s="8"/>
+      <c r="W100" s="2"/>
+      <c r="X100" s="1"/>
+    </row>
+    <row r="101" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="B101" s="21"/>
+      <c r="C101" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="D101" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="E101" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="E101" s="2"/>
-      <c r="F101" s="7"/>
-      <c r="G101" s="1"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="1"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="7"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="2"/>
       <c r="J101" s="1"/>
-      <c r="K101" s="7"/>
-      <c r="L101" s="1"/>
+      <c r="K101" s="1"/>
+      <c r="L101" s="7"/>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
-      <c r="P101" s="7"/>
-      <c r="Q101" s="2"/>
+      <c r="P101" s="1"/>
+      <c r="Q101" s="7"/>
       <c r="R101" s="2"/>
       <c r="S101" s="2"/>
-      <c r="T101" s="1"/>
-      <c r="U101" s="8"/>
-      <c r="V101" s="2"/>
-      <c r="W101" s="1"/>
-    </row>
-    <row r="102" spans="1:23" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T101" s="2"/>
+      <c r="U101" s="1"/>
+      <c r="V101" s="8"/>
+      <c r="W101" s="2"/>
+      <c r="X101" s="1"/>
+    </row>
+    <row r="102" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B102" s="21"/>
+      <c r="C102" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="D102" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="D102" s="2" t="s">
+      <c r="E102" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="E102" s="2"/>
-      <c r="F102" s="7"/>
-      <c r="G102" s="1"/>
-      <c r="H102" s="2"/>
-      <c r="I102" s="1"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="7"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="2"/>
       <c r="J102" s="1"/>
-      <c r="K102" s="7"/>
-      <c r="L102" s="1"/>
+      <c r="K102" s="1"/>
+      <c r="L102" s="7"/>
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
       <c r="O102" s="1"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="2"/>
+      <c r="P102" s="1"/>
+      <c r="Q102" s="7"/>
       <c r="R102" s="2"/>
       <c r="S102" s="2"/>
-      <c r="T102" s="1"/>
-      <c r="U102" s="8"/>
-      <c r="V102" s="2"/>
-      <c r="W102" s="1"/>
-    </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="T102" s="2"/>
+      <c r="U102" s="1"/>
+      <c r="V102" s="8"/>
+      <c r="W102" s="2"/>
+      <c r="X102" s="1"/>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A103" s="15" t="s">
         <v>692</v>
       </c>
-      <c r="D103" s="2"/>
+      <c r="B103" s="21"/>
       <c r="E103" s="2"/>
-    </row>
-    <row r="104" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F103" s="2"/>
+    </row>
+    <row r="104" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B104" s="21"/>
+      <c r="C104" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="D104" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="E104" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="E104" s="2"/>
-    </row>
-    <row r="105" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="F104" s="2"/>
+    </row>
+    <row r="105" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="B105" s="21"/>
+      <c r="C105" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="D105" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="E105" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="E105" s="2" t="s">
+      <c r="F105" s="2" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A106" s="15" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="107" spans="1:23" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B106" s="21"/>
+    </row>
+    <row r="107" spans="1:24" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="B107" s="21"/>
+      <c r="C107" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="D107" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="E107" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="E107" s="2" t="s">
+      <c r="F107" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="G107" s="1"/>
-      <c r="H107" s="2"/>
-      <c r="I107" s="1"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="2"/>
       <c r="J107" s="1"/>
-      <c r="L107" s="1"/>
+      <c r="K107" s="1"/>
       <c r="M107" s="1"/>
       <c r="N107" s="1"/>
       <c r="O107" s="1"/>
-      <c r="Q107" s="2"/>
+      <c r="P107" s="1"/>
       <c r="R107" s="2"/>
       <c r="S107" s="2"/>
-      <c r="T107" s="1"/>
-      <c r="U107" s="8"/>
-      <c r="V107" s="2"/>
-      <c r="W107" s="1"/>
-    </row>
-    <row r="108" spans="1:23" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="T107" s="2"/>
+      <c r="U107" s="1"/>
+      <c r="V107" s="8"/>
+      <c r="W107" s="2"/>
+      <c r="X107" s="1"/>
+    </row>
+    <row r="108" spans="1:24" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A108" s="2"/>
-      <c r="B108" s="2" t="s">
+      <c r="B108" s="2"/>
+      <c r="C108" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="D108" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="D108" s="2"/>
       <c r="E108" s="2"/>
-      <c r="G108" s="1"/>
-      <c r="H108" s="2"/>
-      <c r="I108" s="1"/>
+      <c r="F108" s="2"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="2"/>
       <c r="J108" s="1"/>
-      <c r="L108" s="1"/>
+      <c r="K108" s="1"/>
       <c r="M108" s="1"/>
       <c r="N108" s="1"/>
       <c r="O108" s="1"/>
-      <c r="Q108" s="2"/>
+      <c r="P108" s="1"/>
       <c r="R108" s="2"/>
       <c r="S108" s="2"/>
-      <c r="T108" s="1"/>
-      <c r="U108" s="8"/>
-      <c r="V108" s="2"/>
-      <c r="W108" s="1"/>
-    </row>
-    <row r="109" spans="1:23" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="T108" s="2"/>
+      <c r="U108" s="1"/>
+      <c r="V108" s="8"/>
+      <c r="W108" s="2"/>
+      <c r="X108" s="1"/>
+    </row>
+    <row r="109" spans="1:24" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A109" s="2"/>
-      <c r="B109" s="2" t="s">
+      <c r="B109" s="2"/>
+      <c r="C109" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="D109" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="D109" s="2"/>
       <c r="E109" s="2"/>
-      <c r="G109" s="1"/>
-      <c r="H109" s="2"/>
-      <c r="I109" s="1"/>
+      <c r="F109" s="2"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="2"/>
       <c r="J109" s="1"/>
-      <c r="L109" s="1"/>
+      <c r="K109" s="1"/>
       <c r="M109" s="1"/>
       <c r="N109" s="1"/>
       <c r="O109" s="1"/>
-      <c r="Q109" s="2"/>
+      <c r="P109" s="1"/>
       <c r="R109" s="2"/>
       <c r="S109" s="2"/>
-      <c r="T109" s="1"/>
-      <c r="U109" s="8"/>
-      <c r="V109" s="2"/>
-      <c r="W109" s="1"/>
-    </row>
-    <row r="110" spans="1:23" s="7" customFormat="1" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="T109" s="2"/>
+      <c r="U109" s="1"/>
+      <c r="V109" s="8"/>
+      <c r="W109" s="2"/>
+      <c r="X109" s="1"/>
+    </row>
+    <row r="110" spans="1:24" s="7" customFormat="1" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A110" s="2"/>
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="2"/>
+      <c r="C110" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="D110" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="D110" s="2"/>
       <c r="E110" s="2"/>
-      <c r="G110" s="1"/>
-      <c r="H110" s="2"/>
-      <c r="I110" s="1"/>
+      <c r="F110" s="2"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="2"/>
       <c r="J110" s="1"/>
-      <c r="L110" s="1"/>
+      <c r="K110" s="1"/>
       <c r="M110" s="1"/>
       <c r="N110" s="1"/>
       <c r="O110" s="1"/>
-      <c r="Q110" s="2"/>
+      <c r="P110" s="1"/>
       <c r="R110" s="2"/>
       <c r="S110" s="2"/>
-      <c r="T110" s="1"/>
-      <c r="U110" s="8"/>
-      <c r="V110" s="2"/>
-      <c r="W110" s="1"/>
-    </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="T110" s="2"/>
+      <c r="U110" s="1"/>
+      <c r="V110" s="8"/>
+      <c r="W110" s="2"/>
+      <c r="X110" s="1"/>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A111" s="11" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="112" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B111" s="11"/>
+    </row>
+    <row r="112" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>203</v>
       </c>
       <c r="B112" s="2"/>
-      <c r="C112" s="2" t="s">
+      <c r="C112" s="2"/>
+      <c r="D112" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D112" s="2" t="s">
+      <c r="E112" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="E112" s="2" t="s">
+      <c r="F112" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="G112" s="1"/>
-      <c r="H112" s="2"/>
-      <c r="I112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="2"/>
       <c r="J112" s="1"/>
-      <c r="L112" s="1"/>
+      <c r="K112" s="1"/>
       <c r="M112" s="1"/>
       <c r="N112" s="1"/>
       <c r="O112" s="1"/>
-      <c r="Q112" s="2"/>
+      <c r="P112" s="1"/>
       <c r="R112" s="2"/>
       <c r="S112" s="2"/>
-      <c r="T112" s="1"/>
-      <c r="U112" s="8"/>
-      <c r="V112" s="2"/>
-      <c r="W112" s="1"/>
-    </row>
-    <row r="113" spans="1:23" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="T112" s="2"/>
+      <c r="U112" s="1"/>
+      <c r="V112" s="8"/>
+      <c r="W112" s="2"/>
+      <c r="X112" s="1"/>
+    </row>
+    <row r="113" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="B113" s="2"/>
+      <c r="C113" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="D113" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D113" s="2" t="s">
+      <c r="E113" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="E113" s="2" t="s">
+      <c r="F113" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="G113" s="1"/>
-      <c r="H113" s="2"/>
-      <c r="I113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="2"/>
       <c r="J113" s="1"/>
-      <c r="L113" s="1"/>
+      <c r="K113" s="1"/>
       <c r="M113" s="1"/>
       <c r="N113" s="1"/>
       <c r="O113" s="1"/>
-      <c r="Q113" s="2"/>
+      <c r="P113" s="1"/>
       <c r="R113" s="2"/>
       <c r="S113" s="2"/>
-      <c r="T113" s="1"/>
-      <c r="U113" s="8"/>
-      <c r="V113" s="2"/>
-      <c r="W113" s="1"/>
-    </row>
-    <row r="114" spans="1:23" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="T113" s="2"/>
+      <c r="U113" s="1"/>
+      <c r="V113" s="8"/>
+      <c r="W113" s="2"/>
+      <c r="X113" s="1"/>
+    </row>
+    <row r="114" spans="1:24" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B114" s="2"/>
+      <c r="C114" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="D114" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="E114" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E114" s="2" t="s">
+      <c r="F114" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="G114" s="1"/>
-      <c r="H114" s="2"/>
-      <c r="I114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="2"/>
       <c r="J114" s="1"/>
-      <c r="L114" s="1"/>
+      <c r="K114" s="1"/>
       <c r="M114" s="1"/>
       <c r="N114" s="1"/>
       <c r="O114" s="1"/>
-      <c r="Q114" s="2"/>
+      <c r="P114" s="1"/>
       <c r="R114" s="2"/>
       <c r="S114" s="2"/>
-      <c r="T114" s="1"/>
-      <c r="U114" s="8"/>
-      <c r="V114" s="2"/>
-      <c r="W114" s="1"/>
-    </row>
-    <row r="115" spans="1:23" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="T114" s="2"/>
+      <c r="U114" s="1"/>
+      <c r="V114" s="8"/>
+      <c r="W114" s="2"/>
+      <c r="X114" s="1"/>
+    </row>
+    <row r="115" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B115" s="21"/>
+      <c r="C115" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="D115" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D115" s="2" t="s">
+      <c r="E115" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E115" s="2" t="s">
+      <c r="F115" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="G115" s="1"/>
-      <c r="H115" s="2"/>
-      <c r="I115" s="1"/>
+      <c r="H115" s="1"/>
+      <c r="I115" s="2"/>
       <c r="J115" s="1"/>
-      <c r="L115" s="1"/>
+      <c r="K115" s="1"/>
       <c r="M115" s="1"/>
       <c r="N115" s="1"/>
       <c r="O115" s="1"/>
-      <c r="Q115" s="2"/>
+      <c r="P115" s="1"/>
       <c r="R115" s="2"/>
       <c r="S115" s="2"/>
-      <c r="T115" s="1"/>
-      <c r="U115" s="8"/>
-      <c r="V115" s="2"/>
-      <c r="W115" s="1"/>
-    </row>
-    <row r="116" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T115" s="2"/>
+      <c r="U115" s="1"/>
+      <c r="V115" s="8"/>
+      <c r="W115" s="2"/>
+      <c r="X115" s="1"/>
+    </row>
+    <row r="116" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="21"/>
+      <c r="C116" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="D116" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D116" s="2" t="s">
+      <c r="E116" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="E116" s="2" t="s">
+      <c r="F116" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="G116" s="1"/>
-      <c r="H116" s="2"/>
-      <c r="I116" s="1"/>
+      <c r="H116" s="1"/>
+      <c r="I116" s="2"/>
       <c r="J116" s="1"/>
-      <c r="L116" s="1"/>
+      <c r="K116" s="1"/>
       <c r="M116" s="1"/>
       <c r="N116" s="1"/>
       <c r="O116" s="1"/>
-      <c r="Q116" s="2"/>
+      <c r="P116" s="1"/>
       <c r="R116" s="2"/>
       <c r="S116" s="2"/>
-      <c r="T116" s="1"/>
-      <c r="U116" s="8"/>
-      <c r="V116" s="2"/>
-      <c r="W116" s="1"/>
-    </row>
-    <row r="117" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="T116" s="2"/>
+      <c r="U116" s="1"/>
+      <c r="V116" s="8"/>
+      <c r="W116" s="2"/>
+      <c r="X116" s="1"/>
+    </row>
+    <row r="117" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B117" s="21"/>
+      <c r="C117" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="D117" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="E117" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="E117" s="2" t="s">
+      <c r="F117" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="G117" s="1"/>
-      <c r="H117" s="2"/>
-      <c r="I117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="2"/>
       <c r="J117" s="1"/>
-      <c r="L117" s="1"/>
+      <c r="K117" s="1"/>
       <c r="M117" s="1"/>
       <c r="N117" s="1"/>
       <c r="O117" s="1"/>
-      <c r="Q117" s="2"/>
+      <c r="P117" s="1"/>
       <c r="R117" s="2"/>
       <c r="S117" s="2"/>
-      <c r="T117" s="1"/>
-      <c r="U117" s="8"/>
-      <c r="V117" s="2"/>
-      <c r="W117" s="1"/>
-    </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="T117" s="2"/>
+      <c r="U117" s="1"/>
+      <c r="V117" s="8"/>
+      <c r="W117" s="2"/>
+      <c r="X117" s="1"/>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A118" s="15" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="119" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
+        <v>961</v>
+      </c>
+      <c r="B118" s="21"/>
+    </row>
+    <row r="119" spans="1:24" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="B119" s="20"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E119" s="32" t="s">
         <v>940</v>
       </c>
-      <c r="B119" s="1"/>
-      <c r="C119" s="2" t="s">
+      <c r="F119" s="32" t="s">
         <v>942</v>
       </c>
-      <c r="D119" s="32" t="s">
-        <v>941</v>
-      </c>
-      <c r="E119" s="32" t="s">
+    </row>
+    <row r="120" spans="1:24" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
         <v>943</v>
       </c>
-    </row>
-    <row r="120" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A120" s="2" t="s">
+      <c r="B120" s="2"/>
+      <c r="D120" s="25" t="s">
+        <v>945</v>
+      </c>
+      <c r="E120" s="32" t="s">
         <v>944</v>
       </c>
-      <c r="C120" s="25" t="s">
+      <c r="F120" s="32" t="s">
         <v>946</v>
       </c>
-      <c r="D120" s="32" t="s">
-        <v>945</v>
-      </c>
-      <c r="E120" s="32" t="s">
+    </row>
+    <row r="121" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A121" s="25" t="s">
         <v>947</v>
       </c>
-    </row>
-    <row r="121" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A121" s="25" t="s">
+      <c r="B121" s="25"/>
+      <c r="D121" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="E121" s="32" t="s">
         <v>948</v>
       </c>
-      <c r="C121" s="2" t="s">
+    </row>
+    <row r="122" spans="1:24" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
         <v>952</v>
       </c>
-      <c r="D121" s="32" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="122" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
+      <c r="B122" s="2"/>
+      <c r="D122" s="33" t="s">
+        <v>954</v>
+      </c>
+      <c r="E122" s="32" t="s">
         <v>953</v>
       </c>
-      <c r="C122" s="33" t="s">
+      <c r="F122" s="32" t="s">
         <v>955</v>
       </c>
-      <c r="D122" s="32" t="s">
-        <v>954</v>
-      </c>
-      <c r="E122" s="32" t="s">
+    </row>
+    <row r="123" spans="1:24" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
         <v>956</v>
       </c>
-    </row>
-    <row r="123" spans="1:23" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A123" s="2" t="s">
+      <c r="B123" s="2"/>
+      <c r="D123" s="25" t="s">
+        <v>958</v>
+      </c>
+      <c r="E123" s="32" t="s">
         <v>957</v>
       </c>
-      <c r="C123" s="25" t="s">
+      <c r="F123" s="32" t="s">
         <v>959</v>
       </c>
-      <c r="D123" s="32" t="s">
-        <v>958</v>
-      </c>
-      <c r="E123" s="32" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B143" s="1"/>
+    </row>
+    <row r="143" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
-    </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B144" s="1"/>
+      <c r="F143" s="1"/>
+    </row>
+    <row r="144" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
-    </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B145" s="1"/>
+      <c r="F144" s="1"/>
+    </row>
+    <row r="145" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
-    </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B146" s="1"/>
+      <c r="F145" s="1"/>
+    </row>
+    <row r="146" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
-    </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B147" s="1"/>
+      <c r="F146" s="1"/>
+    </row>
+    <row r="147" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
-    </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B148" s="1"/>
+      <c r="F147" s="1"/>
+    </row>
+    <row r="148" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
-    </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B149" s="1"/>
+      <c r="F148" s="1"/>
+    </row>
+    <row r="149" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
-    </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B150" s="1"/>
+      <c r="F149" s="1"/>
+    </row>
+    <row r="150" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
-    </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B151" s="1"/>
+      <c r="F150" s="1"/>
+    </row>
+    <row r="151" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C151" s="1"/>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
+      <c r="F151" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="17" type="noConversion"/>
@@ -25636,10 +25888,10 @@
         <v>436</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D49" s="17" t="s">
         <v>437</v>
@@ -25695,7 +25947,7 @@
         <v>427</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>428</v>
@@ -25730,7 +25982,7 @@
         <v>39</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>334</v>
@@ -25765,7 +26017,7 @@
         <v>120</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>430</v>
@@ -25958,7 +26210,7 @@
         <v>330</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C59" s="17" t="s">
         <v>333</v>
@@ -25993,7 +26245,7 @@
         <v>442</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>443</v>
@@ -26028,7 +26280,7 @@
         <v>421</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>419</v>
@@ -26063,7 +26315,7 @@
         <v>349</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>354</v>
@@ -26439,7 +26691,7 @@
         <v>358</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>338</v>
@@ -26748,7 +27000,7 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -26861,7 +27113,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -26875,10 +27127,10 @@
         <v>13</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
@@ -26902,12 +27154,12 @@
         <v>753</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>816</v>
+        <v>1091</v>
       </c>
       <c r="C25" s="25" t="s">
         <v>751</v>
@@ -27094,7 +27346,7 @@
         <v>814</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="D40" s="24"/>
     </row>
@@ -27106,7 +27358,7 @@
         <v>814</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="D41" s="24" t="s">
         <v>784</v>
@@ -27803,76 +28055,76 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B9" s="21"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -27907,7 +28159,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -27918,111 +28170,111 @@
         <v>375</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="D23" s="32" t="s">
         <v>982</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>984</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>986</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>985</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>987</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>991</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>993</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>989</v>
+      </c>
+      <c r="D26" s="32" t="s">
         <v>988</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>990</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="D28" s="32" t="s">
         <v>994</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>996</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>995</v>
       </c>
       <c r="E28" s="24"/>
     </row>
     <row r="29" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>999</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>996</v>
+      </c>
+      <c r="E29" s="32" t="s">
         <v>998</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>997</v>
-      </c>
-      <c r="E29" s="32" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="28" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -28030,18 +28282,18 @@
     </row>
     <row r="31" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>916</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>915</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>917</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="34" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -28052,140 +28304,140 @@
         <v>232</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C34" s="25"/>
       <c r="D34" s="32"/>
     </row>
     <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>938</v>
+      </c>
+      <c r="D36" s="32" t="s">
         <v>937</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>939</v>
-      </c>
-      <c r="D36" s="32" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C37" s="25"/>
       <c r="D37" s="32"/>
     </row>
     <row r="38" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>974</v>
+      </c>
+      <c r="D38" s="32" t="s">
         <v>932</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C38" s="25" t="s">
-        <v>975</v>
-      </c>
-      <c r="D38" s="32" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="D39" s="32" t="s">
         <v>972</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>974</v>
-      </c>
-      <c r="D39" s="32" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D40" s="32" t="s">
         <v>1010</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C40" s="25" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D40" s="32" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="D41" s="32"/>
     </row>
     <row r="42" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>935</v>
+      </c>
+      <c r="D42" s="32" t="s">
         <v>934</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>936</v>
-      </c>
-      <c r="D42" s="32" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C43" s="25"/>
       <c r="D43" s="32"/>
     </row>
     <row r="44" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="D44" s="32" t="s">
         <v>979</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>981</v>
-      </c>
-      <c r="D44" s="32" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C45" s="25"/>
       <c r="D45" s="32"/>
@@ -28193,88 +28445,88 @@
     </row>
     <row r="46" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D46" s="32" t="s">
         <v>1001</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D46" s="32" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="D47" s="32" t="s">
         <v>976</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D47" s="32" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="D48" s="32" t="s">
         <v>969</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>971</v>
-      </c>
-      <c r="D48" s="32" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D49" s="32" t="s">
         <v>1004</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D49" s="32" t="s">
-        <v>1005</v>
       </c>
       <c r="E49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D50" s="32" t="s">
         <v>1007</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>1009</v>
-      </c>
-      <c r="D50" s="32" t="s">
-        <v>1008</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>927</v>
+      </c>
+      <c r="D51" s="32" t="s">
         <v>926</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C51" s="25" t="s">
-        <v>928</v>
-      </c>
-      <c r="D51" s="32" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
@@ -29617,72 +29869,72 @@
     </row>
     <row r="21" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>1044</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>1046</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D23" s="32" t="s">
         <v>1050</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1052</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>1053</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>1056</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1058</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">

--- a/4 четверть_13_JavaScript_sugarJS.xlsx
+++ b/4 четверть_13_JavaScript_sugarJS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222BE0F7-74AC-4F78-AA53-464D5A9E87C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686A9354-FAAC-43A9-9B90-5BCFEC381F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sugarjs" sheetId="20" r:id="rId1"/>
@@ -2514,24 +2514,6 @@
 This is most commonly used when you only need to check a single field that can ensure the object's uniqueness (such as an id field). If map is not passed, then objects will be deep checked for equality. Supports deep properties.</t>
   </si>
   <si>
-    <t>[1,2,2,3].unique() [1, 2, 3]
-[{a:'a'},{a:'a'}].unique() [{"a":"a"}]
-const users = [
-  {id: 1, name: 'Alice'},
-  {id: 2, name: 'Bob'},
-  {id: 1, name: 'Alice Clone'}, // Дубликат по ID
-  {id: 3, name: 'Charlie'}
-];
-users.unique(function(user) {
-  return user.id;
-});
-[
-  {id: 1, name: 'Alice'},      // Сохранен первый
-  {id: 2, name: 'Bob'},
-  {id: 3, name: 'Charlie'}
-]</t>
-  </si>
-  <si>
     <t>Merges multiple arrays together. This method "zips up" smaller arrays into one large whose elements are "all elements at index 0", "all elements at index 1", etc. Useful when you have associated data that is split over separated arrays. If the arrays passed have more elements than the original array, they will be discarded. If they have fewer elements, the missing elements will filled with null.</t>
   </si>
   <si>
@@ -18507,17 +18489,46 @@
       <t>//["Harry", "Holly"]</t>
     </r>
   </si>
+  <si>
+    <t>[1,2,2,3].unique() [1, 2, 3]
+[{a:'a'},{a:'a'}].unique() [{"a":"a"}]
+const users = [
+  {id: 1, name: 'Alice'},
+  {id: 2, name: 'Bob'},
+  {id: 1, name: 'Alice Clone'}, // Дубликат по ID
+  {id: 3, name: 'Charlie'}
+];
+users.unique('UserMail')
+users.unique({isUserMail: true})
+users.unique({TelegramId: /^\d+$/})
+users.unique(function(user) {
+  return user.id;
+});
+[
+  {id: 1, name: 'Alice'},      // Сохранен первый
+  {id: 2, name: 'Bob'},
+  {id: 3, name: 'Charlie'}
+]</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -18841,9 +18852,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -18854,50 +18865,50 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -18906,42 +18917,45 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -19388,7 +19402,7 @@
     </row>
     <row r="4" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -19412,11 +19426,11 @@
     </row>
     <row r="5" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -19438,13 +19452,13 @@
     </row>
     <row r="6" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -19466,7 +19480,7 @@
     </row>
     <row r="7" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -19492,7 +19506,7 @@
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -20492,17 +20506,17 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -20512,22 +20526,22 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -20537,7 +20551,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -20547,25 +20561,25 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C16" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="D16" s="17" t="s">
         <v>350</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -20603,7 +20617,7 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -20621,16 +20635,16 @@
     </row>
     <row r="20" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="36" t="s">
+        <v>905</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>906</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>907</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="1"/>
@@ -20645,7 +20659,7 @@
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="9"/>
@@ -20658,10 +20672,10 @@
         <v>0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>1</v>
@@ -20672,153 +20686,153 @@
     </row>
     <row r="23" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>1012</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>967</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>1013</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>1017</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>967</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>1018</v>
-      </c>
       <c r="E24" s="32" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>1063</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>1065</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>1064</v>
-      </c>
       <c r="E25" s="32" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D26" s="32" t="s">
         <v>964</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>967</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D26" s="32" t="s">
+      <c r="E26" s="32" t="s">
         <v>965</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D31" s="32" t="s">
         <v>1063</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>1071</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>1068</v>
-      </c>
-      <c r="D31" s="32" t="s">
-        <v>1064</v>
-      </c>
       <c r="E31" s="32" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>901</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="D32" s="17" t="s">
         <v>436</v>
-      </c>
-      <c r="B32" s="27" t="s">
-        <v>902</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>903</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
@@ -20826,10 +20840,10 @@
         <v>95</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>96</v>
@@ -20837,33 +20851,33 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>672</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -20871,10 +20885,10 @@
     <row r="37" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>673</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>674</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -20882,10 +20896,10 @@
     <row r="38" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>676</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -20895,7 +20909,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="2"/>
@@ -20906,7 +20920,7 @@
         <v>27</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>29</v>
@@ -20944,7 +20958,7 @@
         <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>74</v>
@@ -20958,7 +20972,7 @@
         <v>13</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>111</v>
@@ -21029,7 +21043,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C50" s="10"/>
       <c r="D50" s="10"/>
@@ -21040,10 +21054,10 @@
         <v>15</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>1088</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>1089</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>14</v>
@@ -21054,10 +21068,10 @@
         <v>39</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>43</v>
@@ -21071,13 +21085,13 @@
         <v>16</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -21085,13 +21099,13 @@
         <v>21</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
@@ -21099,13 +21113,13 @@
         <v>120</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C55" s="14" t="s">
         <v>121</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>26</v>
@@ -21116,19 +21130,19 @@
         <v>123</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C56" s="14" t="s">
         <v>124</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E56" s="14"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D57" s="10"/>
     </row>
@@ -21137,7 +21151,7 @@
         <v>22</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>19</v>
@@ -21151,10 +21165,10 @@
         <v>42</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>44</v>
@@ -21168,7 +21182,7 @@
         <v>76</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>78</v>
@@ -21182,7 +21196,7 @@
         <v>91</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>93</v>
@@ -21196,13 +21210,13 @@
         <v>45</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>26</v>
@@ -21213,7 +21227,7 @@
         <v>105</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>94</v>
@@ -21227,7 +21241,7 @@
         <v>110</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C64" s="14" t="s">
         <v>108</v>
@@ -21238,7 +21252,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D65" s="14"/>
     </row>
@@ -21247,9 +21261,9 @@
         <v>134</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C66" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="C66" s="38" t="s">
         <v>136</v>
       </c>
       <c r="D66" s="14" t="s">
@@ -21258,46 +21272,46 @@
     </row>
     <row r="67" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D67" s="14" t="s">
         <v>158</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D68" s="14" t="s">
         <v>161</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D68" s="14" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="144" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C69" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C69" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="D69" s="14" t="s">
         <v>163</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="2"/>
@@ -21308,7 +21322,7 @@
         <v>2</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>7</v>
@@ -21325,7 +21339,7 @@
         <v>6</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>9</v>
@@ -21350,7 +21364,7 @@
         <v>48</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>47</v>
@@ -21364,7 +21378,7 @@
         <v>48</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>90</v>
@@ -21375,10 +21389,10 @@
         <v>143</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C76" s="37" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="D76" s="14" t="s">
         <v>144</v>
@@ -21390,10 +21404,10 @@
         <v>64</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>65</v>
@@ -21401,7 +21415,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -21413,7 +21427,7 @@
         <v>63</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>61</v>
@@ -21430,10 +21444,10 @@
         <v>95</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>96</v>
@@ -21444,10 +21458,10 @@
         <v>40</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>41</v>
@@ -21500,7 +21514,7 @@
         <v>32</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>30</v>
@@ -21514,7 +21528,7 @@
         <v>49</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>122</v>
@@ -21528,28 +21542,28 @@
     </row>
     <row r="88" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C88" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C88" s="14" t="s">
-        <v>156</v>
-      </c>
       <c r="D88" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E88" s="14"/>
     </row>
-    <row r="89" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>151</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>153</v>
+        <v>1093</v>
       </c>
       <c r="D89" s="14" t="s">
         <v>152</v>
@@ -21561,7 +21575,7 @@
         <v>66</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>68</v>
@@ -21578,7 +21592,7 @@
         <v>70</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>71</v>
@@ -21592,18 +21606,18 @@
         <v>73</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D93" s="14"/>
     </row>
@@ -21612,7 +21626,7 @@
         <v>79</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>81</v>
@@ -21626,7 +21640,7 @@
         <v>137</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C95" s="24" t="s">
         <v>139</v>
@@ -21640,7 +21654,7 @@
         <v>147</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>149</v>
@@ -21652,7 +21666,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
@@ -21660,7 +21674,7 @@
         <v>104</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C98" s="14" t="s">
         <v>107</v>
@@ -21674,7 +21688,7 @@
         <v>103</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>101</v>
@@ -21691,7 +21705,7 @@
         <v>98</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>99</v>
@@ -21708,7 +21722,7 @@
         <v>113</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C101" s="14" t="s">
         <v>115</v>
@@ -21725,7 +21739,7 @@
         <v>117</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C102" s="14" t="s">
         <v>119</v>
@@ -21742,7 +21756,7 @@
         <v>23</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>25</v>
@@ -21759,7 +21773,7 @@
         <v>33</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>35</v>
@@ -21776,7 +21790,7 @@
         <v>140</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>142</v>
@@ -21788,7 +21802,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C106" s="10"/>
       <c r="D106" s="2"/>
@@ -21799,7 +21813,7 @@
         <v>130</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C107" s="14" t="s">
         <v>125</v>
@@ -21814,7 +21828,7 @@
         <v>126</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C108" s="14" t="s">
         <v>128</v>
@@ -22024,80 +22038,80 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B2" s="11"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B3" s="15"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B4" s="15"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B5" s="15"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B6" s="15"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B7" s="15"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B8" s="15"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B9" s="23"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B10" s="15"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B13" s="15"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B14" s="11"/>
     </row>
@@ -22109,19 +22123,19 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B16" s="15"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B17" s="15"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B18" s="11"/>
     </row>
@@ -22152,7 +22166,7 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="1"/>
@@ -22161,22 +22175,22 @@
     </row>
     <row r="23" spans="1:24" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B23" s="21"/>
       <c r="C23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="27" t="s">
+        <v>909</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>910</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="24" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="2"/>
@@ -22201,17 +22215,17 @@
     </row>
     <row r="25" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>603</v>
-      </c>
       <c r="E25" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F25" s="2"/>
       <c r="H25" s="1"/>
@@ -22232,20 +22246,20 @@
     </row>
     <row r="26" spans="1:24" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>639</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>640</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="2"/>
@@ -22265,17 +22279,17 @@
     </row>
     <row r="27" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="F27" s="2"/>
       <c r="H27" s="1"/>
@@ -22298,13 +22312,13 @@
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F28" s="2"/>
       <c r="H28" s="1"/>
@@ -22327,13 +22341,13 @@
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F29" s="2"/>
       <c r="H29" s="1"/>
@@ -22356,13 +22370,13 @@
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="F30" s="2"/>
       <c r="H30" s="1"/>
@@ -22385,13 +22399,13 @@
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F31" s="2"/>
       <c r="H31" s="1"/>
@@ -22414,13 +22428,13 @@
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="F32" s="2"/>
       <c r="H32" s="1"/>
@@ -22443,13 +22457,13 @@
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="F33" s="2"/>
       <c r="H33" s="1"/>
@@ -22470,20 +22484,20 @@
     </row>
     <row r="34" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>510</v>
-      </c>
       <c r="E34" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="2"/>
@@ -22503,13 +22517,13 @@
     </row>
     <row r="35" spans="1:24" s="7" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="22" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F35" s="4"/>
       <c r="H35" s="1"/>
@@ -22530,7 +22544,7 @@
     </row>
     <row r="36" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="2"/>
@@ -22555,13 +22569,13 @@
     </row>
     <row r="37" spans="1:24" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="22" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="F37" s="4"/>
       <c r="H37" s="1"/>
@@ -22582,13 +22596,13 @@
     </row>
     <row r="38" spans="1:24" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="22" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="F38" s="4"/>
       <c r="H38" s="1"/>
@@ -22609,13 +22623,13 @@
     </row>
     <row r="39" spans="1:24" s="7" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="22" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F39" s="4"/>
       <c r="H39" s="1"/>
@@ -22636,13 +22650,13 @@
     </row>
     <row r="40" spans="1:24" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="22" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="F40" s="4"/>
       <c r="H40" s="1"/>
@@ -22663,13 +22677,13 @@
     </row>
     <row r="41" spans="1:24" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="22" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F41" s="4"/>
       <c r="H41" s="1"/>
@@ -22690,13 +22704,13 @@
     </row>
     <row r="42" spans="1:24" s="7" customFormat="1" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="22" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F42" s="4"/>
       <c r="H42" s="1"/>
@@ -22717,7 +22731,7 @@
     </row>
     <row r="43" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="2"/>
@@ -22742,17 +22756,17 @@
     </row>
     <row r="44" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>275</v>
-      </c>
       <c r="E44" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F44" s="2"/>
       <c r="H44" s="1"/>
@@ -22773,17 +22787,17 @@
     </row>
     <row r="45" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>279</v>
-      </c>
       <c r="E45" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F45" s="2"/>
       <c r="H45" s="1"/>
@@ -22804,17 +22818,17 @@
     </row>
     <row r="46" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>492</v>
-      </c>
       <c r="E46" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F46" s="2"/>
       <c r="H46" s="1"/>
@@ -22835,17 +22849,17 @@
     </row>
     <row r="47" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>496</v>
-      </c>
       <c r="E47" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F47" s="2"/>
       <c r="H47" s="1"/>
@@ -22866,17 +22880,17 @@
     </row>
     <row r="48" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>607</v>
-      </c>
       <c r="E48" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F48" s="2"/>
       <c r="H48" s="1"/>
@@ -22897,7 +22911,7 @@
     </row>
     <row r="49" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B49" s="21"/>
       <c r="C49" s="2"/>
@@ -22922,20 +22936,20 @@
     </row>
     <row r="50" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>231</v>
-      </c>
       <c r="E50" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="2"/>
@@ -22955,20 +22969,20 @@
     </row>
     <row r="51" spans="1:24" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D51" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>623</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>624</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="2"/>
@@ -22988,20 +23002,20 @@
     </row>
     <row r="52" spans="1:24" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D52" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>628</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="2"/>
@@ -23021,20 +23035,20 @@
     </row>
     <row r="53" spans="1:24" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="E53" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>632</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>633</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="2"/>
@@ -23054,20 +23068,20 @@
     </row>
     <row r="54" spans="1:24" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>636</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>637</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="2"/>
@@ -23087,7 +23101,7 @@
     </row>
     <row r="55" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="15" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -23112,22 +23126,22 @@
     </row>
     <row r="56" spans="1:24" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="E56" s="2" t="s">
+      <c r="F56" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="2"/>
@@ -23147,19 +23161,19 @@
     </row>
     <row r="57" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>502</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>503</v>
       </c>
       <c r="F57" s="2"/>
       <c r="H57" s="1"/>
@@ -23180,19 +23194,19 @@
     </row>
     <row r="58" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>580</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="7"/>
@@ -23216,43 +23230,43 @@
     </row>
     <row r="59" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>584</v>
       </c>
       <c r="F59" s="2"/>
     </row>
     <row r="60" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>608</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>609</v>
       </c>
       <c r="F60" s="2"/>
     </row>
     <row r="61" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -23277,20 +23291,20 @@
     </row>
     <row r="62" spans="1:24" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="E62" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F62" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>679</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="2"/>
@@ -23310,11 +23324,11 @@
     </row>
     <row r="63" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
@@ -23337,11 +23351,11 @@
     </row>
     <row r="64" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
@@ -23364,11 +23378,11 @@
     </row>
     <row r="65" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
@@ -23391,11 +23405,11 @@
     </row>
     <row r="66" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
@@ -23418,14 +23432,14 @@
     </row>
     <row r="67" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
@@ -23447,11 +23461,11 @@
     </row>
     <row r="68" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
@@ -23474,11 +23488,11 @@
     </row>
     <row r="69" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
@@ -23501,14 +23515,14 @@
     </row>
     <row r="70" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>261</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
@@ -23530,17 +23544,17 @@
     </row>
     <row r="71" spans="1:24" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>272</v>
-      </c>
       <c r="E71" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F71" s="2"/>
       <c r="H71" s="1"/>
@@ -23561,17 +23575,17 @@
     </row>
     <row r="72" spans="1:24" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>599</v>
-      </c>
       <c r="E72" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="F72" s="2"/>
       <c r="H72" s="1"/>
@@ -23592,20 +23606,20 @@
     </row>
     <row r="73" spans="1:24" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="D73" s="27" t="s">
         <v>898</v>
       </c>
-      <c r="D73" s="27" t="s">
-        <v>899</v>
-      </c>
       <c r="E73" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="2"/>
@@ -23625,17 +23639,17 @@
     </row>
     <row r="74" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>592</v>
-      </c>
       <c r="E74" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F74" s="2"/>
       <c r="H74" s="1"/>
@@ -23656,17 +23670,17 @@
     </row>
     <row r="75" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B75" s="21"/>
       <c r="C75" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>596</v>
-      </c>
       <c r="E75" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F75" s="2"/>
       <c r="H75" s="1"/>
@@ -23687,7 +23701,7 @@
     </row>
     <row r="76" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="15" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B76" s="21"/>
       <c r="C76" s="2"/>
@@ -23716,13 +23730,13 @@
       </c>
       <c r="B77" s="21"/>
       <c r="C77" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>485</v>
-      </c>
       <c r="E77" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F77" s="2"/>
       <c r="H77" s="1"/>
@@ -23743,7 +23757,7 @@
     </row>
     <row r="78" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="15" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B78" s="21"/>
       <c r="C78" s="2"/>
@@ -23768,17 +23782,17 @@
     </row>
     <row r="79" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B79" s="21"/>
       <c r="C79" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>488</v>
-      </c>
       <c r="E79" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F79" s="2"/>
       <c r="H79" s="1"/>
@@ -23799,23 +23813,23 @@
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B80" s="20"/>
     </row>
     <row r="81" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B81" s="21"/>
       <c r="C81" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="E81" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F81" s="2"/>
       <c r="H81" s="1"/>
@@ -23836,7 +23850,7 @@
     </row>
     <row r="82" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="15" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B82" s="21"/>
       <c r="C82" s="2"/>
@@ -23861,17 +23875,17 @@
     </row>
     <row r="83" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B83" s="21"/>
       <c r="C83" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>518</v>
-      </c>
       <c r="E83" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="7"/>
@@ -23895,23 +23909,23 @@
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A84" s="11" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B84" s="20"/>
     </row>
     <row r="85" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B85" s="21"/>
       <c r="C85" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>522</v>
-      </c>
       <c r="E85" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="7"/>
@@ -23935,17 +23949,17 @@
     </row>
     <row r="86" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B86" s="21"/>
       <c r="C86" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>525</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="7"/>
@@ -23997,17 +24011,17 @@
     </row>
     <row r="88" spans="1:24" s="4" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B88" s="21"/>
       <c r="C88" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="D88" s="2" t="s">
-        <v>529</v>
-      </c>
       <c r="E88" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="7"/>
@@ -24031,17 +24045,17 @@
     </row>
     <row r="89" spans="1:24" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="D89" s="2" t="s">
-        <v>533</v>
-      </c>
       <c r="E89" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="7"/>
@@ -24065,17 +24079,17 @@
     </row>
     <row r="90" spans="1:24" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="D90" s="2" t="s">
-        <v>537</v>
-      </c>
       <c r="E90" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="7"/>
@@ -24099,20 +24113,20 @@
     </row>
     <row r="91" spans="1:24" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="1"/>
@@ -24135,20 +24149,20 @@
     </row>
     <row r="92" spans="1:24" s="4" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="E92" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F92" s="2" t="s">
         <v>544</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>545</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="1"/>
@@ -24171,17 +24185,17 @@
     </row>
     <row r="93" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="7"/>
@@ -24205,17 +24219,17 @@
     </row>
     <row r="94" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="7"/>
@@ -24239,20 +24253,20 @@
     </row>
     <row r="95" spans="1:24" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="F95" s="2" t="s">
         <v>559</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="1"/>
@@ -24275,20 +24289,20 @@
     </row>
     <row r="96" spans="1:24" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="E96" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>567</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>568</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="1"/>
@@ -24311,20 +24325,20 @@
     </row>
     <row r="97" spans="1:24" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="E97" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F97" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>553</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="1"/>
@@ -24347,17 +24361,17 @@
     </row>
     <row r="98" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="7"/>
@@ -24381,17 +24395,17 @@
     </row>
     <row r="99" spans="1:24" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B99" s="21"/>
       <c r="C99" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="7"/>
@@ -24415,7 +24429,7 @@
     </row>
     <row r="100" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="15" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B100" s="21"/>
       <c r="C100" s="2"/>
@@ -24443,17 +24457,17 @@
     </row>
     <row r="101" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B101" s="21"/>
       <c r="C101" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F101" s="2"/>
       <c r="G101" s="7"/>
@@ -24477,17 +24491,17 @@
     </row>
     <row r="102" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B102" s="21"/>
       <c r="C102" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="D102" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D102" s="2" t="s">
-        <v>578</v>
-      </c>
       <c r="E102" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="7"/>
@@ -24511,7 +24525,7 @@
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A103" s="15" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B103" s="21"/>
       <c r="E103" s="2"/>
@@ -24519,60 +24533,60 @@
     </row>
     <row r="104" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B104" s="21"/>
       <c r="C104" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="D104" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="E104" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F104" s="2"/>
     </row>
     <row r="105" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B105" s="21"/>
       <c r="C105" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="D105" s="2" t="s">
-        <v>620</v>
-      </c>
       <c r="E105" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F105" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A106" s="15" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B106" s="21"/>
     </row>
     <row r="107" spans="1:24" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B107" s="21"/>
       <c r="C107" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="D107" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>667</v>
-      </c>
       <c r="F107" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H107" s="1"/>
       <c r="I107" s="2"/>
@@ -24594,10 +24608,10 @@
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="D108" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>672</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
@@ -24621,10 +24635,10 @@
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="D109" s="2" t="s">
         <v>673</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>674</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
@@ -24648,10 +24662,10 @@
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="D110" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>676</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
@@ -24673,24 +24687,24 @@
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A111" s="11" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B111" s="11"/>
     </row>
     <row r="112" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H112" s="1"/>
       <c r="I112" s="2"/>
@@ -24710,20 +24724,20 @@
     </row>
     <row r="113" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D113" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D113" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="E113" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H113" s="1"/>
       <c r="I113" s="2"/>
@@ -24743,20 +24757,20 @@
     </row>
     <row r="114" spans="1:24" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B114" s="2"/>
       <c r="C114" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D114" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="D114" s="2" t="s">
-        <v>225</v>
-      </c>
       <c r="E114" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H114" s="1"/>
       <c r="I114" s="2"/>
@@ -24776,20 +24790,20 @@
     </row>
     <row r="115" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B115" s="21"/>
       <c r="C115" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D115" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="D115" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="E115" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H115" s="1"/>
       <c r="I115" s="2"/>
@@ -24809,20 +24823,20 @@
     </row>
     <row r="116" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B116" s="21"/>
       <c r="C116" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D116" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D116" s="2" t="s">
+      <c r="E116" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E116" s="2" t="s">
+      <c r="F116" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="H116" s="1"/>
       <c r="I116" s="2"/>
@@ -24842,20 +24856,20 @@
     </row>
     <row r="117" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B117" s="21"/>
       <c r="C117" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D117" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="E117" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H117" s="1"/>
       <c r="I117" s="2"/>
@@ -24875,81 +24889,81 @@
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A118" s="15" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B118" s="21"/>
     </row>
     <row r="119" spans="1:24" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B119" s="20"/>
       <c r="C119" s="1"/>
       <c r="D119" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="E119" s="32" t="s">
+        <v>939</v>
+      </c>
+      <c r="F119" s="32" t="s">
         <v>941</v>
-      </c>
-      <c r="E119" s="32" t="s">
-        <v>940</v>
-      </c>
-      <c r="F119" s="32" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="120" spans="1:24" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B120" s="2"/>
       <c r="D120" s="25" t="s">
+        <v>944</v>
+      </c>
+      <c r="E120" s="32" t="s">
+        <v>943</v>
+      </c>
+      <c r="F120" s="32" t="s">
         <v>945</v>
-      </c>
-      <c r="E120" s="32" t="s">
-        <v>944</v>
-      </c>
-      <c r="F120" s="32" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="121" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A121" s="25" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B121" s="25"/>
       <c r="D121" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E121" s="32" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="122" spans="1:24" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B122" s="2"/>
       <c r="D122" s="33" t="s">
+        <v>953</v>
+      </c>
+      <c r="E122" s="32" t="s">
+        <v>952</v>
+      </c>
+      <c r="F122" s="32" t="s">
         <v>954</v>
-      </c>
-      <c r="E122" s="32" t="s">
-        <v>953</v>
-      </c>
-      <c r="F122" s="32" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="123" spans="1:24" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B123" s="2"/>
       <c r="D123" s="25" t="s">
+        <v>957</v>
+      </c>
+      <c r="E123" s="32" t="s">
+        <v>956</v>
+      </c>
+      <c r="F123" s="32" t="s">
         <v>958</v>
-      </c>
-      <c r="E123" s="32" t="s">
-        <v>957</v>
-      </c>
-      <c r="F123" s="32" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="143" spans="3:6" x14ac:dyDescent="0.3">
@@ -25007,7 +25021,7 @@
       <c r="F151" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -25053,12 +25067,12 @@
   <sheetData>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -25068,13 +25082,13 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B5" s="20"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B6" s="21"/>
     </row>
@@ -25086,41 +25100,41 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B9" s="20"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B10" s="20"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B13" s="21"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B14" s="20"/>
     </row>
@@ -25149,7 +25163,7 @@
     </row>
     <row r="18" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -25157,37 +25171,37 @@
     </row>
     <row r="19" spans="1:23" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="F19" s="7"/>
     </row>
     <row r="20" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F20" s="7"/>
     </row>
     <row r="21" spans="1:23" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="F21" s="7"/>
     </row>
@@ -25199,115 +25213,115 @@
     </row>
     <row r="23" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D23" s="17" t="s">
         <v>432</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>433</v>
       </c>
       <c r="F23" s="7"/>
     </row>
     <row r="24" spans="1:23" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>474</v>
-      </c>
       <c r="D24" s="17" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F24" s="7"/>
     </row>
     <row r="25" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:23" s="2" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="C26" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:23" s="2" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>340</v>
-      </c>
       <c r="E27" s="17" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F27" s="7"/>
     </row>
     <row r="28" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E28" s="17" t="s">
         <v>380</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>381</v>
       </c>
       <c r="F28" s="7"/>
     </row>
     <row r="29" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F29" s="7"/>
     </row>
     <row r="30" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -25334,19 +25348,19 @@
     </row>
     <row r="31" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="1"/>
@@ -25371,10 +25385,10 @@
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="7"/>
@@ -25400,10 +25414,10 @@
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>295</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="7"/>
@@ -25429,10 +25443,10 @@
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="7"/>
@@ -25458,10 +25472,10 @@
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="7"/>
@@ -25485,19 +25499,19 @@
     </row>
     <row r="36" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="E36" s="17" t="s">
         <v>404</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>405</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="1"/>
@@ -25522,10 +25536,10 @@
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="7"/>
@@ -25551,10 +25565,10 @@
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>295</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="7"/>
@@ -25580,10 +25594,10 @@
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="7"/>
@@ -25609,10 +25623,10 @@
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="7"/>
@@ -25636,19 +25650,19 @@
     </row>
     <row r="41" spans="1:23" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>303</v>
-      </c>
       <c r="E41" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="1"/>
@@ -25673,10 +25687,10 @@
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="7"/>
@@ -25702,10 +25716,10 @@
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>295</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="7"/>
@@ -25731,10 +25745,10 @@
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="7"/>
@@ -25760,10 +25774,10 @@
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="7"/>
@@ -25787,16 +25801,16 @@
     </row>
     <row r="46" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="7"/>
@@ -25820,16 +25834,16 @@
     </row>
     <row r="47" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>329</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="7"/>
@@ -25853,16 +25867,16 @@
     </row>
     <row r="48" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D48" s="17" t="s">
         <v>436</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>437</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="1"/>
@@ -25885,16 +25899,16 @@
     </row>
     <row r="49" spans="1:28" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B49" s="27" t="s">
+        <v>900</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="D49" s="17" t="s">
         <v>436</v>
-      </c>
-      <c r="B49" s="27" t="s">
-        <v>901</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>904</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>437</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="1"/>
@@ -25917,7 +25931,7 @@
     </row>
     <row r="50" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="15" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -25944,16 +25958,16 @@
     </row>
     <row r="51" spans="1:28" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B51" s="36" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B51" s="36" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>429</v>
       </c>
       <c r="E51" s="2"/>
       <c r="G51" s="1"/>
@@ -25982,16 +25996,16 @@
         <v>39</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E52" s="35" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="1"/>
@@ -26017,16 +26031,16 @@
         <v>120</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>431</v>
-      </c>
       <c r="E53" s="17" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="1"/>
@@ -26082,10 +26096,10 @@
         <v>13</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="1"/>
@@ -26108,16 +26122,16 @@
     </row>
     <row r="56" spans="1:28" s="4" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="7"/>
@@ -26141,16 +26155,16 @@
     </row>
     <row r="57" spans="1:28" s="4" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="7"/>
@@ -26174,16 +26188,16 @@
     </row>
     <row r="58" spans="1:28" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="7"/>
@@ -26207,19 +26221,19 @@
     </row>
     <row r="59" spans="1:28" s="4" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A59" s="17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="1"/>
@@ -26242,19 +26256,19 @@
     </row>
     <row r="60" spans="1:28" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>444</v>
-      </c>
       <c r="E60" s="17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="1"/>
@@ -26277,19 +26291,19 @@
     </row>
     <row r="61" spans="1:28" s="4" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C61" s="2" t="s">
+      <c r="E61" s="17" t="s">
         <v>419</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="E61" s="17" t="s">
-        <v>420</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="1"/>
@@ -26312,22 +26326,22 @@
     </row>
     <row r="62" spans="1:28" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E62" s="2"/>
     </row>
     <row r="63" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -26357,13 +26371,13 @@
         <v>23</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="7"/>
@@ -26387,19 +26401,19 @@
     </row>
     <row r="65" spans="1:28" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>313</v>
-      </c>
       <c r="C65" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="1"/>
@@ -26424,11 +26438,11 @@
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="1"/>
@@ -26454,13 +26468,13 @@
         <v>140</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E67" s="2"/>
       <c r="G67" s="1"/>
@@ -26486,19 +26500,19 @@
     </row>
     <row r="68" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="69" spans="1:28" ht="72" x14ac:dyDescent="0.3">
@@ -26506,97 +26520,97 @@
         <v>98</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>400</v>
-      </c>
       <c r="E69" s="17" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="70" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C70" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>412</v>
-      </c>
       <c r="E70" s="17" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="71" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A71" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
     </row>
     <row r="72" spans="1:28" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>356</v>
       </c>
       <c r="E72" s="2"/>
     </row>
     <row r="73" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C73" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>447</v>
       </c>
       <c r="E73" s="2"/>
     </row>
     <row r="74" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A74" s="15" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="C75" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="E75" s="2"/>
     </row>
     <row r="76" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -26605,58 +26619,58 @@
     </row>
     <row r="77" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>379</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>462</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>463</v>
       </c>
       <c r="E78" s="2"/>
     </row>
     <row r="79" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>385</v>
-      </c>
       <c r="E79" s="17" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="80" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A80" s="2"/>
       <c r="B80" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>390</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
@@ -26664,10 +26678,10 @@
     <row r="81" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A81" s="2"/>
       <c r="B81" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>392</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
@@ -26675,26 +26689,26 @@
     <row r="82" spans="1:28" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A82" s="2"/>
       <c r="B82" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
     </row>
     <row r="83" spans="1:28" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="84" spans="1:28" s="7" customFormat="1" ht="144" x14ac:dyDescent="0.3">
@@ -26702,16 +26716,16 @@
         <v>113</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="2"/>
@@ -26736,19 +26750,19 @@
     </row>
     <row r="85" spans="1:28" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E85" s="17" t="s">
         <v>342</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E85" s="17" t="s">
-        <v>343</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="2"/>
@@ -26773,7 +26787,7 @@
     </row>
     <row r="86" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -26802,155 +26816,155 @@
     </row>
     <row r="87" spans="1:28" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" s="11" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="89" spans="1:28" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C89" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="E89" s="2"/>
     </row>
     <row r="90" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A90" s="2"/>
       <c r="C90" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>283</v>
       </c>
       <c r="E90" s="2"/>
     </row>
     <row r="91" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A91" s="2"/>
       <c r="C91" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="E91" s="2"/>
     </row>
     <row r="92" spans="1:28" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A92" s="2"/>
       <c r="C92" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="E92" s="2"/>
     </row>
     <row r="93" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A93" s="2"/>
       <c r="C93" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>289</v>
       </c>
       <c r="E93" s="2"/>
     </row>
     <row r="94" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E94" s="17" t="s">
         <v>455</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="E94" s="17" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="95" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2"/>
       <c r="C95" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>283</v>
       </c>
       <c r="E95" s="2"/>
     </row>
     <row r="96" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2"/>
       <c r="C96" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="E96" s="2"/>
     </row>
     <row r="97" spans="1:5" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A97" s="2"/>
       <c r="C97" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="E97" s="2"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="2"/>
       <c r="C98" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>289</v>
       </c>
       <c r="E98" s="2"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="11" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E100" s="2"/>
     </row>
@@ -27000,91 +27014,91 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B9" s="21"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B10" s="20"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B11" s="20"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B14" s="21"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B15" s="20"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B16" s="20"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B17" s="20"/>
     </row>
@@ -27113,7 +27127,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -27121,37 +27135,37 @@
     </row>
     <row r="22" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C23" s="25"/>
       <c r="D23" s="24"/>
     </row>
     <row r="24" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C24" s="25" t="s">
         <v>749</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>750</v>
-      </c>
       <c r="D24" s="24" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
@@ -27159,596 +27173,596 @@
         <v>82</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C25" s="25" t="s">
+        <v>750</v>
+      </c>
+      <c r="D25" s="24" t="s">
         <v>751</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C26" s="25"/>
       <c r="D26" s="24"/>
     </row>
     <row r="27" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C27" s="25" t="s">
         <v>743</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="C27" s="25" t="s">
+      <c r="D27" s="24" t="s">
         <v>744</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>795</v>
+      </c>
+      <c r="D28" s="27" t="s">
         <v>794</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>796</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>726</v>
+      </c>
+      <c r="D29" s="24" t="s">
         <v>725</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>727</v>
-      </c>
-      <c r="D29" s="24" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C30" s="25"/>
       <c r="D30" s="24"/>
     </row>
     <row r="31" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>864</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>865</v>
+      </c>
+      <c r="E37" s="27" t="s">
         <v>863</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>865</v>
-      </c>
-      <c r="D37" s="27" t="s">
-        <v>866</v>
-      </c>
-      <c r="E37" s="27" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>781</v>
+      </c>
+      <c r="D39" s="24" t="s">
         <v>780</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="C39" s="25" t="s">
-        <v>782</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="D40" s="24"/>
     </row>
     <row r="41" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D41" s="24" t="s">
         <v>783</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="C41" s="25" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D41" s="24" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C42" s="25" t="s">
         <v>770</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>771</v>
-      </c>
       <c r="D42" s="24" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C44" s="25" t="s">
+        <v>747</v>
+      </c>
+      <c r="D44" s="24" t="s">
         <v>746</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>748</v>
-      </c>
-      <c r="D44" s="24" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>799</v>
+      </c>
+      <c r="D45" s="24" t="s">
         <v>785</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="C45" s="25" t="s">
-        <v>800</v>
-      </c>
-      <c r="D45" s="24" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>840</v>
+      </c>
+      <c r="D47" s="27" t="s">
         <v>838</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="C47" s="25" t="s">
-        <v>841</v>
-      </c>
-      <c r="D47" s="27" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>762</v>
+      </c>
+      <c r="D48" s="24" t="s">
         <v>761</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>763</v>
-      </c>
-      <c r="D48" s="24" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>765</v>
+      </c>
+      <c r="D49" s="24" t="s">
         <v>764</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>766</v>
-      </c>
-      <c r="D49" s="24" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>768</v>
+      </c>
+      <c r="D50" s="24" t="s">
         <v>767</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>769</v>
-      </c>
-      <c r="D50" s="24" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="27"/>
     </row>
     <row r="52" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="B52" s="27" t="s">
         <v>825</v>
       </c>
-      <c r="B52" s="27" t="s">
-        <v>826</v>
-      </c>
       <c r="C52" s="25" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B54" s="27" t="s">
         <v>828</v>
       </c>
-      <c r="B54" s="27" t="s">
-        <v>829</v>
-      </c>
       <c r="C54" s="25" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D54" s="27" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>810</v>
+      </c>
+      <c r="C55" s="26" t="s">
         <v>713</v>
       </c>
-      <c r="B55" s="27" t="s">
-        <v>811</v>
-      </c>
-      <c r="C55" s="26" t="s">
+      <c r="D55" s="24" t="s">
         <v>714</v>
-      </c>
-      <c r="D55" s="24" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>822</v>
+      </c>
+      <c r="D57" s="27" t="s">
         <v>821</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="C57" s="25" t="s">
-        <v>823</v>
-      </c>
-      <c r="D57" s="27" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>870</v>
+      </c>
+      <c r="D59" s="27" t="s">
         <v>869</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="C59" s="25" t="s">
+      <c r="E59" s="27" t="s">
         <v>871</v>
-      </c>
-      <c r="D59" s="27" t="s">
-        <v>870</v>
-      </c>
-      <c r="E59" s="27" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>807</v>
+      </c>
+      <c r="D60" s="27" t="s">
         <v>805</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>808</v>
-      </c>
-      <c r="D60" s="27" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>702</v>
+      </c>
+      <c r="D61" s="24" t="s">
         <v>698</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>703</v>
-      </c>
-      <c r="D61" s="24" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C62" s="25"/>
       <c r="D62" s="27"/>
     </row>
     <row r="63" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>797</v>
+      </c>
+      <c r="D63" s="27" t="s">
         <v>791</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="C63" s="25" t="s">
-        <v>798</v>
-      </c>
-      <c r="D63" s="27" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>874</v>
+      </c>
+      <c r="D64" s="27" t="s">
         <v>873</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="E64" s="27" t="s">
         <v>876</v>
-      </c>
-      <c r="C64" s="25" t="s">
-        <v>875</v>
-      </c>
-      <c r="D64" s="27" t="s">
-        <v>874</v>
-      </c>
-      <c r="E64" s="27" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C65" s="25"/>
       <c r="D65" s="24"/>
     </row>
     <row r="66" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="C66" s="25" t="s">
+        <v>703</v>
+      </c>
+      <c r="D66" s="24" t="s">
         <v>695</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>888</v>
-      </c>
-      <c r="C66" s="25" t="s">
-        <v>704</v>
-      </c>
-      <c r="D66" s="24" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>732</v>
+      </c>
+      <c r="D67" s="24" t="s">
         <v>730</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="C67" s="25" t="s">
-        <v>733</v>
-      </c>
-      <c r="D67" s="24" t="s">
+      <c r="E67" s="24" t="s">
         <v>731</v>
-      </c>
-      <c r="E67" s="24" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="C68" s="26" t="s">
+        <v>701</v>
+      </c>
+      <c r="D68" s="24" t="s">
         <v>700</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="C68" s="26" t="s">
-        <v>702</v>
-      </c>
-      <c r="D68" s="24" t="s">
-        <v>701</v>
-      </c>
       <c r="E68" s="24" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="C69" s="25" t="s">
         <v>706</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="C69" s="25" t="s">
-        <v>707</v>
-      </c>
       <c r="D69" s="24" t="s">
+        <v>709</v>
+      </c>
+      <c r="E69" s="24" t="s">
         <v>710</v>
-      </c>
-      <c r="E69" s="24" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>798</v>
+      </c>
+      <c r="D70" s="27" t="s">
         <v>788</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="C70" s="25" t="s">
-        <v>799</v>
-      </c>
-      <c r="D70" s="27" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="28" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B71" s="27"/>
       <c r="C71" s="26"/>
@@ -27756,91 +27770,91 @@
     </row>
     <row r="72" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="C72" s="25" t="s">
+        <v>856</v>
+      </c>
+      <c r="D72" s="27" t="s">
         <v>851</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="C72" s="25" t="s">
-        <v>857</v>
-      </c>
-      <c r="D72" s="27" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="C73" s="25" t="s">
+        <v>855</v>
+      </c>
+      <c r="D73" s="27" t="s">
         <v>853</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>862</v>
-      </c>
-      <c r="C73" s="25" t="s">
-        <v>856</v>
-      </c>
-      <c r="D73" s="27" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>854</v>
+      </c>
+      <c r="D74" s="27" t="s">
         <v>802</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>860</v>
-      </c>
-      <c r="C74" s="25" t="s">
-        <v>855</v>
-      </c>
-      <c r="D74" s="27" t="s">
+      <c r="E74" s="27" t="s">
         <v>803</v>
-      </c>
-      <c r="E74" s="27" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>857</v>
+      </c>
+      <c r="D75" s="24" t="s">
         <v>776</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>859</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>858</v>
-      </c>
-      <c r="D75" s="24" t="s">
+      <c r="E75" s="24" t="s">
         <v>777</v>
-      </c>
-      <c r="E75" s="24" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C76" s="25"/>
       <c r="D76" s="24"/>
     </row>
     <row r="77" spans="1:5" ht="216" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C77" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="D77" s="24" t="s">
         <v>741</v>
-      </c>
-      <c r="D77" s="24" t="s">
-        <v>742</v>
       </c>
       <c r="E77" s="24"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C78" s="25"/>
       <c r="D78" s="27"/>
@@ -27848,75 +27862,75 @@
     </row>
     <row r="79" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="C79" s="25" t="s">
+        <v>847</v>
+      </c>
+      <c r="D79" s="27" t="s">
         <v>842</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="C79" s="25" t="s">
-        <v>848</v>
-      </c>
-      <c r="D79" s="27" t="s">
-        <v>843</v>
-      </c>
       <c r="E79" s="27" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E80" s="27" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D82" s="27" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E82" s="27" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="28" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C83" s="25"/>
       <c r="D83" s="24"/>
@@ -27924,35 +27938,35 @@
     </row>
     <row r="84" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="C84" s="25" t="s">
+        <v>718</v>
+      </c>
+      <c r="D84" s="24" t="s">
         <v>717</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="C84" s="25" t="s">
-        <v>719</v>
-      </c>
-      <c r="D84" s="24" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="C85" s="25" t="s">
         <v>721</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="C85" s="25" t="s">
+      <c r="D85" s="24" t="s">
         <v>722</v>
-      </c>
-      <c r="D85" s="24" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -27960,16 +27974,16 @@
     </row>
     <row r="87" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="C87" s="25" t="s">
+        <v>735</v>
+      </c>
+      <c r="D87" s="24" t="s">
         <v>734</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="C87" s="25" t="s">
-        <v>736</v>
-      </c>
-      <c r="D87" s="24" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -28055,76 +28069,76 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B9" s="21"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -28159,7 +28173,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -28167,114 +28181,114 @@
     </row>
     <row r="22" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="D23" s="32" t="s">
         <v>981</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>983</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>985</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>984</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>986</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>990</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>992</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>988</v>
+      </c>
+      <c r="D26" s="32" t="s">
         <v>987</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>989</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="D28" s="32" t="s">
         <v>993</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>994</v>
       </c>
       <c r="E28" s="24"/>
     </row>
     <row r="29" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>998</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>995</v>
+      </c>
+      <c r="E29" s="32" t="s">
         <v>997</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>999</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>996</v>
-      </c>
-      <c r="E29" s="32" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="28" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -28282,18 +28296,18 @@
     </row>
     <row r="31" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>915</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>914</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>916</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="34" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -28301,143 +28315,143 @@
     </row>
     <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C34" s="25"/>
       <c r="D34" s="32"/>
     </row>
     <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>937</v>
+      </c>
+      <c r="D36" s="32" t="s">
         <v>936</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>938</v>
-      </c>
-      <c r="D36" s="32" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C37" s="25"/>
       <c r="D37" s="32"/>
     </row>
     <row r="38" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>973</v>
+      </c>
+      <c r="D38" s="32" t="s">
         <v>931</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C38" s="25" t="s">
-        <v>974</v>
-      </c>
-      <c r="D38" s="32" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="D39" s="32" t="s">
         <v>971</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>973</v>
-      </c>
-      <c r="D39" s="32" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D40" s="32" t="s">
         <v>1009</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C40" s="25" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D40" s="32" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="D41" s="32"/>
     </row>
     <row r="42" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>934</v>
+      </c>
+      <c r="D42" s="32" t="s">
         <v>933</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>935</v>
-      </c>
-      <c r="D42" s="32" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C43" s="25"/>
       <c r="D43" s="32"/>
     </row>
     <row r="44" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="D44" s="32" t="s">
         <v>978</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="D44" s="32" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C45" s="25"/>
       <c r="D45" s="32"/>
@@ -28445,88 +28459,88 @@
     </row>
     <row r="46" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D46" s="32" t="s">
         <v>1000</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>1002</v>
-      </c>
-      <c r="D46" s="32" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="D47" s="32" t="s">
         <v>975</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>977</v>
-      </c>
-      <c r="D47" s="32" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="D48" s="32" t="s">
         <v>968</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>970</v>
-      </c>
-      <c r="D48" s="32" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D49" s="32" t="s">
         <v>1003</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D49" s="32" t="s">
-        <v>1004</v>
       </c>
       <c r="E49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D50" s="32" t="s">
         <v>1006</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D50" s="32" t="s">
-        <v>1007</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>926</v>
+      </c>
+      <c r="D51" s="32" t="s">
         <v>925</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C51" s="25" t="s">
-        <v>927</v>
-      </c>
-      <c r="D51" s="32" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
@@ -29869,72 +29883,72 @@
     </row>
     <row r="21" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>1043</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>1045</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D23" s="32" t="s">
         <v>1049</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D24" s="32" t="s">
         <v>1052</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D25" s="32" t="s">
         <v>1055</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1057</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">

--- a/4 четверть_13_JavaScript_sugarJS.xlsx
+++ b/4 четверть_13_JavaScript_sugarJS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686A9354-FAAC-43A9-9B90-5BCFEC381F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE26399-7131-44D8-932C-91C05AA6019B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21205,7 +21205,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>45</v>
       </c>
@@ -24691,7 +24691,7 @@
       </c>
       <c r="B111" s="11"/>
     </row>
-    <row r="112" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>202</v>
       </c>
@@ -25265,7 +25265,7 @@
       </c>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:23" s="2" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" s="2" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>338</v>
       </c>
@@ -25991,7 +25991,7 @@
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
     </row>
-    <row r="52" spans="1:28" s="4" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:28" s="4" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>39</v>
       </c>
@@ -26026,7 +26026,7 @@
       <c r="V52" s="2"/>
       <c r="W52" s="1"/>
     </row>
-    <row r="53" spans="1:28" s="4" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:28" s="4" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>120</v>
       </c>
@@ -26219,7 +26219,7 @@
       <c r="V58" s="2"/>
       <c r="W58" s="1"/>
     </row>
-    <row r="59" spans="1:28" s="4" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:28" s="4" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A59" s="17" t="s">
         <v>329</v>
       </c>

--- a/4 четверть_13_JavaScript_sugarJS.xlsx
+++ b/4 четверть_13_JavaScript_sugarJS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE26399-7131-44D8-932C-91C05AA6019B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB174D05-A0C6-4EB0-BB96-CF438A32CBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sugarjs" sheetId="20" r:id="rId1"/>
@@ -1444,12 +1444,6 @@
 [1,2,1].lastIndexOf(7) -1</t>
   </si>
   <si>
-    <t>[3,2,2].least() 3
-['fe','fo','fum'].least(true, 'length') fum
-users.least('profile.type') &lt;User:Harry&gt;
-users.least(true, 'profile.type') [&lt;User:Harry&gt;, &lt;User:Georgia&gt;]</t>
-  </si>
-  <si>
     <t>map(map,[context])</t>
   </si>
   <si>
@@ -1826,12 +1820,6 @@
       </rPr>
       <t>["fee", "fum"]</t>
     </r>
-  </si>
-  <si>
-    <t>[3,2,2].most(2) 3
-['fe','fo','fum'].most(true, 'length') ["fe", "fo"]
-users.most('profile.type') &lt;User:Betty&gt;
-users.most(true, 'profile.type') [&lt;User:Betty&gt;, &lt;User:Mark&gt;]</t>
   </si>
   <si>
     <t>Returns the elements in the array with the most commonly occuring value. 
@@ -18509,6 +18497,115 @@
   {id: 2, name: 'Bob'},
   {id: 3, name: 'Charlie'}
 ]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[3,2,2].most(2) 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- нужно проверять</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">//Ищем элементы, которые встречаются минимум 2 раза </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+['fe','fo','fum'].most(true, 'length') ["fe", "fo"]
+users.most('profile.type') &lt;User:Betty&gt;
+users.most(true, 'profile.type') [&lt;User:Betty&gt;, &lt;User:Mark&gt;]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[3,2,2].least() 3
+['fe','fo','fum'].least(true, 'length') </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">fum </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">//'length' : ['fe','fo','fum'] преобразуется в массив длин [2,2,3]
+//ture: [2,2,3] -&gt; ['fum']
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>users.least('profile.type') &lt;User:Harry&gt;
+users.least(true, 'profile.type') [&lt;User:Harry&gt;, &lt;User:Georgia&gt;]</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -18854,7 +18951,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -18966,6 +19063,9 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7B23FFB3-A72F-409B-B670-C03B7A66220A}"/>
@@ -18995,7 +19095,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>3417570</xdr:colOff>
+      <xdr:colOff>3408045</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>840585</xdr:rowOff>
     </xdr:to>
@@ -19402,7 +19502,7 @@
     </row>
     <row r="4" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -19426,11 +19526,11 @@
     </row>
     <row r="5" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -19452,13 +19552,13 @@
     </row>
     <row r="6" spans="1:23" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -19480,7 +19580,7 @@
     </row>
     <row r="7" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -19506,7 +19606,7 @@
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -20506,80 +20606,80 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C16" s="19" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -20617,7 +20717,7 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -20635,16 +20735,16 @@
     </row>
     <row r="20" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="1"/>
@@ -20659,7 +20759,7 @@
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="9"/>
@@ -20672,10 +20772,10 @@
         <v>0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>1</v>
@@ -20686,198 +20786,198 @@
     </row>
     <row r="23" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>1011</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>966</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="C24" s="25" t="s">
         <v>1016</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>966</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>1018</v>
-      </c>
       <c r="D24" s="32" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="E24" s="32" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C25" s="25" t="s">
         <v>1062</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>1064</v>
-      </c>
       <c r="D25" s="32" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>962</v>
+      </c>
+      <c r="E26" s="32" t="s">
         <v>963</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>966</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1065</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>964</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="D31" s="32" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="E31" s="32" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="D33" s="14" t="s">
         <v>95</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>904</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>667</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -20885,10 +20985,10 @@
     <row r="37" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -20896,10 +20996,10 @@
     <row r="38" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -20909,7 +21009,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="2"/>
@@ -20920,7 +21020,7 @@
         <v>27</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>29</v>
@@ -20931,7 +21031,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
@@ -20958,7 +21058,7 @@
         <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>74</v>
@@ -20966,16 +21066,16 @@
     </row>
     <row r="45" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>26</v>
@@ -21028,22 +21128,22 @@
     </row>
     <row r="49" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E49" s="14"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="15" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C50" s="10"/>
       <c r="D50" s="10"/>
@@ -21054,10 +21154,10 @@
         <v>15</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>14</v>
@@ -21068,10 +21168,10 @@
         <v>39</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>43</v>
@@ -21085,13 +21185,13 @@
         <v>16</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -21099,27 +21199,27 @@
         <v>21</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D55" s="16" t="s">
         <v>183</v>
-      </c>
-      <c r="C55" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>185</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>26</v>
@@ -21127,22 +21227,22 @@
     </row>
     <row r="56" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E56" s="14"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="15" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D57" s="10"/>
     </row>
@@ -21151,7 +21251,7 @@
         <v>22</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>19</v>
@@ -21165,10 +21265,10 @@
         <v>42</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>44</v>
@@ -21182,7 +21282,7 @@
         <v>76</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>78</v>
@@ -21196,7 +21296,7 @@
         <v>91</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>93</v>
@@ -21210,108 +21310,108 @@
         <v>45</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D63" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C64" s="14" t="s">
-        <v>108</v>
+        <v>174</v>
+      </c>
+      <c r="C64" s="39" t="s">
+        <v>1092</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D65" s="14"/>
     </row>
     <row r="66" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C66" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C66" s="38" t="s">
-        <v>136</v>
-      </c>
       <c r="D66" s="14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="D67" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="144" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="2"/>
@@ -21322,7 +21422,7 @@
         <v>2</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>7</v>
@@ -21339,7 +21439,7 @@
         <v>6</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>9</v>
@@ -21351,7 +21451,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D73" s="10"/>
       <c r="E73" s="10"/>
@@ -21364,7 +21464,7 @@
         <v>48</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>47</v>
@@ -21378,7 +21478,7 @@
         <v>48</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>90</v>
@@ -21386,16 +21486,16 @@
     </row>
     <row r="76" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C76" s="37" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E76" s="14"/>
     </row>
@@ -21404,10 +21504,10 @@
         <v>64</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>65</v>
@@ -21415,7 +21515,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -21427,7 +21527,7 @@
         <v>63</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>61</v>
@@ -21441,16 +21541,16 @@
     </row>
     <row r="80" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="D80" s="14" t="s">
         <v>95</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>904</v>
-      </c>
-      <c r="D80" s="14" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
@@ -21458,10 +21558,10 @@
         <v>40</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>41</v>
@@ -21505,7 +21605,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D85" s="14"/>
     </row>
@@ -21514,7 +21614,7 @@
         <v>32</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>30</v>
@@ -21528,10 +21628,10 @@
         <v>49</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>50</v>
@@ -21542,31 +21642,31 @@
     </row>
     <row r="88" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E88" s="14"/>
     </row>
     <row r="89" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="D89" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E89" s="1"/>
     </row>
@@ -21575,7 +21675,7 @@
         <v>66</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>68</v>
@@ -21592,7 +21692,7 @@
         <v>70</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>71</v>
@@ -21606,18 +21706,18 @@
         <v>73</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D93" s="14"/>
     </row>
@@ -21626,7 +21726,7 @@
         <v>79</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>81</v>
@@ -21637,64 +21737,64 @@
     </row>
     <row r="95" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C95" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C95" s="24" t="s">
-        <v>139</v>
-      </c>
       <c r="D95" s="14" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="D96" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E96" s="1"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C99" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D99" s="14" t="s">
         <v>101</v>
-      </c>
-      <c r="D99" s="14" t="s">
-        <v>102</v>
       </c>
       <c r="E99" s="14" t="s">
         <v>26</v>
@@ -21702,16 +21802,16 @@
     </row>
     <row r="100" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C100" s="2" t="s">
+      <c r="D100" s="14" t="s">
         <v>99</v>
-      </c>
-      <c r="D100" s="14" t="s">
-        <v>100</v>
       </c>
       <c r="E100" s="14" t="s">
         <v>26</v>
@@ -21719,36 +21819,36 @@
     </row>
     <row r="101" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="C101" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="C101" s="14" t="s">
-        <v>115</v>
-      </c>
       <c r="D101" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E101" s="14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="C102" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="C102" s="14" t="s">
-        <v>119</v>
-      </c>
       <c r="D102" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
@@ -21756,7 +21856,7 @@
         <v>23</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>25</v>
@@ -21773,7 +21873,7 @@
         <v>33</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>35</v>
@@ -21787,22 +21887,22 @@
     </row>
     <row r="105" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="D105" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E105" s="14"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C106" s="10"/>
       <c r="D106" s="2"/>
@@ -21810,31 +21910,31 @@
     </row>
     <row r="107" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D107" s="14" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E107" s="14"/>
     </row>
     <row r="108" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C108" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C108" s="14" t="s">
-        <v>128</v>
-      </c>
       <c r="D108" s="14" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E108" s="2"/>
     </row>
@@ -22038,104 +22138,104 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B2" s="11"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B3" s="15"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B4" s="15"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B5" s="15"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B6" s="15"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B7" s="15"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B8" s="15"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B9" s="23"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B10" s="15"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B13" s="15"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B14" s="11"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B15" s="15"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B16" s="15"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B17" s="15"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B18" s="11"/>
     </row>
@@ -22166,7 +22266,7 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="1"/>
@@ -22175,22 +22275,22 @@
     </row>
     <row r="23" spans="1:24" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B23" s="21"/>
       <c r="C23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="24" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="2"/>
@@ -22215,17 +22315,17 @@
     </row>
     <row r="25" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F25" s="2"/>
       <c r="H25" s="1"/>
@@ -22246,20 +22346,20 @@
     </row>
     <row r="26" spans="1:24" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="2"/>
@@ -22279,17 +22379,17 @@
     </row>
     <row r="27" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F27" s="2"/>
       <c r="H27" s="1"/>
@@ -22312,13 +22412,13 @@
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F28" s="2"/>
       <c r="H28" s="1"/>
@@ -22341,13 +22441,13 @@
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F29" s="2"/>
       <c r="H29" s="1"/>
@@ -22370,13 +22470,13 @@
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F30" s="2"/>
       <c r="H30" s="1"/>
@@ -22399,13 +22499,13 @@
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F31" s="2"/>
       <c r="H31" s="1"/>
@@ -22428,13 +22528,13 @@
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F32" s="2"/>
       <c r="H32" s="1"/>
@@ -22457,13 +22557,13 @@
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F33" s="2"/>
       <c r="H33" s="1"/>
@@ -22484,20 +22584,20 @@
     </row>
     <row r="34" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="2"/>
@@ -22517,13 +22617,13 @@
     </row>
     <row r="35" spans="1:24" s="7" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="22" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="F35" s="4"/>
       <c r="H35" s="1"/>
@@ -22544,7 +22644,7 @@
     </row>
     <row r="36" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="2"/>
@@ -22569,13 +22669,13 @@
     </row>
     <row r="37" spans="1:24" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="22" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="F37" s="4"/>
       <c r="H37" s="1"/>
@@ -22596,13 +22696,13 @@
     </row>
     <row r="38" spans="1:24" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="22" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="F38" s="4"/>
       <c r="H38" s="1"/>
@@ -22623,13 +22723,13 @@
     </row>
     <row r="39" spans="1:24" s="7" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="22" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="F39" s="4"/>
       <c r="H39" s="1"/>
@@ -22650,13 +22750,13 @@
     </row>
     <row r="40" spans="1:24" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="22" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F40" s="4"/>
       <c r="H40" s="1"/>
@@ -22677,13 +22777,13 @@
     </row>
     <row r="41" spans="1:24" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="22" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F41" s="4"/>
       <c r="H41" s="1"/>
@@ -22704,13 +22804,13 @@
     </row>
     <row r="42" spans="1:24" s="7" customFormat="1" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="22" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="F42" s="4"/>
       <c r="H42" s="1"/>
@@ -22731,7 +22831,7 @@
     </row>
     <row r="43" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="2"/>
@@ -22756,17 +22856,17 @@
     </row>
     <row r="44" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="F44" s="2"/>
       <c r="H44" s="1"/>
@@ -22787,17 +22887,17 @@
     </row>
     <row r="45" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F45" s="2"/>
       <c r="H45" s="1"/>
@@ -22818,17 +22918,17 @@
     </row>
     <row r="46" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F46" s="2"/>
       <c r="H46" s="1"/>
@@ -22849,17 +22949,17 @@
     </row>
     <row r="47" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F47" s="2"/>
       <c r="H47" s="1"/>
@@ -22880,17 +22980,17 @@
     </row>
     <row r="48" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F48" s="2"/>
       <c r="H48" s="1"/>
@@ -22911,7 +23011,7 @@
     </row>
     <row r="49" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B49" s="21"/>
       <c r="C49" s="2"/>
@@ -22936,20 +23036,20 @@
     </row>
     <row r="50" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="2"/>
@@ -22969,20 +23069,20 @@
     </row>
     <row r="51" spans="1:24" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E51" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>623</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="2"/>
@@ -23002,20 +23102,20 @@
     </row>
     <row r="52" spans="1:24" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="2" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E52" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>625</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>627</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="2"/>
@@ -23035,20 +23135,20 @@
     </row>
     <row r="53" spans="1:24" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>630</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>632</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="2"/>
@@ -23068,20 +23168,20 @@
     </row>
     <row r="54" spans="1:24" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>637</v>
-      </c>
       <c r="E54" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>634</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>636</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="2"/>
@@ -23101,7 +23201,7 @@
     </row>
     <row r="55" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="15" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -23126,22 +23226,22 @@
     </row>
     <row r="56" spans="1:24" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>1091</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="2"/>
@@ -23161,19 +23261,19 @@
     </row>
     <row r="57" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>1091</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>503</v>
-      </c>
       <c r="D57" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F57" s="2"/>
       <c r="H57" s="1"/>
@@ -23194,19 +23294,19 @@
     </row>
     <row r="58" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>1091</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>580</v>
-      </c>
       <c r="D58" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="7"/>
@@ -23230,43 +23330,43 @@
     </row>
     <row r="59" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>1091</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>584</v>
-      </c>
       <c r="D59" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="F59" s="2"/>
     </row>
     <row r="60" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>1091</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>609</v>
-      </c>
       <c r="D60" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F60" s="2"/>
     </row>
     <row r="61" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -23291,20 +23391,20 @@
     </row>
     <row r="62" spans="1:24" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F62" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>678</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="2"/>
@@ -23324,11 +23424,11 @@
     </row>
     <row r="63" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
@@ -23351,11 +23451,11 @@
     </row>
     <row r="64" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
@@ -23378,11 +23478,11 @@
     </row>
     <row r="65" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
@@ -23405,11 +23505,11 @@
     </row>
     <row r="66" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
@@ -23432,14 +23532,14 @@
     </row>
     <row r="67" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
@@ -23461,11 +23561,11 @@
     </row>
     <row r="68" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
@@ -23488,11 +23588,11 @@
     </row>
     <row r="69" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
@@ -23515,14 +23615,14 @@
     </row>
     <row r="70" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
@@ -23544,17 +23644,17 @@
     </row>
     <row r="71" spans="1:24" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F71" s="2"/>
       <c r="H71" s="1"/>
@@ -23575,17 +23675,17 @@
     </row>
     <row r="72" spans="1:24" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="F72" s="2"/>
       <c r="H72" s="1"/>
@@ -23606,20 +23706,20 @@
     </row>
     <row r="73" spans="1:24" s="7" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" s="2" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="2"/>
@@ -23639,17 +23739,17 @@
     </row>
     <row r="74" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="F74" s="2"/>
       <c r="H74" s="1"/>
@@ -23670,17 +23770,17 @@
     </row>
     <row r="75" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B75" s="21"/>
       <c r="C75" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="F75" s="2"/>
       <c r="H75" s="1"/>
@@ -23701,7 +23801,7 @@
     </row>
     <row r="76" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="15" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B76" s="21"/>
       <c r="C76" s="2"/>
@@ -23730,13 +23830,13 @@
       </c>
       <c r="B77" s="21"/>
       <c r="C77" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F77" s="2"/>
       <c r="H77" s="1"/>
@@ -23757,7 +23857,7 @@
     </row>
     <row r="78" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="15" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B78" s="21"/>
       <c r="C78" s="2"/>
@@ -23782,17 +23882,17 @@
     </row>
     <row r="79" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B79" s="21"/>
       <c r="C79" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F79" s="2"/>
       <c r="H79" s="1"/>
@@ -23813,23 +23913,23 @@
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B80" s="20"/>
     </row>
     <row r="81" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B81" s="21"/>
       <c r="C81" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F81" s="2"/>
       <c r="H81" s="1"/>
@@ -23850,7 +23950,7 @@
     </row>
     <row r="82" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="15" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B82" s="21"/>
       <c r="C82" s="2"/>
@@ -23875,17 +23975,17 @@
     </row>
     <row r="83" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B83" s="21"/>
       <c r="C83" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="7"/>
@@ -23909,23 +24009,23 @@
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A84" s="11" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B84" s="20"/>
     </row>
     <row r="85" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B85" s="21"/>
       <c r="C85" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="7"/>
@@ -23949,17 +24049,17 @@
     </row>
     <row r="86" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B86" s="21"/>
       <c r="C86" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="7"/>
@@ -23983,7 +24083,7 @@
     </row>
     <row r="87" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B87" s="21"/>
       <c r="C87" s="2"/>
@@ -24011,17 +24111,17 @@
     </row>
     <row r="88" spans="1:24" s="4" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B88" s="21"/>
       <c r="C88" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="7"/>
@@ -24045,17 +24145,17 @@
     </row>
     <row r="89" spans="1:24" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="7"/>
@@ -24079,17 +24179,17 @@
     </row>
     <row r="90" spans="1:24" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="7"/>
@@ -24113,20 +24213,20 @@
     </row>
     <row r="91" spans="1:24" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D91" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E91" s="2" t="s">
-        <v>538</v>
-      </c>
       <c r="F91" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="1"/>
@@ -24149,20 +24249,20 @@
     </row>
     <row r="92" spans="1:24" s="4" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="F92" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="1"/>
@@ -24185,17 +24285,17 @@
     </row>
     <row r="93" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="7"/>
@@ -24219,17 +24319,17 @@
     </row>
     <row r="94" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="7"/>
@@ -24253,20 +24353,20 @@
     </row>
     <row r="95" spans="1:24" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E95" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="F95" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>559</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="1"/>
@@ -24289,20 +24389,20 @@
     </row>
     <row r="96" spans="1:24" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>565</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>567</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="1"/>
@@ -24325,20 +24425,20 @@
     </row>
     <row r="97" spans="1:24" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="F97" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>552</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="1"/>
@@ -24361,17 +24461,17 @@
     </row>
     <row r="98" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="7"/>
@@ -24395,17 +24495,17 @@
     </row>
     <row r="99" spans="1:24" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B99" s="21"/>
       <c r="C99" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="7"/>
@@ -24429,7 +24529,7 @@
     </row>
     <row r="100" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="15" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B100" s="21"/>
       <c r="C100" s="2"/>
@@ -24457,17 +24557,17 @@
     </row>
     <row r="101" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B101" s="21"/>
       <c r="C101" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F101" s="2"/>
       <c r="G101" s="7"/>
@@ -24491,17 +24591,17 @@
     </row>
     <row r="102" spans="1:24" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B102" s="21"/>
       <c r="C102" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="7"/>
@@ -24525,7 +24625,7 @@
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A103" s="15" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B103" s="21"/>
       <c r="E103" s="2"/>
@@ -24533,60 +24633,60 @@
     </row>
     <row r="104" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B104" s="21"/>
       <c r="C104" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F104" s="2"/>
     </row>
     <row r="105" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B105" s="21"/>
       <c r="C105" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A106" s="15" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B106" s="21"/>
     </row>
     <row r="107" spans="1:24" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B107" s="21"/>
       <c r="C107" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="D107" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="D107" s="2" t="s">
-        <v>667</v>
-      </c>
       <c r="E107" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H107" s="1"/>
       <c r="I107" s="2"/>
@@ -24608,10 +24708,10 @@
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
@@ -24635,10 +24735,10 @@
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
@@ -24662,10 +24762,10 @@
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
@@ -24687,24 +24787,24 @@
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A111" s="11" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B111" s="11"/>
     </row>
     <row r="112" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H112" s="1"/>
       <c r="I112" s="2"/>
@@ -24724,20 +24824,20 @@
     </row>
     <row r="113" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H113" s="1"/>
       <c r="I113" s="2"/>
@@ -24757,20 +24857,20 @@
     </row>
     <row r="114" spans="1:24" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B114" s="2"/>
       <c r="C114" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H114" s="1"/>
       <c r="I114" s="2"/>
@@ -24790,20 +24890,20 @@
     </row>
     <row r="115" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B115" s="21"/>
       <c r="C115" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H115" s="1"/>
       <c r="I115" s="2"/>
@@ -24823,20 +24923,20 @@
     </row>
     <row r="116" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B116" s="21"/>
       <c r="C116" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E116" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D116" s="2" t="s">
+      <c r="F116" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="H116" s="1"/>
       <c r="I116" s="2"/>
@@ -24856,20 +24956,20 @@
     </row>
     <row r="117" spans="1:24" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B117" s="21"/>
       <c r="C117" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H117" s="1"/>
       <c r="I117" s="2"/>
@@ -24889,81 +24989,81 @@
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A118" s="15" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B118" s="21"/>
     </row>
     <row r="119" spans="1:24" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B119" s="20"/>
       <c r="C119" s="1"/>
       <c r="D119" s="2" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="E119" s="32" t="s">
+        <v>937</v>
+      </c>
+      <c r="F119" s="32" t="s">
         <v>939</v>
-      </c>
-      <c r="F119" s="32" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="120" spans="1:24" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B120" s="2"/>
       <c r="D120" s="25" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="E120" s="32" t="s">
+        <v>941</v>
+      </c>
+      <c r="F120" s="32" t="s">
         <v>943</v>
-      </c>
-      <c r="F120" s="32" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="121" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A121" s="25" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B121" s="25"/>
       <c r="D121" s="2" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="E121" s="32" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="122" spans="1:24" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B122" s="2"/>
       <c r="D122" s="33" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="E122" s="32" t="s">
+        <v>950</v>
+      </c>
+      <c r="F122" s="32" t="s">
         <v>952</v>
-      </c>
-      <c r="F122" s="32" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="123" spans="1:24" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B123" s="2"/>
       <c r="D123" s="25" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="E123" s="32" t="s">
+        <v>954</v>
+      </c>
+      <c r="F123" s="32" t="s">
         <v>956</v>
-      </c>
-      <c r="F123" s="32" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="143" spans="3:6" x14ac:dyDescent="0.3">
@@ -25067,74 +25167,74 @@
   <sheetData>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B5" s="20"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B6" s="21"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B9" s="20"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B10" s="20"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B13" s="21"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B14" s="20"/>
     </row>
@@ -25163,7 +25263,7 @@
     </row>
     <row r="18" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -25171,157 +25271,157 @@
     </row>
     <row r="19" spans="1:23" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>308</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F19" s="7"/>
     </row>
     <row r="20" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F20" s="7"/>
     </row>
     <row r="21" spans="1:23" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>439</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>433</v>
-      </c>
       <c r="C23" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F23" s="7"/>
     </row>
     <row r="24" spans="1:23" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F24" s="7"/>
     </row>
     <row r="25" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:23" s="2" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="C26" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:23" s="2" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>340</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F27" s="7"/>
     </row>
     <row r="28" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="D28" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F28" s="7"/>
     </row>
     <row r="29" spans="1:23" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F29" s="7"/>
     </row>
     <row r="30" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -25348,19 +25448,19 @@
     </row>
     <row r="31" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="1"/>
@@ -25385,10 +25485,10 @@
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="7"/>
@@ -25414,10 +25514,10 @@
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="7"/>
@@ -25443,10 +25543,10 @@
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="7"/>
@@ -25472,10 +25572,10 @@
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="7"/>
@@ -25499,19 +25599,19 @@
     </row>
     <row r="36" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>403</v>
-      </c>
       <c r="D36" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E36" s="17" t="s">
         <v>402</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>404</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="1"/>
@@ -25536,10 +25636,10 @@
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="7"/>
@@ -25565,10 +25665,10 @@
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="7"/>
@@ -25594,10 +25694,10 @@
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="7"/>
@@ -25623,10 +25723,10 @@
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="7"/>
@@ -25650,19 +25750,19 @@
     </row>
     <row r="41" spans="1:23" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="1"/>
@@ -25687,10 +25787,10 @@
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="7"/>
@@ -25716,10 +25816,10 @@
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="7"/>
@@ -25745,10 +25845,10 @@
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="7"/>
@@ -25774,10 +25874,10 @@
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="7"/>
@@ -25801,16 +25901,16 @@
     </row>
     <row r="46" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>407</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="7"/>
@@ -25834,16 +25934,16 @@
     </row>
     <row r="47" spans="1:23" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>328</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="7"/>
@@ -25867,16 +25967,16 @@
     </row>
     <row r="48" spans="1:23" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="1"/>
@@ -25899,16 +25999,16 @@
     </row>
     <row r="49" spans="1:28" s="4" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="1"/>
@@ -25931,7 +26031,7 @@
     </row>
     <row r="50" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="15" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -25958,16 +26058,16 @@
     </row>
     <row r="51" spans="1:28" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B51" s="36" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="B51" s="36" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="E51" s="2"/>
       <c r="G51" s="1"/>
@@ -25996,16 +26096,16 @@
         <v>39</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>335</v>
-      </c>
       <c r="E52" s="35" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="1"/>
@@ -26028,19 +26128,19 @@
     </row>
     <row r="53" spans="1:28" s="4" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="1"/>
@@ -26063,7 +26163,7 @@
     </row>
     <row r="54" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -26096,10 +26196,10 @@
         <v>13</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="1"/>
@@ -26122,16 +26222,16 @@
     </row>
     <row r="56" spans="1:28" s="4" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="7"/>
@@ -26155,16 +26255,16 @@
     </row>
     <row r="57" spans="1:28" s="4" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="7"/>
@@ -26188,16 +26288,16 @@
     </row>
     <row r="58" spans="1:28" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="7"/>
@@ -26221,19 +26321,19 @@
     </row>
     <row r="59" spans="1:28" s="4" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A59" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C59" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="D59" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="E59" s="17" t="s">
         <v>329</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C59" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="D59" s="17" t="s">
-        <v>334</v>
-      </c>
-      <c r="E59" s="17" t="s">
-        <v>331</v>
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="1"/>
@@ -26256,19 +26356,19 @@
     </row>
     <row r="60" spans="1:28" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>443</v>
-      </c>
       <c r="E60" s="17" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="1"/>
@@ -26291,19 +26391,19 @@
     </row>
     <row r="61" spans="1:28" s="4" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="1"/>
@@ -26326,22 +26426,22 @@
     </row>
     <row r="62" spans="1:28" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E62" s="2"/>
     </row>
     <row r="63" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -26371,13 +26471,13 @@
         <v>23</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="7"/>
@@ -26401,19 +26501,19 @@
     </row>
     <row r="65" spans="1:28" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="1"/>
@@ -26438,11 +26538,11 @@
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="17" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="1"/>
@@ -26465,16 +26565,16 @@
     </row>
     <row r="67" spans="1:28" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E67" s="2"/>
       <c r="G67" s="1"/>
@@ -26500,117 +26600,117 @@
     </row>
     <row r="68" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="69" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E69" s="17" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="70" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="71" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A71" s="15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
     </row>
     <row r="72" spans="1:28" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="D72" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E72" s="2"/>
     </row>
     <row r="73" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="E73" s="2"/>
     </row>
     <row r="74" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A74" s="15" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>360</v>
       </c>
       <c r="E75" s="2"/>
     </row>
     <row r="76" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -26619,58 +26719,58 @@
     </row>
     <row r="77" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>463</v>
-      </c>
       <c r="C78" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E78" s="2"/>
     </row>
     <row r="79" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>385</v>
-      </c>
       <c r="D79" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="80" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A80" s="2"/>
       <c r="B80" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
@@ -26678,10 +26778,10 @@
     <row r="81" spans="1:28" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A81" s="2"/>
       <c r="B81" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
@@ -26689,43 +26789,43 @@
     <row r="82" spans="1:28" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A82" s="2"/>
       <c r="B82" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
     </row>
     <row r="83" spans="1:28" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="84" spans="1:28" s="7" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="2"/>
@@ -26750,19 +26850,19 @@
     </row>
     <row r="85" spans="1:28" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="D85" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="2"/>
@@ -26787,7 +26887,7 @@
     </row>
     <row r="86" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -26816,155 +26916,155 @@
     </row>
     <row r="87" spans="1:28" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D87" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>451</v>
-      </c>
       <c r="E87" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" s="11" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="89" spans="1:28" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E89" s="2"/>
     </row>
     <row r="90" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A90" s="2"/>
       <c r="C90" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E90" s="2"/>
     </row>
     <row r="91" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A91" s="2"/>
       <c r="C91" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E91" s="2"/>
     </row>
     <row r="92" spans="1:28" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A92" s="2"/>
       <c r="C92" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E92" s="2"/>
     </row>
     <row r="93" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A93" s="2"/>
       <c r="C93" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E93" s="2"/>
     </row>
     <row r="94" spans="1:28" ht="72" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>456</v>
-      </c>
       <c r="D94" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E94" s="17" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="95" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2"/>
       <c r="C95" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E95" s="2"/>
     </row>
     <row r="96" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2"/>
       <c r="C96" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E96" s="2"/>
     </row>
     <row r="97" spans="1:5" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A97" s="2"/>
       <c r="C97" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E97" s="2"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="2"/>
       <c r="C98" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E98" s="2"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="11" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E100" s="2"/>
     </row>
@@ -27014,91 +27114,91 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B9" s="21"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B10" s="20"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B11" s="20"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B14" s="21"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B15" s="20"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B16" s="20"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B17" s="20"/>
     </row>
@@ -27127,7 +27227,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -27135,37 +27235,37 @@
     </row>
     <row r="22" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C23" s="25"/>
       <c r="D23" s="24"/>
     </row>
     <row r="24" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
@@ -27173,596 +27273,596 @@
         <v>82</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C26" s="25"/>
       <c r="D26" s="24"/>
     </row>
     <row r="27" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>741</v>
+      </c>
+      <c r="D27" s="24" t="s">
         <v>742</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="C27" s="25" t="s">
-        <v>743</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C28" s="25" t="s">
         <v>793</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>795</v>
-      </c>
       <c r="D28" s="27" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C29" s="25" t="s">
         <v>724</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>726</v>
-      </c>
       <c r="D29" s="24" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C30" s="25"/>
       <c r="D30" s="24"/>
     </row>
     <row r="31" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C33" s="25" t="s">
         <v>753</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C33" s="25" t="s">
-        <v>755</v>
-      </c>
       <c r="D33" s="24" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="C37" s="25" t="s">
         <v>862</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>866</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>864</v>
-      </c>
       <c r="D37" s="27" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C39" s="25" t="s">
         <v>779</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="C39" s="25" t="s">
-        <v>781</v>
-      </c>
       <c r="D39" s="24" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="D40" s="24"/>
     </row>
     <row r="41" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C42" s="25" t="s">
+        <v>768</v>
+      </c>
+      <c r="D42" s="24" t="s">
         <v>770</v>
-      </c>
-      <c r="D42" s="24" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C43" s="25" t="s">
+        <v>772</v>
+      </c>
+      <c r="D43" s="24" t="s">
         <v>771</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="C43" s="25" t="s">
-        <v>774</v>
-      </c>
-      <c r="D43" s="24" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C44" s="25" t="s">
         <v>745</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>747</v>
-      </c>
       <c r="D44" s="24" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="C48" s="25" t="s">
         <v>760</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>762</v>
-      </c>
       <c r="D48" s="24" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="C49" s="25" t="s">
         <v>763</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>765</v>
-      </c>
       <c r="D49" s="24" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="C50" s="25" t="s">
         <v>766</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>768</v>
-      </c>
       <c r="D50" s="24" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="27"/>
     </row>
     <row r="52" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="B53" s="27" t="s">
         <v>826</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="C53" s="25" t="s">
         <v>828</v>
       </c>
-      <c r="C53" s="25" t="s">
-        <v>830</v>
-      </c>
       <c r="D53" s="27" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B54" s="27" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C54" s="25" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D54" s="27" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>808</v>
+      </c>
+      <c r="C55" s="26" t="s">
+        <v>711</v>
+      </c>
+      <c r="D55" s="24" t="s">
         <v>712</v>
-      </c>
-      <c r="B55" s="27" t="s">
-        <v>810</v>
-      </c>
-      <c r="C55" s="26" t="s">
-        <v>713</v>
-      </c>
-      <c r="D55" s="24" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="C57" s="25" t="s">
         <v>820</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="C57" s="25" t="s">
-        <v>822</v>
-      </c>
       <c r="D57" s="27" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="C59" s="25" t="s">
         <v>868</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="C59" s="25" t="s">
-        <v>870</v>
-      </c>
       <c r="D59" s="27" t="s">
+        <v>867</v>
+      </c>
+      <c r="E59" s="27" t="s">
         <v>869</v>
-      </c>
-      <c r="E59" s="27" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>806</v>
-      </c>
       <c r="C60" s="25" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C61" s="25" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D61" s="24" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C62" s="25"/>
       <c r="D62" s="27"/>
     </row>
     <row r="63" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C63" s="25" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D63" s="27" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="C64" s="25" t="s">
         <v>872</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="C64" s="25" t="s">
+      <c r="D64" s="27" t="s">
+        <v>871</v>
+      </c>
+      <c r="E64" s="27" t="s">
         <v>874</v>
-      </c>
-      <c r="D64" s="27" t="s">
-        <v>873</v>
-      </c>
-      <c r="E64" s="27" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C65" s="25"/>
       <c r="D65" s="24"/>
     </row>
     <row r="66" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C66" s="25" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D66" s="24" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>730</v>
+      </c>
+      <c r="D67" s="24" t="s">
+        <v>728</v>
+      </c>
+      <c r="E67" s="24" t="s">
         <v>729</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="C67" s="25" t="s">
-        <v>732</v>
-      </c>
-      <c r="D67" s="24" t="s">
-        <v>730</v>
-      </c>
-      <c r="E67" s="24" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="C68" s="26" t="s">
         <v>699</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="C68" s="26" t="s">
-        <v>701</v>
-      </c>
       <c r="D68" s="24" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E68" s="24" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="C69" s="25" t="s">
+        <v>704</v>
+      </c>
+      <c r="D69" s="24" t="s">
         <v>707</v>
       </c>
-      <c r="C69" s="25" t="s">
-        <v>706</v>
-      </c>
-      <c r="D69" s="24" t="s">
-        <v>709</v>
-      </c>
       <c r="E69" s="24" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="C70" s="25" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D70" s="27" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="28" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B71" s="27"/>
       <c r="C71" s="26"/>
@@ -27770,91 +27870,91 @@
     </row>
     <row r="72" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="C72" s="25" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>852</v>
+      </c>
+      <c r="D74" s="27" t="s">
+        <v>800</v>
+      </c>
+      <c r="E74" s="27" t="s">
         <v>801</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>859</v>
-      </c>
-      <c r="C74" s="25" t="s">
-        <v>854</v>
-      </c>
-      <c r="D74" s="27" t="s">
-        <v>802</v>
-      </c>
-      <c r="E74" s="27" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>855</v>
+      </c>
+      <c r="D75" s="24" t="s">
+        <v>774</v>
+      </c>
+      <c r="E75" s="24" t="s">
         <v>775</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>858</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>857</v>
-      </c>
-      <c r="D75" s="24" t="s">
-        <v>776</v>
-      </c>
-      <c r="E75" s="24" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="C76" s="25"/>
       <c r="D76" s="24"/>
     </row>
     <row r="77" spans="1:5" ht="216" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="D77" s="24" t="s">
         <v>739</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="D77" s="24" t="s">
-        <v>741</v>
       </c>
       <c r="E77" s="24"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C78" s="25"/>
       <c r="D78" s="27"/>
@@ -27862,75 +27962,75 @@
     </row>
     <row r="79" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C79" s="25" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E79" s="27" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="E80" s="27" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D82" s="27" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="E82" s="27" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="28" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C83" s="25"/>
       <c r="D83" s="24"/>
@@ -27938,35 +28038,35 @@
     </row>
     <row r="84" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="C84" s="25" t="s">
         <v>716</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="C84" s="25" t="s">
-        <v>718</v>
-      </c>
       <c r="D84" s="24" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="C85" s="25" t="s">
+        <v>719</v>
+      </c>
+      <c r="D85" s="24" t="s">
         <v>720</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="C85" s="25" t="s">
-        <v>721</v>
-      </c>
-      <c r="D85" s="24" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -27974,16 +28074,16 @@
     </row>
     <row r="87" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="C87" s="25" t="s">
         <v>733</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="C87" s="25" t="s">
-        <v>735</v>
-      </c>
       <c r="D87" s="24" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -28069,76 +28169,76 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B6" s="20"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B9" s="21"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -28173,7 +28273,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -28181,114 +28281,114 @@
     </row>
     <row r="22" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>982</v>
-      </c>
       <c r="D23" s="32" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C24" s="25" t="s">
         <v>983</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>1019</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>985</v>
-      </c>
       <c r="D24" s="32" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>991</v>
-      </c>
       <c r="D25" s="32" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C26" s="25" t="s">
         <v>986</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>988</v>
-      </c>
       <c r="D26" s="32" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>992</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>994</v>
-      </c>
       <c r="D28" s="32" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="E28" s="24"/>
     </row>
     <row r="29" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C29" s="25" t="s">
         <v>996</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>998</v>
-      </c>
       <c r="D29" s="32" t="s">
+        <v>993</v>
+      </c>
+      <c r="E29" s="32" t="s">
         <v>995</v>
-      </c>
-      <c r="E29" s="32" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="28" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -28296,18 +28396,18 @@
     </row>
     <row r="31" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="C31" s="32" t="s">
         <v>913</v>
       </c>
-      <c r="C31" s="32" t="s">
-        <v>915</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="34" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -28315,143 +28415,143 @@
     </row>
     <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C34" s="25"/>
       <c r="D34" s="32"/>
     </row>
     <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C36" s="25" t="s">
         <v>935</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>937</v>
-      </c>
       <c r="D36" s="32" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C37" s="25"/>
       <c r="D37" s="32"/>
     </row>
     <row r="38" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="D38" s="32" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>970</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>972</v>
-      </c>
       <c r="D39" s="32" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C40" s="25" t="s">
         <v>1008</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C40" s="25" t="s">
-        <v>1010</v>
-      </c>
       <c r="D40" s="32" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="D41" s="32"/>
     </row>
     <row r="42" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C42" s="25" t="s">
         <v>932</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>934</v>
-      </c>
       <c r="D42" s="32" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C43" s="25"/>
       <c r="D43" s="32"/>
     </row>
     <row r="44" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>977</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>979</v>
-      </c>
       <c r="D44" s="32" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="C45" s="25"/>
       <c r="D45" s="32"/>
@@ -28459,88 +28559,88 @@
     </row>
     <row r="46" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>1001</v>
-      </c>
       <c r="D46" s="32" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>976</v>
-      </c>
       <c r="D47" s="32" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>967</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>969</v>
-      </c>
       <c r="D48" s="32" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C49" s="25" t="s">
         <v>1002</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>1004</v>
-      </c>
       <c r="D49" s="32" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C50" s="25" t="s">
         <v>1005</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>1007</v>
-      </c>
       <c r="D50" s="32" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C51" s="25" t="s">
         <v>924</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C51" s="25" t="s">
-        <v>926</v>
-      </c>
       <c r="D51" s="32" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
@@ -29883,72 +29983,72 @@
     </row>
     <row r="21" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C22" s="32" t="s">
         <v>1044</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>1046</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>1048</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1050</v>
-      </c>
       <c r="D23" s="32" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C24" s="25" t="s">
         <v>1051</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>1053</v>
-      </c>
       <c r="D24" s="32" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>1054</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1056</v>
-      </c>
       <c r="D25" s="32" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">

--- a/4 четверть_13_JavaScript_sugarJS.xlsx
+++ b/4 четверть_13_JavaScript_sugarJS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB174D05-A0C6-4EB0-BB96-CF438A32CBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4EACC82-AF8E-4C0E-93FF-DE353A550C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sugarjs" sheetId="20" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="1094">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="1096">
   <si>
     <t>construct(n,indexMapFn)</t>
   </si>
@@ -18607,17 +18607,133 @@
 users.least(true, 'profile.type') [&lt;User:Harry&gt;, &lt;User:Georgia&gt;]</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Slice
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Аналог </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>to</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>если с аргументом</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Slice
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Аналог </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>first</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>если с аргументом</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -18949,9 +19065,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -18962,50 +19078,50 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="26" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -19014,42 +19130,42 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -19064,6 +19180,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -20705,14 +20824,14 @@
     <row r="18" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="21"/>
       <c r="C18" s="21"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
       <c r="H18" s="21"/>
       <c r="Q18" s="21"/>
       <c r="R18" s="21"/>
       <c r="S18" s="21"/>
       <c r="T18" s="21"/>
-      <c r="U18" s="31"/>
+      <c r="U18" s="30"/>
       <c r="V18" s="21"/>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
@@ -20740,7 +20859,7 @@
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="35" t="s">
         <v>903</v>
       </c>
       <c r="D20" s="2" t="s">
@@ -20774,7 +20893,7 @@
       <c r="B22" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="31" t="s">
         <v>1013</v>
       </c>
       <c r="D22" s="2" t="s">
@@ -20811,10 +20930,10 @@
       <c r="C24" s="25" t="s">
         <v>1016</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="31" t="s">
         <v>1015</v>
       </c>
-      <c r="E24" s="32" t="s">
+      <c r="E24" s="31" t="s">
         <v>963</v>
       </c>
     </row>
@@ -20828,10 +20947,10 @@
       <c r="C25" s="25" t="s">
         <v>1062</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="31" t="s">
         <v>1061</v>
       </c>
-      <c r="E25" s="32" t="s">
+      <c r="E25" s="31" t="s">
         <v>963</v>
       </c>
     </row>
@@ -20845,10 +20964,10 @@
       <c r="C26" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="31" t="s">
         <v>962</v>
       </c>
-      <c r="E26" s="32" t="s">
+      <c r="E26" s="31" t="s">
         <v>963</v>
       </c>
     </row>
@@ -20914,10 +21033,10 @@
       <c r="C31" s="25" t="s">
         <v>1065</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="31" t="s">
         <v>1061</v>
       </c>
-      <c r="E31" s="32" t="s">
+      <c r="E31" s="31" t="s">
         <v>963</v>
       </c>
     </row>
@@ -21305,7 +21424,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>45</v>
       </c>
@@ -21343,7 +21462,7 @@
       <c r="B64" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C64" s="39" t="s">
+      <c r="C64" s="38" t="s">
         <v>1092</v>
       </c>
       <c r="D64" s="14" t="s">
@@ -21363,7 +21482,7 @@
       <c r="B66" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C66" s="38" t="s">
+      <c r="C66" s="37" t="s">
         <v>134</v>
       </c>
       <c r="D66" s="14" t="s">
@@ -21402,7 +21521,7 @@
       <c r="B69" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C69" s="38" t="s">
+      <c r="C69" s="37" t="s">
         <v>160</v>
       </c>
       <c r="D69" s="14" t="s">
@@ -21491,7 +21610,7 @@
       <c r="B76" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C76" s="37" t="s">
+      <c r="C76" s="36" t="s">
         <v>1080</v>
       </c>
       <c r="D76" s="14" t="s">
@@ -21742,7 +21861,7 @@
       <c r="B95" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C95" s="24" t="s">
+      <c r="C95" s="39" t="s">
         <v>137</v>
       </c>
       <c r="D95" s="14" t="s">
@@ -25002,10 +25121,10 @@
       <c r="D119" s="2" t="s">
         <v>938</v>
       </c>
-      <c r="E119" s="32" t="s">
+      <c r="E119" s="31" t="s">
         <v>937</v>
       </c>
-      <c r="F119" s="32" t="s">
+      <c r="F119" s="31" t="s">
         <v>939</v>
       </c>
     </row>
@@ -25017,10 +25136,10 @@
       <c r="D120" s="25" t="s">
         <v>942</v>
       </c>
-      <c r="E120" s="32" t="s">
+      <c r="E120" s="31" t="s">
         <v>941</v>
       </c>
-      <c r="F120" s="32" t="s">
+      <c r="F120" s="31" t="s">
         <v>943</v>
       </c>
     </row>
@@ -25032,7 +25151,7 @@
       <c r="D121" s="2" t="s">
         <v>948</v>
       </c>
-      <c r="E121" s="32" t="s">
+      <c r="E121" s="31" t="s">
         <v>945</v>
       </c>
     </row>
@@ -25041,13 +25160,13 @@
         <v>949</v>
       </c>
       <c r="B122" s="2"/>
-      <c r="D122" s="33" t="s">
+      <c r="D122" s="32" t="s">
         <v>951</v>
       </c>
-      <c r="E122" s="32" t="s">
+      <c r="E122" s="31" t="s">
         <v>950</v>
       </c>
-      <c r="F122" s="32" t="s">
+      <c r="F122" s="31" t="s">
         <v>952</v>
       </c>
     </row>
@@ -25059,10 +25178,10 @@
       <c r="D123" s="25" t="s">
         <v>955</v>
       </c>
-      <c r="E123" s="32" t="s">
+      <c r="E123" s="31" t="s">
         <v>954</v>
       </c>
-      <c r="F123" s="32" t="s">
+      <c r="F123" s="31" t="s">
         <v>956</v>
       </c>
     </row>
@@ -25121,7 +25240,7 @@
       <c r="F151" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -26060,7 +26179,7 @@
       <c r="A51" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="B51" s="36" t="s">
+      <c r="B51" s="35" t="s">
         <v>1073</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -26095,7 +26214,7 @@
       <c r="A52" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B52" s="36" t="s">
+      <c r="B52" s="35" t="s">
         <v>1074</v>
       </c>
       <c r="C52" s="2" t="s">
@@ -26104,7 +26223,7 @@
       <c r="D52" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="E52" s="35" t="s">
+      <c r="E52" s="34" t="s">
         <v>329</v>
       </c>
       <c r="F52" s="7"/>
@@ -26130,7 +26249,7 @@
       <c r="A53" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B53" s="36" t="s">
+      <c r="B53" s="35" t="s">
         <v>1075</v>
       </c>
       <c r="C53" s="2" t="s">
@@ -27343,9 +27462,9 @@
         <v>725</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C31" s="29" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C31" s="40" t="s">
         <v>882</v>
       </c>
       <c r="D31" s="24" t="s">
@@ -27357,7 +27476,7 @@
         <v>806</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>143</v>
+        <v>1095</v>
       </c>
       <c r="C32" s="25" t="s">
         <v>883</v>
@@ -28183,7 +28302,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="33" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -28286,7 +28405,7 @@
       <c r="B22" s="2" t="s">
         <v>1027</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="36" t="s">
         <v>907</v>
       </c>
       <c r="D22" s="2" t="s">
@@ -28303,7 +28422,7 @@
       <c r="C23" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="31" t="s">
         <v>979</v>
       </c>
     </row>
@@ -28317,7 +28436,7 @@
       <c r="C24" s="25" t="s">
         <v>983</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="31" t="s">
         <v>982</v>
       </c>
     </row>
@@ -28331,7 +28450,7 @@
       <c r="C25" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="31" t="s">
         <v>988</v>
       </c>
     </row>
@@ -28345,7 +28464,7 @@
       <c r="C26" s="25" t="s">
         <v>986</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="31" t="s">
         <v>985</v>
       </c>
     </row>
@@ -28364,7 +28483,7 @@
       <c r="C28" s="2" t="s">
         <v>992</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="31" t="s">
         <v>991</v>
       </c>
       <c r="E28" s="24"/>
@@ -28379,10 +28498,10 @@
       <c r="C29" s="25" t="s">
         <v>996</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="31" t="s">
         <v>993</v>
       </c>
-      <c r="E29" s="32" t="s">
+      <c r="E29" s="31" t="s">
         <v>995</v>
       </c>
     </row>
@@ -28398,7 +28517,7 @@
       <c r="A31" s="2" t="s">
         <v>911</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="C31" s="31" t="s">
         <v>913</v>
       </c>
       <c r="D31" s="2" t="s">
@@ -28406,7 +28525,7 @@
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A32" s="34" t="s">
+      <c r="A32" s="33" t="s">
         <v>1021</v>
       </c>
       <c r="B32" s="1"/>
@@ -28420,7 +28539,7 @@
       <c r="C33" s="25" t="s">
         <v>921</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="31" t="s">
         <v>920</v>
       </c>
     </row>
@@ -28429,7 +28548,7 @@
         <v>1023</v>
       </c>
       <c r="C34" s="25"/>
-      <c r="D34" s="32"/>
+      <c r="D34" s="31"/>
     </row>
     <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
@@ -28441,7 +28560,7 @@
       <c r="C35" s="25" t="s">
         <v>926</v>
       </c>
-      <c r="D35" s="32" t="s">
+      <c r="D35" s="31" t="s">
         <v>925</v>
       </c>
     </row>
@@ -28455,7 +28574,7 @@
       <c r="C36" s="25" t="s">
         <v>935</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="D36" s="31" t="s">
         <v>934</v>
       </c>
     </row>
@@ -28464,7 +28583,7 @@
         <v>1022</v>
       </c>
       <c r="C37" s="25"/>
-      <c r="D37" s="32"/>
+      <c r="D37" s="31"/>
     </row>
     <row r="38" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
@@ -28476,7 +28595,7 @@
       <c r="C38" s="25" t="s">
         <v>971</v>
       </c>
-      <c r="D38" s="32" t="s">
+      <c r="D38" s="31" t="s">
         <v>929</v>
       </c>
     </row>
@@ -28490,7 +28609,7 @@
       <c r="C39" s="2" t="s">
         <v>970</v>
       </c>
-      <c r="D39" s="32" t="s">
+      <c r="D39" s="31" t="s">
         <v>969</v>
       </c>
     </row>
@@ -28504,7 +28623,7 @@
       <c r="C40" s="25" t="s">
         <v>1008</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="31" t="s">
         <v>1007</v>
       </c>
     </row>
@@ -28512,7 +28631,7 @@
       <c r="A41" s="15" t="s">
         <v>1025</v>
       </c>
-      <c r="D41" s="32"/>
+      <c r="D41" s="31"/>
     </row>
     <row r="42" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
@@ -28524,7 +28643,7 @@
       <c r="C42" s="25" t="s">
         <v>932</v>
       </c>
-      <c r="D42" s="32" t="s">
+      <c r="D42" s="31" t="s">
         <v>931</v>
       </c>
     </row>
@@ -28533,7 +28652,7 @@
         <v>1038</v>
       </c>
       <c r="C43" s="25"/>
-      <c r="D43" s="32"/>
+      <c r="D43" s="31"/>
     </row>
     <row r="44" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
@@ -28545,7 +28664,7 @@
       <c r="C44" s="2" t="s">
         <v>977</v>
       </c>
-      <c r="D44" s="32" t="s">
+      <c r="D44" s="31" t="s">
         <v>976</v>
       </c>
     </row>
@@ -28554,8 +28673,8 @@
         <v>1037</v>
       </c>
       <c r="C45" s="25"/>
-      <c r="D45" s="32"/>
-      <c r="E45" s="32"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
     </row>
     <row r="46" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
@@ -28567,7 +28686,7 @@
       <c r="C46" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="D46" s="32" t="s">
+      <c r="D46" s="31" t="s">
         <v>998</v>
       </c>
     </row>
@@ -28581,7 +28700,7 @@
       <c r="C47" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="D47" s="32" t="s">
+      <c r="D47" s="31" t="s">
         <v>973</v>
       </c>
     </row>
@@ -28595,7 +28714,7 @@
       <c r="C48" s="2" t="s">
         <v>967</v>
       </c>
-      <c r="D48" s="32" t="s">
+      <c r="D48" s="31" t="s">
         <v>966</v>
       </c>
     </row>
@@ -28609,7 +28728,7 @@
       <c r="C49" s="25" t="s">
         <v>1002</v>
       </c>
-      <c r="D49" s="32" t="s">
+      <c r="D49" s="31" t="s">
         <v>1001</v>
       </c>
       <c r="E49" s="1"/>
@@ -28624,7 +28743,7 @@
       <c r="C50" s="25" t="s">
         <v>1005</v>
       </c>
-      <c r="D50" s="32" t="s">
+      <c r="D50" s="31" t="s">
         <v>1004</v>
       </c>
       <c r="E50" s="1"/>
@@ -28639,7 +28758,7 @@
       <c r="C51" s="25" t="s">
         <v>924</v>
       </c>
-      <c r="D51" s="32" t="s">
+      <c r="D51" s="31" t="s">
         <v>923</v>
       </c>
     </row>
@@ -28661,7 +28780,7 @@
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="25"/>
-      <c r="D53" s="32"/>
+      <c r="D53" s="31"/>
       <c r="E53" s="4"/>
       <c r="G53" s="1"/>
       <c r="H53" s="2"/>
@@ -28683,7 +28802,7 @@
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="25"/>
-      <c r="D55" s="32"/>
+      <c r="D55" s="31"/>
       <c r="E55" s="4"/>
       <c r="G55" s="1"/>
       <c r="H55" s="2"/>
@@ -28704,7 +28823,7 @@
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="25"/>
-      <c r="D56" s="32"/>
+      <c r="D56" s="31"/>
       <c r="E56" s="4"/>
       <c r="G56" s="1"/>
       <c r="H56" s="2"/>
@@ -28725,7 +28844,7 @@
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="25"/>
-      <c r="D57" s="32"/>
+      <c r="D57" s="31"/>
       <c r="E57" s="4"/>
       <c r="G57" s="1"/>
       <c r="H57" s="2"/>
@@ -28746,7 +28865,7 @@
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="25"/>
-      <c r="D58" s="32"/>
+      <c r="D58" s="31"/>
       <c r="E58" s="4"/>
       <c r="G58" s="1"/>
       <c r="H58" s="2"/>
@@ -28767,7 +28886,7 @@
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="25"/>
-      <c r="D59" s="32"/>
+      <c r="D59" s="31"/>
       <c r="E59" s="4"/>
       <c r="G59" s="1"/>
       <c r="H59" s="2"/>
@@ -28788,7 +28907,7 @@
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="25"/>
-      <c r="D60" s="32"/>
+      <c r="D60" s="31"/>
       <c r="E60" s="4"/>
       <c r="G60" s="1"/>
       <c r="H60" s="2"/>
@@ -28809,7 +28928,7 @@
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="25"/>
-      <c r="D61" s="32"/>
+      <c r="D61" s="31"/>
       <c r="E61" s="4"/>
       <c r="G61" s="1"/>
       <c r="H61" s="2"/>
@@ -28830,7 +28949,7 @@
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="25"/>
-      <c r="D62" s="32"/>
+      <c r="D62" s="31"/>
       <c r="E62" s="4"/>
       <c r="G62" s="1"/>
       <c r="H62" s="2"/>
@@ -28851,7 +28970,7 @@
       <c r="A63" s="2"/>
       <c r="B63" s="27"/>
       <c r="C63" s="25"/>
-      <c r="D63" s="32"/>
+      <c r="D63" s="31"/>
       <c r="E63" s="4"/>
       <c r="G63" s="1"/>
       <c r="H63" s="2"/>
@@ -28872,7 +28991,7 @@
       <c r="A64" s="2"/>
       <c r="B64" s="27"/>
       <c r="C64" s="25"/>
-      <c r="D64" s="32"/>
+      <c r="D64" s="31"/>
       <c r="E64" s="4"/>
       <c r="G64" s="1"/>
       <c r="H64" s="2"/>
@@ -28893,7 +29012,7 @@
       <c r="A65" s="2"/>
       <c r="B65" s="27"/>
       <c r="C65" s="25"/>
-      <c r="D65" s="32"/>
+      <c r="D65" s="31"/>
       <c r="E65" s="4"/>
       <c r="G65" s="1"/>
       <c r="H65" s="2"/>
@@ -28914,7 +29033,7 @@
       <c r="A66" s="2"/>
       <c r="B66" s="27"/>
       <c r="C66" s="26"/>
-      <c r="D66" s="32"/>
+      <c r="D66" s="31"/>
       <c r="E66" s="4"/>
       <c r="G66" s="1"/>
       <c r="H66" s="2"/>
@@ -28935,7 +29054,7 @@
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="32"/>
+      <c r="D67" s="31"/>
       <c r="E67" s="4"/>
       <c r="G67" s="1"/>
       <c r="H67" s="2"/>
@@ -28956,7 +29075,7 @@
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="25"/>
-      <c r="D68" s="32"/>
+      <c r="D68" s="31"/>
       <c r="E68" s="4"/>
       <c r="G68" s="1"/>
       <c r="H68" s="2"/>
@@ -28977,7 +29096,7 @@
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="32"/>
+      <c r="D69" s="31"/>
       <c r="E69" s="4"/>
       <c r="G69" s="1"/>
       <c r="H69" s="2"/>
@@ -28998,7 +29117,7 @@
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="25"/>
-      <c r="D70" s="32"/>
+      <c r="D70" s="31"/>
       <c r="E70" s="27"/>
       <c r="G70" s="1"/>
       <c r="H70" s="2"/>
@@ -29915,7 +30034,7 @@
       <c r="A4" s="28"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="34"/>
+      <c r="A5" s="33"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="15"/>
@@ -30002,7 +30121,7 @@
       <c r="B22" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="31" t="s">
         <v>1044</v>
       </c>
       <c r="D22" s="2" t="s">
@@ -30019,7 +30138,7 @@
       <c r="C23" s="2" t="s">
         <v>1048</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="31" t="s">
         <v>1047</v>
       </c>
     </row>
@@ -30033,7 +30152,7 @@
       <c r="C24" s="25" t="s">
         <v>1051</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="31" t="s">
         <v>1050</v>
       </c>
     </row>
@@ -30047,28 +30166,28 @@
       <c r="C25" s="2" t="s">
         <v>1054</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="31" t="s">
         <v>1053</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="C26" s="25"/>
-      <c r="D26" s="32"/>
+      <c r="D26" s="31"/>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
-      <c r="D28" s="32"/>
+      <c r="D28" s="31"/>
       <c r="E28" s="24"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="C29" s="25"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
@@ -30078,7 +30197,7 @@
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
-      <c r="C31" s="32"/>
+      <c r="C31" s="31"/>
       <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
@@ -30090,92 +30209,92 @@
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="C33" s="25"/>
-      <c r="D33" s="32"/>
+      <c r="D33" s="31"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="C34" s="25"/>
-      <c r="D34" s="32"/>
+      <c r="D34" s="31"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="C35" s="25"/>
-      <c r="D35" s="32"/>
+      <c r="D35" s="31"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="C36" s="25"/>
-      <c r="D36" s="32"/>
+      <c r="D36" s="31"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="C37" s="25"/>
-      <c r="D37" s="32"/>
+      <c r="D37" s="31"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="C38" s="25"/>
-      <c r="D38" s="32"/>
+      <c r="D38" s="31"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
-      <c r="D39" s="32"/>
+      <c r="D39" s="31"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="C40" s="25"/>
-      <c r="D40" s="32"/>
+      <c r="D40" s="31"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
-      <c r="D41" s="32"/>
+      <c r="D41" s="31"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="C42" s="25"/>
-      <c r="D42" s="32"/>
+      <c r="D42" s="31"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="C43" s="25"/>
-      <c r="D43" s="32"/>
+      <c r="D43" s="31"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
-      <c r="D44" s="32"/>
+      <c r="D44" s="31"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="C45" s="25"/>
-      <c r="D45" s="32"/>
-      <c r="E45" s="32"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
-      <c r="D46" s="32"/>
+      <c r="D46" s="31"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D47" s="32"/>
+      <c r="D47" s="31"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D48" s="32"/>
+      <c r="D48" s="31"/>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
       <c r="C49" s="25"/>
-      <c r="D49" s="32"/>
+      <c r="D49" s="31"/>
       <c r="E49" s="1"/>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
       <c r="C50" s="25"/>
-      <c r="D50" s="32"/>
+      <c r="D50" s="31"/>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
       <c r="C51" s="25"/>
-      <c r="D51" s="32"/>
+      <c r="D51" s="31"/>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C52" s="1"/>
@@ -30195,7 +30314,7 @@
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="25"/>
-      <c r="D53" s="32"/>
+      <c r="D53" s="31"/>
       <c r="E53" s="4"/>
       <c r="G53" s="1"/>
       <c r="H53" s="2"/>
@@ -30217,7 +30336,7 @@
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="25"/>
-      <c r="D55" s="32"/>
+      <c r="D55" s="31"/>
       <c r="E55" s="4"/>
       <c r="G55" s="1"/>
       <c r="H55" s="2"/>
@@ -30238,7 +30357,7 @@
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="25"/>
-      <c r="D56" s="32"/>
+      <c r="D56" s="31"/>
       <c r="E56" s="4"/>
       <c r="G56" s="1"/>
       <c r="H56" s="2"/>
@@ -30259,7 +30378,7 @@
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="25"/>
-      <c r="D57" s="32"/>
+      <c r="D57" s="31"/>
       <c r="E57" s="4"/>
       <c r="G57" s="1"/>
       <c r="H57" s="2"/>
@@ -30280,7 +30399,7 @@
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="25"/>
-      <c r="D58" s="32"/>
+      <c r="D58" s="31"/>
       <c r="E58" s="4"/>
       <c r="G58" s="1"/>
       <c r="H58" s="2"/>
@@ -30301,7 +30420,7 @@
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="25"/>
-      <c r="D59" s="32"/>
+      <c r="D59" s="31"/>
       <c r="E59" s="4"/>
       <c r="G59" s="1"/>
       <c r="H59" s="2"/>
@@ -30322,7 +30441,7 @@
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="25"/>
-      <c r="D60" s="32"/>
+      <c r="D60" s="31"/>
       <c r="E60" s="4"/>
       <c r="G60" s="1"/>
       <c r="H60" s="2"/>
@@ -30343,7 +30462,7 @@
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="25"/>
-      <c r="D61" s="32"/>
+      <c r="D61" s="31"/>
       <c r="E61" s="4"/>
       <c r="G61" s="1"/>
       <c r="H61" s="2"/>
@@ -30364,7 +30483,7 @@
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="25"/>
-      <c r="D62" s="32"/>
+      <c r="D62" s="31"/>
       <c r="E62" s="4"/>
       <c r="G62" s="1"/>
       <c r="H62" s="2"/>
@@ -30385,7 +30504,7 @@
       <c r="A63" s="2"/>
       <c r="B63" s="27"/>
       <c r="C63" s="25"/>
-      <c r="D63" s="32"/>
+      <c r="D63" s="31"/>
       <c r="E63" s="4"/>
       <c r="G63" s="1"/>
       <c r="H63" s="2"/>
@@ -30406,7 +30525,7 @@
       <c r="A64" s="2"/>
       <c r="B64" s="27"/>
       <c r="C64" s="25"/>
-      <c r="D64" s="32"/>
+      <c r="D64" s="31"/>
       <c r="E64" s="4"/>
       <c r="G64" s="1"/>
       <c r="H64" s="2"/>
@@ -30427,7 +30546,7 @@
       <c r="A65" s="2"/>
       <c r="B65" s="27"/>
       <c r="C65" s="25"/>
-      <c r="D65" s="32"/>
+      <c r="D65" s="31"/>
       <c r="E65" s="4"/>
       <c r="G65" s="1"/>
       <c r="H65" s="2"/>
@@ -30448,7 +30567,7 @@
       <c r="A66" s="2"/>
       <c r="B66" s="27"/>
       <c r="C66" s="26"/>
-      <c r="D66" s="32"/>
+      <c r="D66" s="31"/>
       <c r="E66" s="4"/>
       <c r="G66" s="1"/>
       <c r="H66" s="2"/>
@@ -30469,7 +30588,7 @@
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="32"/>
+      <c r="D67" s="31"/>
       <c r="E67" s="4"/>
       <c r="G67" s="1"/>
       <c r="H67" s="2"/>
@@ -30490,7 +30609,7 @@
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="25"/>
-      <c r="D68" s="32"/>
+      <c r="D68" s="31"/>
       <c r="E68" s="4"/>
       <c r="G68" s="1"/>
       <c r="H68" s="2"/>
@@ -30511,7 +30630,7 @@
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="32"/>
+      <c r="D69" s="31"/>
       <c r="E69" s="4"/>
       <c r="G69" s="1"/>
       <c r="H69" s="2"/>
@@ -30532,7 +30651,7 @@
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="25"/>
-      <c r="D70" s="32"/>
+      <c r="D70" s="31"/>
       <c r="E70" s="27"/>
       <c r="G70" s="1"/>
       <c r="H70" s="2"/>

--- a/4 четверть_13_JavaScript_sugarJS.xlsx
+++ b/4 четверть_13_JavaScript_sugarJS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4EACC82-AF8E-4C0E-93FF-DE353A550C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E030B44-31A4-4AF8-B237-E283ABA11370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sugarjs" sheetId="20" r:id="rId1"/>
@@ -18720,12 +18720,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -19065,9 +19073,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -19078,50 +19086,50 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -19130,39 +19138,42 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -19179,10 +19190,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -23484,7 +23498,7 @@
       <c r="F60" s="2"/>
     </row>
     <row r="61" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="23" t="s">
+      <c r="A61" s="42" t="s">
         <v>690</v>
       </c>
       <c r="B61" s="2"/>
@@ -24910,7 +24924,7 @@
       </c>
       <c r="B111" s="11"/>
     </row>
-    <row r="112" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>200</v>
       </c>
@@ -25240,7 +25254,7 @@
       <c r="F151" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -28506,7 +28520,7 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="41" t="s">
         <v>1020</v>
       </c>
       <c r="B30" s="1"/>

--- a/4 четверть_13_JavaScript_sugarJS.xlsx
+++ b/4 четверть_13_JavaScript_sugarJS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E030B44-31A4-4AF8-B237-E283ABA11370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFCAF4B3-4CB7-4B3D-9E10-73529873333C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8070" yWindow="-17895" windowWidth="23250" windowHeight="12450" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sugarjs" sheetId="20" r:id="rId1"/>
@@ -17830,186 +17830,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">compare </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>keys</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-boolean
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">аналог: 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>key</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> in { </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>planing</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: null, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>journal</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: null, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>planexport</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: null, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>favoriteexport</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: null }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Оператор in проверяет, существует ли свойство с указанным именем в объекте</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>[</t>
     </r>
     <r>
@@ -18715,17 +18535,252 @@
       <t>если с аргументом</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">compare </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>keys</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+boolean
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">аналог: 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> { </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>planing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: null, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>journal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: null, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>planexport</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: null, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>favoriteexport</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: null }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Оператор in проверяет, существует ли </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ключ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> с указанным именем в объекте</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="38" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -19073,7 +19128,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -19086,50 +19141,50 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="29" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="28" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -19138,39 +19193,42 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -19187,16 +19245,13 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -21191,7 +21246,7 @@
         <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>74</v>
@@ -21205,7 +21260,7 @@
         <v>13</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>109</v>
@@ -21287,10 +21342,10 @@
         <v>15</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>1085</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>1086</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>14</v>
@@ -21304,7 +21359,7 @@
         <v>197</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>43</v>
@@ -21438,7 +21493,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>45</v>
       </c>
@@ -21463,7 +21518,7 @@
         <v>174</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="D63" s="14" t="s">
         <v>105</v>
@@ -21477,7 +21532,7 @@
         <v>174</v>
       </c>
       <c r="C64" s="38" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D64" s="14" t="s">
         <v>107</v>
@@ -21597,7 +21652,7 @@
         <v>48</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>47</v>
@@ -21611,7 +21666,7 @@
         <v>48</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>90</v>
@@ -21625,7 +21680,7 @@
         <v>193</v>
       </c>
       <c r="C76" s="36" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="D76" s="14" t="s">
         <v>142</v>
@@ -21694,7 +21749,7 @@
         <v>385</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>41</v>
@@ -21796,7 +21851,7 @@
         <v>187</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="D89" s="14" t="s">
         <v>150</v>
@@ -23362,7 +23417,7 @@
         <v>494</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>497</v>
@@ -23397,7 +23452,7 @@
         <v>499</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>501</v>
@@ -23430,7 +23485,7 @@
         <v>576</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>578</v>
@@ -23466,7 +23521,7 @@
         <v>580</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>582</v>
@@ -23484,7 +23539,7 @@
         <v>605</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>607</v>
@@ -24924,7 +24979,7 @@
       </c>
       <c r="B111" s="11"/>
     </row>
-    <row r="112" spans="1:24" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:24" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>200</v>
       </c>
@@ -25254,7 +25309,7 @@
       <c r="F151" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="20" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -26562,7 +26617,7 @@
         <v>346</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1079</v>
+        <v>1095</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>351</v>
@@ -27406,7 +27461,7 @@
         <v>82</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="C25" s="25" t="s">
         <v>748</v>
@@ -27476,7 +27531,7 @@
         <v>725</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C31" s="40" t="s">
         <v>882</v>
@@ -27490,7 +27545,7 @@
         <v>806</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C32" s="25" t="s">
         <v>883</v>
